--- a/Data_Raw/Manually_Collected_Data_Version2.xlsx
+++ b/Data_Raw/Manually_Collected_Data_Version2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\From BigDisk\GIT\Benefish_Data_Collection\Data_Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0C5421-203F-4471-A818-5981A2F9EB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62CAFA2-176A-4AEE-AFAD-4387F3637DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="913" firstSheet="4" activeTab="18" xr2:uid="{DADAB8C2-813A-4B64-AE11-C65CAFCECFBF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="913" firstSheet="8" activeTab="8" xr2:uid="{DADAB8C2-813A-4B64-AE11-C65CAFCECFBF}"/>
   </bookViews>
   <sheets>
     <sheet name="American_Samoa" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="Wallis_and_Futuna" sheetId="22" r:id="rId22"/>
     <sheet name="International_Waters" sheetId="23" r:id="rId23"/>
     <sheet name="Summary_Tables" sheetId="24" r:id="rId24"/>
+    <sheet name="Exchange_Rates" sheetId="25" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_ftn1" localSheetId="12">Palau!#REF!</definedName>
@@ -44,7 +45,7 @@
     <definedName name="_ftnref1" localSheetId="12">Palau!$D$69</definedName>
     <definedName name="_ftnref2" localSheetId="12">Palau!$E$69</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5950" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5968" uniqueCount="1356">
   <si>
     <t>Live fish</t>
   </si>
@@ -5153,6 +5154,54 @@
   <si>
     <t>TotalXXValue</t>
   </si>
+  <si>
+    <t>56 t</t>
+  </si>
+  <si>
+    <t>12 t</t>
+  </si>
+  <si>
+    <t>10 t</t>
+  </si>
+  <si>
+    <t>3150 t</t>
+  </si>
+  <si>
+    <t>12334 pcs</t>
+  </si>
+  <si>
+    <t>NZ$</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>F$</t>
+  </si>
+  <si>
+    <t>A$</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>ST$</t>
+  </si>
+  <si>
+    <t>T$</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>0.1 t</t>
+  </si>
+  <si>
+    <t>8 t</t>
+  </si>
+  <si>
+    <t>0 t</t>
+  </si>
 </sst>
 </file>
 
@@ -5161,7 +5210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5314,6 +5363,16 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="MyriadPro-Light"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="MyriadPro-Light"/>
     </font>
   </fonts>
   <fills count="7">
@@ -6590,7 +6649,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="585">
+  <cellXfs count="587">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7828,6 +7887,12 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8982,20 +9047,20 @@
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1"/>
     <row r="18" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A18" s="433" t="s">
+      <c r="A18" s="435" t="s">
         <v>887</v>
       </c>
-      <c r="B18" s="434"/>
-      <c r="C18" s="434"/>
-      <c r="D18" s="434"/>
-      <c r="E18" s="434"/>
-      <c r="F18" s="435"/>
+      <c r="B18" s="436"/>
+      <c r="C18" s="436"/>
+      <c r="D18" s="436"/>
+      <c r="E18" s="436"/>
+      <c r="F18" s="437"/>
       <c r="G18" s="252"/>
-      <c r="H18" s="436" t="s">
+      <c r="H18" s="438" t="s">
         <v>888</v>
       </c>
-      <c r="I18" s="436"/>
-      <c r="J18" s="436"/>
+      <c r="I18" s="438"/>
+      <c r="J18" s="438"/>
       <c r="K18" s="328"/>
       <c r="L18" s="11" t="s">
         <v>8</v>
@@ -9520,7 +9585,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="418" t="s">
+      <c r="A41" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B41" s="7">
@@ -9540,7 +9605,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="419"/>
+      <c r="A42" s="421"/>
       <c r="B42" s="7">
         <v>2007</v>
       </c>
@@ -9558,7 +9623,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="419"/>
+      <c r="A43" s="421"/>
       <c r="B43" s="7">
         <v>2014</v>
       </c>
@@ -9576,7 +9641,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="420"/>
+      <c r="A44" s="422"/>
       <c r="B44" s="69">
         <v>2021</v>
       </c>
@@ -9594,7 +9659,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="421" t="s">
+      <c r="A45" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B45" s="20">
@@ -9614,7 +9679,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="422"/>
+      <c r="A46" s="424"/>
       <c r="B46" s="20">
         <v>2007</v>
       </c>
@@ -9632,7 +9697,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="422"/>
+      <c r="A47" s="424"/>
       <c r="B47" s="20">
         <v>2014</v>
       </c>
@@ -9650,7 +9715,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="437"/>
+      <c r="A48" s="439"/>
       <c r="B48" s="20">
         <v>2021</v>
       </c>
@@ -9668,7 +9733,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="418" t="s">
+      <c r="A49" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B49" s="7">
@@ -9688,7 +9753,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="419"/>
+      <c r="A50" s="421"/>
       <c r="B50" s="7">
         <v>2007</v>
       </c>
@@ -9706,7 +9771,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="419"/>
+      <c r="A51" s="421"/>
       <c r="B51" s="7">
         <v>2014</v>
       </c>
@@ -9724,7 +9789,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="420"/>
+      <c r="A52" s="422"/>
       <c r="B52" s="69">
         <v>2021</v>
       </c>
@@ -9742,7 +9807,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="430" t="s">
+      <c r="A53" s="432" t="s">
         <v>19</v>
       </c>
       <c r="B53" s="20">
@@ -9762,7 +9827,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="431"/>
+      <c r="A54" s="433"/>
       <c r="B54" s="20">
         <v>2007</v>
       </c>
@@ -9780,7 +9845,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="431"/>
+      <c r="A55" s="433"/>
       <c r="B55" s="20">
         <v>2014</v>
       </c>
@@ -9798,7 +9863,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="432"/>
+      <c r="A56" s="434"/>
       <c r="B56" s="20">
         <v>2021</v>
       </c>
@@ -9816,7 +9881,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="418" t="s">
+      <c r="A57" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B57" s="7">
@@ -9836,7 +9901,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="419"/>
+      <c r="A58" s="421"/>
       <c r="B58" s="7">
         <v>2007</v>
       </c>
@@ -9854,7 +9919,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="419"/>
+      <c r="A59" s="421"/>
       <c r="B59" s="7">
         <v>2014</v>
       </c>
@@ -9872,7 +9937,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="420"/>
+      <c r="A60" s="422"/>
       <c r="B60" s="69">
         <v>2021</v>
       </c>
@@ -9890,7 +9955,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="421" t="s">
+      <c r="A61" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="20">
@@ -9910,7 +9975,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="422"/>
+      <c r="A62" s="424"/>
       <c r="B62" s="20">
         <v>2007</v>
       </c>
@@ -9928,7 +9993,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="422"/>
+      <c r="A63" s="424"/>
       <c r="B63" s="20">
         <v>2014</v>
       </c>
@@ -9946,7 +10011,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="423"/>
+      <c r="A64" s="425"/>
       <c r="B64" s="24">
         <v>2021</v>
       </c>
@@ -9965,16 +10030,16 @@
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="67" spans="1:8" ht="48">
-      <c r="A67" s="424" t="s">
+      <c r="A67" s="426" t="s">
         <v>12</v>
       </c>
       <c r="B67" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C67" s="426" t="s">
+      <c r="C67" s="428" t="s">
         <v>44</v>
       </c>
-      <c r="D67" s="428" t="s">
+      <c r="D67" s="430" t="s">
         <v>133</v>
       </c>
       <c r="E67" s="11" t="s">
@@ -9985,12 +10050,12 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="18.75" thickBot="1">
-      <c r="A68" s="425"/>
+      <c r="A68" s="427"/>
       <c r="B68" s="135" t="s">
         <v>904</v>
       </c>
-      <c r="C68" s="427"/>
-      <c r="D68" s="429"/>
+      <c r="C68" s="429"/>
+      <c r="D68" s="431"/>
       <c r="E68" s="30" t="s">
         <v>905</v>
       </c>
@@ -11069,16 +11134,16 @@
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="41" spans="1:6">
-      <c r="A41" s="453" t="s">
+      <c r="A41" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B41" s="46" t="s">
         <v>631</v>
       </c>
-      <c r="C41" s="426" t="s">
+      <c r="C41" s="428" t="s">
         <v>353</v>
       </c>
-      <c r="D41" s="428" t="s">
+      <c r="D41" s="430" t="s">
         <v>1042</v>
       </c>
       <c r="E41" s="11" t="s">
@@ -11089,12 +11154,12 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="454"/>
+      <c r="A42" s="456"/>
       <c r="B42" s="36" t="s">
         <v>1041</v>
       </c>
-      <c r="C42" s="427"/>
-      <c r="D42" s="429"/>
+      <c r="C42" s="429"/>
+      <c r="D42" s="431"/>
       <c r="E42" s="30" t="s">
         <v>26</v>
       </c>
@@ -11103,7 +11168,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A43" s="418" t="s">
+      <c r="A43" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="7">
@@ -11123,7 +11188,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="419"/>
+      <c r="A44" s="421"/>
       <c r="B44" s="7">
         <v>2007</v>
       </c>
@@ -11141,7 +11206,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="419"/>
+      <c r="A45" s="421"/>
       <c r="B45" s="7">
         <v>2014</v>
       </c>
@@ -11159,7 +11224,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="420"/>
+      <c r="A46" s="422"/>
       <c r="B46" s="69">
         <v>2021</v>
       </c>
@@ -11177,7 +11242,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A47" s="421" t="s">
+      <c r="A47" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="20">
@@ -11197,7 +11262,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="422"/>
+      <c r="A48" s="424"/>
       <c r="B48" s="20">
         <v>2007</v>
       </c>
@@ -11215,7 +11280,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="422"/>
+      <c r="A49" s="424"/>
       <c r="B49" s="20">
         <v>2014</v>
       </c>
@@ -11233,7 +11298,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="437"/>
+      <c r="A50" s="439"/>
       <c r="B50" s="20">
         <v>2021</v>
       </c>
@@ -11251,7 +11316,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A51" s="418" t="s">
+      <c r="A51" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B51" s="7">
@@ -11271,7 +11336,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="419"/>
+      <c r="A52" s="421"/>
       <c r="B52" s="7">
         <v>2007</v>
       </c>
@@ -11289,7 +11354,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="84.75" thickBot="1">
-      <c r="A53" s="419"/>
+      <c r="A53" s="421"/>
       <c r="B53" s="7">
         <v>2014</v>
       </c>
@@ -11307,7 +11372,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="420"/>
+      <c r="A54" s="422"/>
       <c r="B54" s="69">
         <v>2021</v>
       </c>
@@ -11325,7 +11390,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A55" s="421" t="s">
+      <c r="A55" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B55" s="20">
@@ -11345,7 +11410,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="422"/>
+      <c r="A56" s="424"/>
       <c r="B56" s="20">
         <v>2007</v>
       </c>
@@ -11363,7 +11428,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="422"/>
+      <c r="A57" s="424"/>
       <c r="B57" s="20">
         <v>2014</v>
       </c>
@@ -11381,7 +11446,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="437"/>
+      <c r="A58" s="439"/>
       <c r="B58" s="20">
         <v>2021</v>
       </c>
@@ -11399,7 +11464,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A59" s="418" t="s">
+      <c r="A59" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B59" s="7">
@@ -11419,7 +11484,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="419"/>
+      <c r="A60" s="421"/>
       <c r="B60" s="7">
         <v>2007</v>
       </c>
@@ -11437,7 +11502,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="419"/>
+      <c r="A61" s="421"/>
       <c r="B61" s="7">
         <v>2014</v>
       </c>
@@ -11455,7 +11520,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="420"/>
+      <c r="A62" s="422"/>
       <c r="B62" s="69">
         <v>2021</v>
       </c>
@@ -11473,7 +11538,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A63" s="421" t="s">
+      <c r="A63" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="20">
@@ -11493,7 +11558,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="422"/>
+      <c r="A64" s="424"/>
       <c r="B64" s="20">
         <v>2007</v>
       </c>
@@ -11511,7 +11576,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A65" s="422"/>
+      <c r="A65" s="424"/>
       <c r="B65" s="20">
         <v>2014</v>
       </c>
@@ -11529,7 +11594,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A66" s="423"/>
+      <c r="A66" s="425"/>
       <c r="B66" s="24">
         <v>2021</v>
       </c>
@@ -11548,13 +11613,13 @@
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="69" spans="1:9" ht="48">
-      <c r="A69" s="453" t="s">
+      <c r="A69" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B69" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C69" s="445" t="s">
+      <c r="C69" s="447" t="s">
         <v>44</v>
       </c>
       <c r="D69" s="47" t="s">
@@ -11568,11 +11633,11 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="18.75" thickBot="1">
-      <c r="A70" s="454"/>
+      <c r="A70" s="456"/>
       <c r="B70" s="178" t="s">
         <v>1045</v>
       </c>
-      <c r="C70" s="476"/>
+      <c r="C70" s="478"/>
       <c r="D70" s="136" t="s">
         <v>921</v>
       </c>
@@ -11965,10 +12030,10 @@
     </row>
     <row r="89" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="90" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A90" s="512">
+      <c r="A90" s="514">
         <v>2016</v>
       </c>
-      <c r="B90" s="513"/>
+      <c r="B90" s="515"/>
       <c r="C90" s="3">
         <v>2017</v>
       </c>
@@ -12229,19 +12294,19 @@
         <v>36</v>
       </c>
       <c r="B101" s="252"/>
-      <c r="C101" s="436" t="s">
+      <c r="C101" s="438" t="s">
         <v>1048</v>
       </c>
-      <c r="D101" s="507"/>
-      <c r="E101" s="508" t="s">
+      <c r="D101" s="509"/>
+      <c r="E101" s="510" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="509"/>
+      <c r="F101" s="511"/>
       <c r="G101" s="252"/>
-      <c r="H101" s="509" t="s">
+      <c r="H101" s="511" t="s">
         <v>75</v>
       </c>
-      <c r="I101" s="509"/>
+      <c r="I101" s="511"/>
       <c r="J101" s="328"/>
       <c r="K101" s="11" t="s">
         <v>8</v>
@@ -12257,21 +12322,21 @@
       <c r="B102" s="101" t="s">
         <v>1063</v>
       </c>
-      <c r="C102" s="510" t="s">
+      <c r="C102" s="512" t="s">
         <v>1064</v>
       </c>
-      <c r="D102" s="511"/>
-      <c r="E102" s="510" t="s">
+      <c r="D102" s="513"/>
+      <c r="E102" s="512" t="s">
         <v>1063</v>
       </c>
-      <c r="F102" s="511"/>
+      <c r="F102" s="513"/>
       <c r="G102" s="7" t="s">
         <v>1064</v>
       </c>
-      <c r="H102" s="510" t="s">
+      <c r="H102" s="512" t="s">
         <v>1063</v>
       </c>
-      <c r="I102" s="511"/>
+      <c r="I102" s="513"/>
       <c r="J102" s="12" t="s">
         <v>1064</v>
       </c>
@@ -12289,21 +12354,21 @@
       <c r="B103" s="311">
         <v>0.8</v>
       </c>
-      <c r="C103" s="503">
+      <c r="C103" s="505">
         <v>0.2</v>
       </c>
-      <c r="D103" s="504"/>
-      <c r="E103" s="503">
+      <c r="D103" s="506"/>
+      <c r="E103" s="505">
         <v>0.94</v>
       </c>
-      <c r="F103" s="504"/>
+      <c r="F103" s="506"/>
       <c r="G103" s="311">
         <v>0.06</v>
       </c>
-      <c r="H103" s="503">
+      <c r="H103" s="505">
         <v>1</v>
       </c>
-      <c r="I103" s="504"/>
+      <c r="I103" s="506"/>
       <c r="J103" s="312">
         <v>0</v>
       </c>
@@ -12397,21 +12462,21 @@
       <c r="B106" s="69" t="s">
         <v>1074</v>
       </c>
-      <c r="C106" s="505" t="s">
+      <c r="C106" s="507" t="s">
         <v>1075</v>
       </c>
-      <c r="D106" s="506"/>
-      <c r="E106" s="505" t="s">
+      <c r="D106" s="508"/>
+      <c r="E106" s="507" t="s">
         <v>1076</v>
       </c>
-      <c r="F106" s="506"/>
+      <c r="F106" s="508"/>
       <c r="G106" s="69" t="s">
         <v>1077</v>
       </c>
-      <c r="H106" s="505" t="s">
+      <c r="H106" s="507" t="s">
         <v>1078</v>
       </c>
-      <c r="I106" s="506"/>
+      <c r="I106" s="508"/>
       <c r="J106" s="51" t="s">
         <v>105</v>
       </c>
@@ -12424,7 +12489,7 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="109" spans="1:12" ht="24">
-      <c r="A109" s="453" t="s">
+      <c r="A109" s="455" t="s">
         <v>1081</v>
       </c>
       <c r="B109" s="46" t="s">
@@ -12433,10 +12498,10 @@
       <c r="C109" s="46" t="s">
         <v>1082</v>
       </c>
-      <c r="D109" s="426" t="s">
+      <c r="D109" s="428" t="s">
         <v>1085</v>
       </c>
-      <c r="E109" s="428" t="s">
+      <c r="E109" s="430" t="s">
         <v>1086</v>
       </c>
       <c r="F109" s="11" t="s">
@@ -12447,15 +12512,15 @@
       </c>
     </row>
     <row r="110" spans="1:12" ht="36.75" thickBot="1">
-      <c r="A110" s="454"/>
+      <c r="A110" s="456"/>
       <c r="B110" s="36" t="s">
         <v>1083</v>
       </c>
       <c r="C110" s="36" t="s">
         <v>1084</v>
       </c>
-      <c r="D110" s="427"/>
-      <c r="E110" s="429"/>
+      <c r="D110" s="429"/>
+      <c r="E110" s="431"/>
       <c r="F110" s="30" t="s">
         <v>1090</v>
       </c>
@@ -12852,7 +12917,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A11" s="418" t="s">
+      <c r="A11" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="7">
@@ -12872,7 +12937,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A12" s="419"/>
+      <c r="A12" s="421"/>
       <c r="B12" s="7">
         <v>2007</v>
       </c>
@@ -12890,7 +12955,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A13" s="419"/>
+      <c r="A13" s="421"/>
       <c r="B13" s="7">
         <v>2014</v>
       </c>
@@ -12908,7 +12973,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A14" s="420"/>
+      <c r="A14" s="422"/>
       <c r="B14" s="69">
         <v>2021</v>
       </c>
@@ -12926,7 +12991,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A15" s="421" t="s">
+      <c r="A15" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="20">
@@ -12946,7 +13011,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A16" s="422"/>
+      <c r="A16" s="424"/>
       <c r="B16" s="20">
         <v>2007</v>
       </c>
@@ -12964,7 +13029,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="422"/>
+      <c r="A17" s="424"/>
       <c r="B17" s="20">
         <v>2014</v>
       </c>
@@ -12982,7 +13047,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="437"/>
+      <c r="A18" s="439"/>
       <c r="B18" s="20">
         <v>2021</v>
       </c>
@@ -13000,7 +13065,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="514" t="s">
+      <c r="A19" s="516" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="7">
@@ -13020,7 +13085,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="515"/>
+      <c r="A20" s="517"/>
       <c r="B20" s="7">
         <v>2007</v>
       </c>
@@ -13038,7 +13103,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="515"/>
+      <c r="A21" s="517"/>
       <c r="B21" s="7">
         <v>2014</v>
       </c>
@@ -13056,7 +13121,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="516"/>
+      <c r="A22" s="518"/>
       <c r="B22" s="69">
         <v>2021</v>
       </c>
@@ -13074,7 +13139,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="421" t="s">
+      <c r="A23" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="20">
@@ -13094,7 +13159,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="422"/>
+      <c r="A24" s="424"/>
       <c r="B24" s="20">
         <v>2007</v>
       </c>
@@ -13112,7 +13177,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="422"/>
+      <c r="A25" s="424"/>
       <c r="B25" s="20">
         <v>2014</v>
       </c>
@@ -13130,7 +13195,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="437"/>
+      <c r="A26" s="439"/>
       <c r="B26" s="20">
         <v>2021</v>
       </c>
@@ -13148,7 +13213,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="418" t="s">
+      <c r="A27" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B27" s="7">
@@ -13168,7 +13233,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="419"/>
+      <c r="A28" s="421"/>
       <c r="B28" s="7">
         <v>2007</v>
       </c>
@@ -13186,7 +13251,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="419"/>
+      <c r="A29" s="421"/>
       <c r="B29" s="7">
         <v>2014</v>
       </c>
@@ -13204,7 +13269,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="420"/>
+      <c r="A30" s="422"/>
       <c r="B30" s="69">
         <v>2021</v>
       </c>
@@ -13222,7 +13287,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="421" t="s">
+      <c r="A31" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="20">
@@ -13242,7 +13307,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="422"/>
+      <c r="A32" s="424"/>
       <c r="B32" s="20">
         <v>2007</v>
       </c>
@@ -13260,7 +13325,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A33" s="422"/>
+      <c r="A33" s="424"/>
       <c r="B33" s="20">
         <v>2014</v>
       </c>
@@ -13278,7 +13343,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="423"/>
+      <c r="A34" s="425"/>
       <c r="B34" s="24">
         <v>2021</v>
       </c>
@@ -13388,16 +13453,16 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="41" spans="1:7" ht="48">
-      <c r="A41" s="453" t="s">
+      <c r="A41" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B41" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="426" t="s">
+      <c r="C41" s="428" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="428" t="s">
+      <c r="D41" s="430" t="s">
         <v>408</v>
       </c>
       <c r="E41" s="11" t="s">
@@ -13408,12 +13473,12 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="18.75" thickBot="1">
-      <c r="A42" s="454"/>
+      <c r="A42" s="456"/>
       <c r="B42" s="135" t="s">
         <v>407</v>
       </c>
-      <c r="C42" s="427"/>
-      <c r="D42" s="429"/>
+      <c r="C42" s="429"/>
+      <c r="D42" s="431"/>
       <c r="E42" s="30" t="s">
         <v>409</v>
       </c>
@@ -14087,11 +14152,11 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="10" spans="1:6" ht="30.6" customHeight="1">
-      <c r="A10" s="465"/>
-      <c r="B10" s="426" t="s">
+      <c r="A10" s="467"/>
+      <c r="B10" s="428" t="s">
         <v>1101</v>
       </c>
-      <c r="C10" s="426" t="s">
+      <c r="C10" s="428" t="s">
         <v>1098</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -14105,9 +14170,9 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A11" s="477"/>
-      <c r="B11" s="427"/>
-      <c r="C11" s="427"/>
+      <c r="A11" s="479"/>
+      <c r="B11" s="429"/>
+      <c r="C11" s="429"/>
       <c r="D11" s="136" t="s">
         <v>1103</v>
       </c>
@@ -14377,10 +14442,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="30" spans="1:6">
-      <c r="A30" s="424" t="s">
+      <c r="A30" s="426" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="426" t="s">
+      <c r="B30" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="46" t="s">
@@ -14397,8 +14462,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A31" s="425"/>
-      <c r="B31" s="427"/>
+      <c r="A31" s="427"/>
+      <c r="B31" s="429"/>
       <c r="C31" s="135" t="s">
         <v>197</v>
       </c>
@@ -14413,7 +14478,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="418" t="s">
+      <c r="A32" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="7">
@@ -14433,7 +14498,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="419"/>
+      <c r="A33" s="421"/>
       <c r="B33" s="7">
         <v>2007</v>
       </c>
@@ -14451,7 +14516,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="419"/>
+      <c r="A34" s="421"/>
       <c r="B34" s="7">
         <v>2014</v>
       </c>
@@ -14469,7 +14534,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="420"/>
+      <c r="A35" s="422"/>
       <c r="B35" s="69">
         <v>2021</v>
       </c>
@@ -14487,7 +14552,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="471" t="s">
+      <c r="A36" s="473" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="20">
@@ -14507,7 +14572,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="517"/>
+      <c r="A37" s="519"/>
       <c r="B37" s="20">
         <v>2007</v>
       </c>
@@ -14525,7 +14590,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="517"/>
+      <c r="A38" s="519"/>
       <c r="B38" s="20">
         <v>2014</v>
       </c>
@@ -14543,7 +14608,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="472"/>
+      <c r="A39" s="474"/>
       <c r="B39" s="20">
         <v>2021</v>
       </c>
@@ -14561,7 +14626,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="418" t="s">
+      <c r="A40" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B40" s="7">
@@ -14581,7 +14646,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="419"/>
+      <c r="A41" s="421"/>
       <c r="B41" s="7">
         <v>2007</v>
       </c>
@@ -14599,7 +14664,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="419"/>
+      <c r="A42" s="421"/>
       <c r="B42" s="7">
         <v>2014</v>
       </c>
@@ -14617,7 +14682,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="420"/>
+      <c r="A43" s="422"/>
       <c r="B43" s="69">
         <v>2021</v>
       </c>
@@ -14635,7 +14700,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="471" t="s">
+      <c r="A44" s="473" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="20">
@@ -14655,7 +14720,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="517"/>
+      <c r="A45" s="519"/>
       <c r="B45" s="20">
         <v>2007</v>
       </c>
@@ -14673,7 +14738,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="517"/>
+      <c r="A46" s="519"/>
       <c r="B46" s="20">
         <v>2014</v>
       </c>
@@ -14691,7 +14756,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="472"/>
+      <c r="A47" s="474"/>
       <c r="B47" s="20">
         <v>2021</v>
       </c>
@@ -14709,7 +14774,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="418" t="s">
+      <c r="A48" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B48" s="7">
@@ -14729,7 +14794,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="419"/>
+      <c r="A49" s="421"/>
       <c r="B49" s="7">
         <v>2007</v>
       </c>
@@ -14747,7 +14812,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="419"/>
+      <c r="A50" s="421"/>
       <c r="B50" s="7">
         <v>2014</v>
       </c>
@@ -14765,7 +14830,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="420"/>
+      <c r="A51" s="422"/>
       <c r="B51" s="69">
         <v>2021</v>
       </c>
@@ -14783,7 +14848,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="421" t="s">
+      <c r="A52" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="20">
@@ -14803,7 +14868,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="422"/>
+      <c r="A53" s="424"/>
       <c r="B53" s="20">
         <v>2007</v>
       </c>
@@ -14821,7 +14886,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="24.75" thickBot="1">
-      <c r="A54" s="422"/>
+      <c r="A54" s="424"/>
       <c r="B54" s="20">
         <v>2014</v>
       </c>
@@ -14839,7 +14904,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="423"/>
+      <c r="A55" s="425"/>
       <c r="B55" s="24">
         <v>2021</v>
       </c>
@@ -15778,13 +15843,13 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="43" spans="1:6" ht="24">
-      <c r="A43" s="453" t="s">
+      <c r="A43" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="525" t="s">
+      <c r="B43" s="527" t="s">
         <v>477</v>
       </c>
-      <c r="C43" s="526"/>
+      <c r="C43" s="528"/>
       <c r="D43" s="47" t="s">
         <v>478</v>
       </c>
@@ -15796,9 +15861,9 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="454"/>
-      <c r="B44" s="527"/>
-      <c r="C44" s="528"/>
+      <c r="A44" s="456"/>
+      <c r="B44" s="529"/>
+      <c r="C44" s="530"/>
       <c r="D44" s="136" t="s">
         <v>287</v>
       </c>
@@ -15810,7 +15875,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="418" t="s">
+      <c r="A45" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B45" s="7">
@@ -15830,7 +15895,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="419"/>
+      <c r="A46" s="421"/>
       <c r="B46" s="7">
         <v>2007</v>
       </c>
@@ -15848,7 +15913,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="419"/>
+      <c r="A47" s="421"/>
       <c r="B47" s="7">
         <v>2014</v>
       </c>
@@ -15866,7 +15931,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="420"/>
+      <c r="A48" s="422"/>
       <c r="B48" s="69">
         <v>2021</v>
       </c>
@@ -15884,7 +15949,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="421" t="s">
+      <c r="A49" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B49" s="20">
@@ -15904,7 +15969,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="422"/>
+      <c r="A50" s="424"/>
       <c r="B50" s="20">
         <v>2007</v>
       </c>
@@ -15922,7 +15987,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="422"/>
+      <c r="A51" s="424"/>
       <c r="B51" s="20">
         <v>2014</v>
       </c>
@@ -15940,7 +16005,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="437"/>
+      <c r="A52" s="439"/>
       <c r="B52" s="20">
         <v>2021</v>
       </c>
@@ -15958,7 +16023,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="418" t="s">
+      <c r="A53" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B53" s="7">
@@ -15978,7 +16043,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="419"/>
+      <c r="A54" s="421"/>
       <c r="B54" s="7">
         <v>2007</v>
       </c>
@@ -15996,7 +16061,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="419"/>
+      <c r="A55" s="421"/>
       <c r="B55" s="7">
         <v>2014</v>
       </c>
@@ -16014,7 +16079,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="420"/>
+      <c r="A56" s="422"/>
       <c r="B56" s="69">
         <v>2021</v>
       </c>
@@ -16032,7 +16097,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="421" t="s">
+      <c r="A57" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B57" s="20">
@@ -16052,7 +16117,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="422"/>
+      <c r="A58" s="424"/>
       <c r="B58" s="20">
         <v>2007</v>
       </c>
@@ -16070,7 +16135,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="422"/>
+      <c r="A59" s="424"/>
       <c r="B59" s="20">
         <v>2014</v>
       </c>
@@ -16088,7 +16153,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="437"/>
+      <c r="A60" s="439"/>
       <c r="B60" s="20">
         <v>2021</v>
       </c>
@@ -16106,7 +16171,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="418" t="s">
+      <c r="A61" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="7">
@@ -16126,7 +16191,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="419"/>
+      <c r="A62" s="421"/>
       <c r="B62" s="7">
         <v>2007</v>
       </c>
@@ -16144,7 +16209,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="420"/>
+      <c r="A63" s="422"/>
       <c r="B63" s="69">
         <v>2014</v>
       </c>
@@ -16162,7 +16227,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="421" t="s">
+      <c r="A64" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="20">
@@ -16182,7 +16247,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="24.75" thickBot="1">
-      <c r="A65" s="422"/>
+      <c r="A65" s="424"/>
       <c r="B65" s="20">
         <v>2007</v>
       </c>
@@ -16200,7 +16265,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="36.75" thickBot="1">
-      <c r="A66" s="422"/>
+      <c r="A66" s="424"/>
       <c r="B66" s="20">
         <v>2014</v>
       </c>
@@ -16218,7 +16283,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="24.75" thickBot="1">
-      <c r="A67" s="423"/>
+      <c r="A67" s="425"/>
       <c r="B67" s="24">
         <v>2021</v>
       </c>
@@ -16328,13 +16393,13 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="74" spans="1:7" ht="48">
-      <c r="A74" s="518" t="s">
+      <c r="A74" s="520" t="s">
         <v>12</v>
       </c>
       <c r="B74" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="426" t="s">
+      <c r="C74" s="428" t="s">
         <v>44</v>
       </c>
       <c r="D74" s="47" t="s">
@@ -16348,11 +16413,11 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="18.75" thickBot="1">
-      <c r="A75" s="519"/>
+      <c r="A75" s="521"/>
       <c r="B75" s="135" t="s">
         <v>490</v>
       </c>
-      <c r="C75" s="427"/>
+      <c r="C75" s="429"/>
       <c r="D75" s="136" t="s">
         <v>287</v>
       </c>
@@ -16695,17 +16760,17 @@
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="95" spans="1:8" ht="36">
-      <c r="A95" s="520"/>
-      <c r="B95" s="522" t="s">
+      <c r="A95" s="522"/>
+      <c r="B95" s="524" t="s">
         <v>499</v>
       </c>
-      <c r="C95" s="469" t="s">
+      <c r="C95" s="471" t="s">
         <v>500</v>
       </c>
       <c r="D95" s="46" t="s">
         <v>501</v>
       </c>
-      <c r="E95" s="467" t="s">
+      <c r="E95" s="469" t="s">
         <v>503</v>
       </c>
       <c r="F95" s="47" t="s">
@@ -16719,13 +16784,13 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="36.75" thickBot="1">
-      <c r="A96" s="521"/>
-      <c r="B96" s="523"/>
-      <c r="C96" s="524"/>
+      <c r="A96" s="523"/>
+      <c r="B96" s="525"/>
+      <c r="C96" s="526"/>
       <c r="D96" s="224" t="s">
         <v>502</v>
       </c>
-      <c r="E96" s="502"/>
+      <c r="E96" s="504"/>
       <c r="F96" s="38" t="s">
         <v>505</v>
       </c>
@@ -17326,13 +17391,13 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="20" spans="1:6">
-      <c r="A20" s="529" t="s">
+      <c r="A20" s="531" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="347" t="s">
         <v>285</v>
       </c>
-      <c r="C20" s="530" t="s">
+      <c r="C20" s="532" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="348" t="s">
@@ -17346,11 +17411,11 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="524"/>
+      <c r="A21" s="526"/>
       <c r="B21" s="286" t="s">
         <v>1118</v>
       </c>
-      <c r="C21" s="427"/>
+      <c r="C21" s="429"/>
       <c r="D21" s="178" t="s">
         <v>46</v>
       </c>
@@ -18058,16 +18123,16 @@
     </row>
     <row r="30" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="31" spans="1:7">
-      <c r="A31" s="453" t="s">
+      <c r="A31" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="467" t="s">
+      <c r="B31" s="469" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D31" s="428" t="s">
+      <c r="D31" s="430" t="s">
         <v>529</v>
       </c>
       <c r="E31" s="11" t="s">
@@ -18078,12 +18143,12 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="27.75" thickBot="1">
-      <c r="A32" s="454"/>
-      <c r="B32" s="502"/>
+      <c r="A32" s="456"/>
+      <c r="B32" s="504"/>
       <c r="C32" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="D32" s="429"/>
+      <c r="D32" s="431"/>
       <c r="E32" s="30" t="s">
         <v>26</v>
       </c>
@@ -18092,7 +18157,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="418" t="s">
+      <c r="A33" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="7">
@@ -18112,7 +18177,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="419"/>
+      <c r="A34" s="421"/>
       <c r="B34" s="7">
         <v>2007</v>
       </c>
@@ -18130,7 +18195,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="419"/>
+      <c r="A35" s="421"/>
       <c r="B35" s="7">
         <v>2014</v>
       </c>
@@ -18148,7 +18213,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="420"/>
+      <c r="A36" s="422"/>
       <c r="B36" s="69">
         <v>2021</v>
       </c>
@@ -18166,7 +18231,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="421" t="s">
+      <c r="A37" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B37" s="20">
@@ -18186,7 +18251,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="422"/>
+      <c r="A38" s="424"/>
       <c r="B38" s="20">
         <v>2007</v>
       </c>
@@ -18204,7 +18269,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="422"/>
+      <c r="A39" s="424"/>
       <c r="B39" s="20">
         <v>2014</v>
       </c>
@@ -18222,7 +18287,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="437"/>
+      <c r="A40" s="439"/>
       <c r="B40" s="20">
         <v>2021</v>
       </c>
@@ -18240,7 +18305,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="418" t="s">
+      <c r="A41" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B41" s="7">
@@ -18260,7 +18325,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="419"/>
+      <c r="A42" s="421"/>
       <c r="B42" s="7">
         <v>2007</v>
       </c>
@@ -18278,7 +18343,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="419"/>
+      <c r="A43" s="421"/>
       <c r="B43" s="7">
         <v>2014</v>
       </c>
@@ -18296,7 +18361,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="420"/>
+      <c r="A44" s="422"/>
       <c r="B44" s="69">
         <v>2021</v>
       </c>
@@ -18314,7 +18379,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="421" t="s">
+      <c r="A45" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B45" s="20">
@@ -18334,7 +18399,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="422"/>
+      <c r="A46" s="424"/>
       <c r="B46" s="20">
         <v>2007</v>
       </c>
@@ -18352,7 +18417,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="422"/>
+      <c r="A47" s="424"/>
       <c r="B47" s="20">
         <v>2014</v>
       </c>
@@ -18370,7 +18435,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="437"/>
+      <c r="A48" s="439"/>
       <c r="B48" s="20">
         <v>2021</v>
       </c>
@@ -18388,7 +18453,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A49" s="418" t="s">
+      <c r="A49" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B49" s="7">
@@ -18408,7 +18473,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A50" s="419"/>
+      <c r="A50" s="421"/>
       <c r="B50" s="7">
         <v>2007</v>
       </c>
@@ -18426,7 +18491,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A51" s="419"/>
+      <c r="A51" s="421"/>
       <c r="B51" s="7">
         <v>2014</v>
       </c>
@@ -18444,7 +18509,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A52" s="420"/>
+      <c r="A52" s="422"/>
       <c r="B52" s="69">
         <v>2021</v>
       </c>
@@ -18462,7 +18527,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A53" s="421" t="s">
+      <c r="A53" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="20">
@@ -18482,7 +18547,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A54" s="422"/>
+      <c r="A54" s="424"/>
       <c r="B54" s="20">
         <v>2007</v>
       </c>
@@ -18500,7 +18565,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="36.75" thickBot="1">
-      <c r="A55" s="422"/>
+      <c r="A55" s="424"/>
       <c r="B55" s="20">
         <v>2014</v>
       </c>
@@ -18518,7 +18583,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A56" s="423"/>
+      <c r="A56" s="425"/>
       <c r="B56" s="24">
         <v>2021</v>
       </c>
@@ -18781,16 +18846,16 @@
     </row>
     <row r="65" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="66" spans="1:6" ht="60">
-      <c r="A66" s="453" t="s">
+      <c r="A66" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B66" s="231" t="s">
         <v>285</v>
       </c>
-      <c r="C66" s="533" t="s">
+      <c r="C66" s="535" t="s">
         <v>44</v>
       </c>
-      <c r="D66" s="531" t="s">
+      <c r="D66" s="533" t="s">
         <v>541</v>
       </c>
       <c r="E66" s="11" t="s">
@@ -18801,12 +18866,12 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="18.75" thickBot="1">
-      <c r="A67" s="454"/>
+      <c r="A67" s="456"/>
       <c r="B67" s="135" t="s">
         <v>540</v>
       </c>
-      <c r="C67" s="534"/>
-      <c r="D67" s="532"/>
+      <c r="C67" s="536"/>
+      <c r="D67" s="534"/>
       <c r="E67" s="30" t="s">
         <v>51</v>
       </c>
@@ -19022,17 +19087,17 @@
     </row>
     <row r="80" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="81" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A81" s="453" t="s">
+      <c r="A81" s="455" t="s">
         <v>556</v>
       </c>
-      <c r="B81" s="461" t="s">
+      <c r="B81" s="463" t="s">
         <v>557</v>
       </c>
-      <c r="C81" s="464"/>
-      <c r="D81" s="464"/>
-      <c r="E81" s="464"/>
-      <c r="F81" s="464"/>
-      <c r="G81" s="462"/>
+      <c r="C81" s="466"/>
+      <c r="D81" s="466"/>
+      <c r="E81" s="466"/>
+      <c r="F81" s="466"/>
+      <c r="G81" s="464"/>
       <c r="H81" s="11" t="s">
         <v>8</v>
       </c>
@@ -19041,19 +19106,19 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A82" s="535"/>
-      <c r="B82" s="537">
+      <c r="A82" s="537"/>
+      <c r="B82" s="539">
         <v>2018</v>
       </c>
-      <c r="C82" s="538"/>
-      <c r="D82" s="537">
+      <c r="C82" s="540"/>
+      <c r="D82" s="539">
         <v>2019</v>
       </c>
-      <c r="E82" s="538"/>
-      <c r="F82" s="537">
+      <c r="E82" s="540"/>
+      <c r="F82" s="539">
         <v>2020</v>
       </c>
-      <c r="G82" s="539"/>
+      <c r="G82" s="541"/>
       <c r="H82" s="30" t="s">
         <v>577</v>
       </c>
@@ -19062,7 +19127,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A83" s="536"/>
+      <c r="A83" s="538"/>
       <c r="B83" s="234" t="s">
         <v>558</v>
       </c>
@@ -19671,6 +19736,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F46E2DC-7814-4582-91B0-360FF40F7368}">
   <dimension ref="A1:G137"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1">
       <c r="A1" s="253"/>
@@ -19693,7 +19767,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="24.75" thickBot="1">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>93</v>
       </c>
@@ -19716,7 +19790,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24.75" thickBot="1">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1">
       <c r="A3" s="6" t="s">
         <v>613</v>
       </c>
@@ -19801,7 +19875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24.75" thickBot="1">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>93</v>
       </c>
@@ -19818,7 +19892,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24.75" thickBot="1">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>613</v>
       </c>
@@ -19870,7 +19944,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
-    <row r="13" spans="1:7" ht="24.75" thickBot="1">
+    <row r="13" spans="1:7" ht="15.75" thickBot="1">
       <c r="A13" s="253"/>
       <c r="B13" s="254" t="s">
         <v>353</v>
@@ -19888,7 +19962,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24.75" thickBot="1">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>93</v>
       </c>
@@ -19949,7 +20023,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="18" spans="1:6" ht="24.75" thickBot="1">
+    <row r="18" spans="1:6" ht="15.75" thickBot="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
         <v>353</v>
@@ -20016,7 +20090,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="23" spans="1:6" ht="24.75" thickBot="1">
+    <row r="23" spans="1:6" ht="15.75" thickBot="1">
       <c r="A23" s="71" t="s">
         <v>12</v>
       </c>
@@ -20033,7 +20107,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="36.75" thickBot="1">
+    <row r="24" spans="1:6" ht="15.75" thickBot="1">
       <c r="A24" s="40" t="s">
         <v>16</v>
       </c>
@@ -20050,7 +20124,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="36.75" thickBot="1">
+    <row r="25" spans="1:6" ht="15.75" thickBot="1">
       <c r="A25" s="40" t="s">
         <v>47</v>
       </c>
@@ -20067,7 +20141,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="36.75" thickBot="1">
+    <row r="26" spans="1:6" ht="15.75" thickBot="1">
       <c r="A26" s="40" t="s">
         <v>18</v>
       </c>
@@ -20084,7 +20158,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="36.75" thickBot="1">
+    <row r="27" spans="1:6" ht="15.75" thickBot="1">
       <c r="A27" s="40" t="s">
         <v>19</v>
       </c>
@@ -20101,7 +20175,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24.75" thickBot="1">
+    <row r="28" spans="1:6" ht="15.75" thickBot="1">
       <c r="A28" s="40" t="s">
         <v>20</v>
       </c>
@@ -20118,7 +20192,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.75" thickBot="1">
+    <row r="29" spans="1:6" ht="15.75" thickBot="1">
       <c r="A29" s="40" t="s">
         <v>22</v>
       </c>
@@ -20153,7 +20227,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="32" spans="1:6" ht="24">
+    <row r="32" spans="1:6">
       <c r="A32" s="182" t="s">
         <v>629</v>
       </c>
@@ -20173,7 +20247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="27.75" thickBot="1">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="183" t="s">
         <v>630</v>
       </c>
@@ -20194,7 +20268,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="418" t="s">
+      <c r="A34" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="7">
@@ -20214,7 +20288,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="419"/>
+      <c r="A35" s="421"/>
       <c r="B35" s="7">
         <v>2007</v>
       </c>
@@ -20232,7 +20306,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="419"/>
+      <c r="A36" s="421"/>
       <c r="B36" s="7">
         <v>2014</v>
       </c>
@@ -20250,7 +20324,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="420"/>
+      <c r="A37" s="422"/>
       <c r="B37" s="69">
         <v>2021</v>
       </c>
@@ -20268,7 +20342,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="421" t="s">
+      <c r="A38" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="20">
@@ -20288,7 +20362,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="422"/>
+      <c r="A39" s="424"/>
       <c r="B39" s="20">
         <v>2007</v>
       </c>
@@ -20306,7 +20380,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="422"/>
+      <c r="A40" s="424"/>
       <c r="B40" s="20">
         <v>2014</v>
       </c>
@@ -20324,7 +20398,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="437"/>
+      <c r="A41" s="439"/>
       <c r="B41" s="20">
         <v>2021</v>
       </c>
@@ -20342,7 +20416,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="540" t="s">
+      <c r="A42" s="542" t="s">
         <v>18</v>
       </c>
       <c r="B42" s="257">
@@ -20362,7 +20436,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="541"/>
+      <c r="A43" s="543"/>
       <c r="B43" s="257">
         <v>2007</v>
       </c>
@@ -20380,7 +20454,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="541"/>
+      <c r="A44" s="543"/>
       <c r="B44" s="257">
         <v>2014</v>
       </c>
@@ -20398,7 +20472,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="542"/>
+      <c r="A45" s="544"/>
       <c r="B45" s="260">
         <v>2021</v>
       </c>
@@ -20416,7 +20490,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="421" t="s">
+      <c r="A46" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B46" s="20">
@@ -20436,7 +20510,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="422"/>
+      <c r="A47" s="424"/>
       <c r="B47" s="20">
         <v>2007</v>
       </c>
@@ -20454,7 +20528,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="422"/>
+      <c r="A48" s="424"/>
       <c r="B48" s="20">
         <v>2014</v>
       </c>
@@ -20472,7 +20546,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="437"/>
+      <c r="A49" s="439"/>
       <c r="B49" s="20">
         <v>2021</v>
       </c>
@@ -20490,7 +20564,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="540" t="s">
+      <c r="A50" s="542" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="257">
@@ -20510,7 +20584,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="541"/>
+      <c r="A51" s="543"/>
       <c r="B51" s="257">
         <v>2007</v>
       </c>
@@ -20528,7 +20602,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="541"/>
+      <c r="A52" s="543"/>
       <c r="B52" s="257">
         <v>2014</v>
       </c>
@@ -20546,7 +20620,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="542"/>
+      <c r="A53" s="544"/>
       <c r="B53" s="260">
         <v>2021</v>
       </c>
@@ -20564,7 +20638,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="421" t="s">
+      <c r="A54" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="20">
@@ -20583,8 +20657,8 @@
         <v>636</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="24.75" thickBot="1">
-      <c r="A55" s="422"/>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A55" s="424"/>
       <c r="B55" s="20">
         <v>2007</v>
       </c>
@@ -20601,8 +20675,8 @@
         <v>636</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A56" s="422"/>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A56" s="424"/>
       <c r="B56" s="20">
         <v>2014</v>
       </c>
@@ -20620,12 +20694,12 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="423"/>
+      <c r="A57" s="425"/>
       <c r="B57" s="24">
         <v>2021</v>
       </c>
-      <c r="C57" s="264">
-        <v>3150</v>
+      <c r="C57" s="264" t="s">
+        <v>1343</v>
       </c>
       <c r="D57" s="25">
         <v>15750000</v>
@@ -20656,7 +20730,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="36.75" thickBot="1">
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
       <c r="A60" s="40" t="s">
         <v>281</v>
       </c>
@@ -20696,7 +20770,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="36.75" thickBot="1">
+    <row r="62" spans="1:6" ht="15.75" thickBot="1">
       <c r="A62" s="42" t="s">
         <v>11</v>
       </c>
@@ -20717,7 +20791,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="64" spans="1:6" ht="24.75" thickBot="1">
+    <row r="64" spans="1:6" ht="15.75" thickBot="1">
       <c r="A64" s="265" t="s">
         <v>640</v>
       </c>
@@ -20729,7 +20803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="24.75" thickBot="1">
+    <row r="65" spans="1:6" ht="15.75" thickBot="1">
       <c r="A65" s="267" t="s">
         <v>641</v>
       </c>
@@ -20743,7 +20817,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="48.75" thickBot="1">
+    <row r="66" spans="1:6" ht="24.75" thickBot="1">
       <c r="A66" s="267" t="s">
         <v>642</v>
       </c>
@@ -20757,7 +20831,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="36.75" thickBot="1">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1">
       <c r="A67" s="267" t="s">
         <v>643</v>
       </c>
@@ -20771,7 +20845,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="24.75" thickBot="1">
+    <row r="68" spans="1:6" ht="15.75" thickBot="1">
       <c r="A68" s="268" t="s">
         <v>644</v>
       </c>
@@ -20783,7 +20857,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="24.75" thickBot="1">
+    <row r="69" spans="1:6" ht="15.75" thickBot="1">
       <c r="A69" s="267" t="s">
         <v>641</v>
       </c>
@@ -20797,7 +20871,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="48.75" thickBot="1">
+    <row r="70" spans="1:6" ht="24.75" thickBot="1">
       <c r="A70" s="267" t="s">
         <v>642</v>
       </c>
@@ -20811,7 +20885,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="36.75" thickBot="1">
+    <row r="71" spans="1:6" ht="15.75" thickBot="1">
       <c r="A71" s="267" t="s">
         <v>643</v>
       </c>
@@ -20825,7 +20899,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="60.75" thickBot="1">
+    <row r="72" spans="1:6" ht="24.75" thickBot="1">
       <c r="A72" s="268" t="s">
         <v>645</v>
       </c>
@@ -20840,7 +20914,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="74" spans="1:6" ht="30.75" thickBot="1">
+    <row r="74" spans="1:6" ht="21.75" thickBot="1">
       <c r="A74" s="271" t="s">
         <v>12</v>
       </c>
@@ -20860,7 +20934,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="36.75" thickBot="1">
+    <row r="75" spans="1:6" ht="15.75" thickBot="1">
       <c r="A75" s="275" t="s">
         <v>16</v>
       </c>
@@ -20880,7 +20954,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="36.75" thickBot="1">
+    <row r="76" spans="1:6" ht="15.75" thickBot="1">
       <c r="A76" s="275" t="s">
         <v>47</v>
       </c>
@@ -20900,7 +20974,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="36.75" thickBot="1">
+    <row r="77" spans="1:6" ht="15.75" thickBot="1">
       <c r="A77" s="275" t="s">
         <v>18</v>
       </c>
@@ -20914,7 +20988,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="96.75" thickBot="1">
+    <row r="78" spans="1:6" ht="15.75" thickBot="1">
       <c r="A78" s="280" t="s">
         <v>93</v>
       </c>
@@ -20934,7 +21008,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="24.75" thickBot="1">
+    <row r="79" spans="1:6" ht="15.75" thickBot="1">
       <c r="A79" s="282" t="s">
         <v>613</v>
       </c>
@@ -20954,7 +21028,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="24.75" thickBot="1">
+    <row r="80" spans="1:6" ht="15.75" thickBot="1">
       <c r="A80" s="275" t="s">
         <v>20</v>
       </c>
@@ -20974,7 +21048,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="24.75" thickBot="1">
+    <row r="81" spans="1:6" ht="15.75" thickBot="1">
       <c r="A81" s="275" t="s">
         <v>48</v>
       </c>
@@ -21013,7 +21087,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="84" spans="1:6" ht="33.75" thickBot="1">
+    <row r="84" spans="1:6" ht="24.75" thickBot="1">
       <c r="A84" s="71" t="s">
         <v>651</v>
       </c>
@@ -21030,7 +21104,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="60.75" thickBot="1">
+    <row r="85" spans="1:6" ht="24.75" thickBot="1">
       <c r="A85" s="6" t="s">
         <v>654</v>
       </c>
@@ -21047,7 +21121,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="48.75" thickBot="1">
+    <row r="86" spans="1:6" ht="24.75" thickBot="1">
       <c r="A86" s="6" t="s">
         <v>657</v>
       </c>
@@ -21064,7 +21138,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="48.75" thickBot="1">
+    <row r="87" spans="1:6" ht="24.75" thickBot="1">
       <c r="A87" s="6" t="s">
         <v>660</v>
       </c>
@@ -21082,7 +21156,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="90" spans="1:6" ht="36.75" thickBot="1">
+    <row r="90" spans="1:6" ht="15.75" thickBot="1">
       <c r="A90" s="2"/>
       <c r="B90" s="55" t="s">
         <v>495</v>
@@ -21241,7 +21315,7 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="99" spans="1:6" ht="60.75" thickBot="1">
+    <row r="99" spans="1:6" ht="15.75" thickBot="1">
       <c r="A99" s="2"/>
       <c r="B99" s="55" t="s">
         <v>667</v>
@@ -21360,7 +21434,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="106" spans="1:6" ht="24.75" thickBot="1">
+    <row r="106" spans="1:6" ht="15.75" thickBot="1">
       <c r="A106" s="82"/>
       <c r="B106" s="3" t="s">
         <v>671</v>
@@ -21519,7 +21593,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="115" spans="1:6" ht="24.75" thickBot="1">
+    <row r="115" spans="1:6" ht="15.75" thickBot="1">
       <c r="A115" s="71" t="s">
         <v>676</v>
       </c>
@@ -21533,7 +21607,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="48.75" thickBot="1">
+    <row r="116" spans="1:6" ht="24.75" thickBot="1">
       <c r="A116" s="40" t="s">
         <v>677</v>
       </c>
@@ -21547,7 +21621,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="48.75" thickBot="1">
+    <row r="117" spans="1:6" ht="24.75" thickBot="1">
       <c r="A117" s="40" t="s">
         <v>678</v>
       </c>
@@ -21561,7 +21635,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="24.75" thickBot="1">
+    <row r="118" spans="1:6" ht="15.75" thickBot="1">
       <c r="A118" s="40" t="s">
         <v>679</v>
       </c>
@@ -21575,7 +21649,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="48.75" thickBot="1">
+    <row r="119" spans="1:6" ht="24.75" thickBot="1">
       <c r="A119" s="40" t="s">
         <v>680</v>
       </c>
@@ -21604,7 +21678,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="122" spans="1:6" ht="24.75" thickBot="1">
+    <row r="122" spans="1:6" ht="15.75" thickBot="1">
       <c r="A122" s="71" t="s">
         <v>683</v>
       </c>
@@ -21618,7 +21692,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="36.75" thickBot="1">
+    <row r="123" spans="1:6" ht="15.75" thickBot="1">
       <c r="A123" s="40" t="s">
         <v>684</v>
       </c>
@@ -21632,7 +21706,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="48.75" thickBot="1">
+    <row r="124" spans="1:6" ht="24.75" thickBot="1">
       <c r="A124" s="40" t="s">
         <v>685</v>
       </c>
@@ -21646,7 +21720,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="24.75" thickBot="1">
+    <row r="125" spans="1:6" ht="15.75" thickBot="1">
       <c r="A125" s="40" t="s">
         <v>686</v>
       </c>
@@ -21660,7 +21734,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="48.75" thickBot="1">
+    <row r="126" spans="1:6" ht="24.75" thickBot="1">
       <c r="A126" s="40" t="s">
         <v>687</v>
       </c>
@@ -21674,7 +21748,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="36.75" thickBot="1">
+    <row r="127" spans="1:6" ht="15.75" thickBot="1">
       <c r="A127" s="40" t="s">
         <v>688</v>
       </c>
@@ -21688,7 +21762,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="48.75" thickBot="1">
+    <row r="128" spans="1:6" ht="24.75" thickBot="1">
       <c r="A128" s="40" t="s">
         <v>689</v>
       </c>
@@ -21717,7 +21791,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="131" spans="1:6" ht="36.75" thickBot="1">
+    <row r="131" spans="1:6" ht="15.75" thickBot="1">
       <c r="A131" s="52" t="s">
         <v>692</v>
       </c>
@@ -21737,7 +21811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="24.75" thickBot="1">
+    <row r="132" spans="1:6" ht="15.75" thickBot="1">
       <c r="A132" s="6" t="s">
         <v>695</v>
       </c>
@@ -21757,7 +21831,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="24.75" thickBot="1">
+    <row r="133" spans="1:6" ht="15.75" thickBot="1">
       <c r="A133" s="6" t="s">
         <v>141</v>
       </c>
@@ -21777,7 +21851,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.75" thickBot="1">
+    <row r="134" spans="1:6" ht="15.75" thickBot="1">
       <c r="A134" s="6" t="s">
         <v>702</v>
       </c>
@@ -21797,7 +21871,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="24.75" thickBot="1">
+    <row r="135" spans="1:6" ht="15.75" thickBot="1">
       <c r="A135" s="6" t="s">
         <v>706</v>
       </c>
@@ -21817,7 +21891,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="36.75" thickBot="1">
+    <row r="136" spans="1:6" ht="15.75" thickBot="1">
       <c r="A136" s="6" t="s">
         <v>710</v>
       </c>
@@ -21837,7 +21911,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="36.75" thickBot="1">
+    <row r="137" spans="1:6" ht="15.75" thickBot="1">
       <c r="A137" s="6" t="s">
         <v>714</v>
       </c>
@@ -21880,10 +21954,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="349"/>
-      <c r="C1" s="543" t="s">
+      <c r="C1" s="545" t="s">
         <v>1121</v>
       </c>
-      <c r="D1" s="543"/>
+      <c r="D1" s="545"/>
       <c r="E1" s="350"/>
       <c r="F1" s="11" t="s">
         <v>8</v>
@@ -22172,10 +22246,10 @@
       <c r="C20" s="103"/>
       <c r="D20" s="352"/>
       <c r="E20" s="352"/>
-      <c r="F20" s="544" t="s">
+      <c r="F20" s="546" t="s">
         <v>1135</v>
       </c>
-      <c r="G20" s="544"/>
+      <c r="G20" s="546"/>
       <c r="H20" s="352"/>
       <c r="I20" s="353"/>
       <c r="J20" s="11" t="s">
@@ -22219,7 +22293,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A22" s="418">
+      <c r="A22" s="420">
         <v>2016</v>
       </c>
       <c r="B22" s="101" t="s">
@@ -22254,7 +22328,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A23" s="442"/>
+      <c r="A23" s="444"/>
       <c r="B23" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22287,7 +22361,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A24" s="418">
+      <c r="A24" s="420">
         <v>2017</v>
       </c>
       <c r="B24" s="101" t="s">
@@ -22322,7 +22396,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A25" s="442"/>
+      <c r="A25" s="444"/>
       <c r="B25" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22355,7 +22429,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A26" s="418">
+      <c r="A26" s="420">
         <v>2018</v>
       </c>
       <c r="B26" s="101" t="s">
@@ -22390,7 +22464,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A27" s="442"/>
+      <c r="A27" s="444"/>
       <c r="B27" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22423,7 +22497,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A28" s="418">
+      <c r="A28" s="420">
         <v>2019</v>
       </c>
       <c r="B28" s="101" t="s">
@@ -22458,7 +22532,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A29" s="442"/>
+      <c r="A29" s="444"/>
       <c r="B29" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22491,7 +22565,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A30" s="418">
+      <c r="A30" s="420">
         <v>2020</v>
       </c>
       <c r="B30" s="101" t="s">
@@ -22526,7 +22600,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A31" s="442"/>
+      <c r="A31" s="444"/>
       <c r="B31" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22559,7 +22633,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A32" s="418">
+      <c r="A32" s="420">
         <v>2021</v>
       </c>
       <c r="B32" s="101" t="s">
@@ -22594,7 +22668,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A33" s="420"/>
+      <c r="A33" s="422"/>
       <c r="B33" s="107" t="s">
         <v>1125</v>
       </c>
@@ -22785,7 +22859,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A47" s="418" t="s">
+      <c r="A47" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B47" s="7">
@@ -22805,7 +22879,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A48" s="419"/>
+      <c r="A48" s="421"/>
       <c r="B48" s="7">
         <v>2007</v>
       </c>
@@ -22823,7 +22897,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="419"/>
+      <c r="A49" s="421"/>
       <c r="B49" s="7">
         <v>2014</v>
       </c>
@@ -22841,7 +22915,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="420"/>
+      <c r="A50" s="422"/>
       <c r="B50" s="69">
         <v>2021</v>
       </c>
@@ -22859,7 +22933,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="421" t="s">
+      <c r="A51" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B51" s="20">
@@ -22879,7 +22953,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="422"/>
+      <c r="A52" s="424"/>
       <c r="B52" s="20">
         <v>2007</v>
       </c>
@@ -22897,7 +22971,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="422"/>
+      <c r="A53" s="424"/>
       <c r="B53" s="20">
         <v>2014</v>
       </c>
@@ -22915,7 +22989,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="437"/>
+      <c r="A54" s="439"/>
       <c r="B54" s="20">
         <v>2021</v>
       </c>
@@ -22933,7 +23007,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="418" t="s">
+      <c r="A55" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B55" s="7">
@@ -22953,7 +23027,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="419"/>
+      <c r="A56" s="421"/>
       <c r="B56" s="7">
         <v>2007</v>
       </c>
@@ -22971,7 +23045,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="419"/>
+      <c r="A57" s="421"/>
       <c r="B57" s="7">
         <v>2014</v>
       </c>
@@ -22989,7 +23063,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="420"/>
+      <c r="A58" s="422"/>
       <c r="B58" s="69">
         <v>2021</v>
       </c>
@@ -23007,7 +23081,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="421" t="s">
+      <c r="A59" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B59" s="20">
@@ -23027,7 +23101,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="422"/>
+      <c r="A60" s="424"/>
       <c r="B60" s="20">
         <v>2007</v>
       </c>
@@ -23045,7 +23119,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="422"/>
+      <c r="A61" s="424"/>
       <c r="B61" s="20">
         <v>2014</v>
       </c>
@@ -23063,7 +23137,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="437"/>
+      <c r="A62" s="439"/>
       <c r="B62" s="20">
         <v>2021</v>
       </c>
@@ -23081,7 +23155,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="418" t="s">
+      <c r="A63" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="7">
@@ -23101,7 +23175,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="419"/>
+      <c r="A64" s="421"/>
       <c r="B64" s="7">
         <v>2007</v>
       </c>
@@ -23119,7 +23193,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A65" s="419"/>
+      <c r="A65" s="421"/>
       <c r="B65" s="7">
         <v>2014</v>
       </c>
@@ -23137,7 +23211,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A66" s="420"/>
+      <c r="A66" s="422"/>
       <c r="B66" s="69">
         <v>2021</v>
       </c>
@@ -23155,7 +23229,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A67" s="421" t="s">
+      <c r="A67" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="20">
@@ -23175,7 +23249,7 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A68" s="422"/>
+      <c r="A68" s="424"/>
       <c r="B68" s="20">
         <v>2007</v>
       </c>
@@ -23193,7 +23267,7 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A69" s="422"/>
+      <c r="A69" s="424"/>
       <c r="B69" s="20">
         <v>2014</v>
       </c>
@@ -23211,7 +23285,7 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A70" s="423"/>
+      <c r="A70" s="425"/>
       <c r="B70" s="24">
         <v>2021</v>
       </c>
@@ -23367,16 +23441,16 @@
     </row>
     <row r="80" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="81" spans="1:6" ht="48">
-      <c r="A81" s="453" t="s">
+      <c r="A81" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B81" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="426" t="s">
+      <c r="C81" s="428" t="s">
         <v>44</v>
       </c>
-      <c r="D81" s="428" t="s">
+      <c r="D81" s="430" t="s">
         <v>1155</v>
       </c>
       <c r="E81" s="11" t="s">
@@ -23387,12 +23461,12 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="18.75" thickBot="1">
-      <c r="A82" s="454"/>
+      <c r="A82" s="456"/>
       <c r="B82" s="135" t="s">
         <v>1154</v>
       </c>
-      <c r="C82" s="427"/>
-      <c r="D82" s="429"/>
+      <c r="C82" s="429"/>
+      <c r="D82" s="431"/>
       <c r="E82" s="30" t="s">
         <v>1156</v>
       </c>
@@ -23729,6 +23803,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8ADE0F4-4960-4862-9100-6C103FA17195}">
   <dimension ref="A1:J105"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1" s="52" t="s">
@@ -23860,7 +23946,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="24.75" thickBot="1">
+    <row r="6" spans="1:8" ht="15.75" thickBot="1">
       <c r="A6" s="40" t="s">
         <v>720</v>
       </c>
@@ -23914,7 +24000,7 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:8">
-      <c r="A9" s="453" t="s">
+      <c r="A9" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="46" t="s">
@@ -23930,8 +24016,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="27.75" thickBot="1">
-      <c r="A10" s="454"/>
+    <row r="10" spans="1:8" ht="18.75" thickBot="1">
+      <c r="A10" s="456"/>
       <c r="B10" s="135" t="s">
         <v>197</v>
       </c>
@@ -23945,7 +24031,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="36.75" thickBot="1">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1">
       <c r="A11" s="40" t="s">
         <v>16</v>
       </c>
@@ -23962,7 +24048,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="36.75" thickBot="1">
+    <row r="12" spans="1:8" ht="15.75" thickBot="1">
       <c r="A12" s="40" t="s">
         <v>47</v>
       </c>
@@ -23979,7 +24065,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="36.75" thickBot="1">
+    <row r="13" spans="1:8" ht="15.75" thickBot="1">
       <c r="A13" s="40" t="s">
         <v>18</v>
       </c>
@@ -23996,7 +24082,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="36.75" thickBot="1">
+    <row r="14" spans="1:8" ht="15.75" thickBot="1">
       <c r="A14" s="40" t="s">
         <v>19</v>
       </c>
@@ -24013,7 +24099,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="24.75" thickBot="1">
+    <row r="15" spans="1:8" ht="15.75" thickBot="1">
       <c r="A15" s="40" t="s">
         <v>20</v>
       </c>
@@ -24030,7 +24116,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="24.75" thickBot="1">
+    <row r="16" spans="1:8" ht="15.75" thickBot="1">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
@@ -24047,7 +24133,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="36.75" thickBot="1">
+    <row r="17" spans="1:6" ht="24.75" thickBot="1">
       <c r="A17" s="42" t="s">
         <v>76</v>
       </c>
@@ -24065,11 +24151,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="19" spans="1:6" ht="24">
-      <c r="A19" s="453" t="s">
+    <row r="19" spans="1:6">
+      <c r="A19" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="426" t="s">
+      <c r="B19" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="46" t="s">
@@ -24085,9 +24171,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A20" s="454"/>
-      <c r="B20" s="427"/>
+    <row r="20" spans="1:6" ht="18.75" thickBot="1">
+      <c r="A20" s="456"/>
+      <c r="B20" s="429"/>
       <c r="C20" s="286" t="s">
         <v>197</v>
       </c>
@@ -24120,7 +24206,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="555" t="s">
+      <c r="A22" s="557" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="7">
@@ -24140,7 +24226,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="555"/>
+      <c r="A23" s="557"/>
       <c r="B23" s="7">
         <v>2014</v>
       </c>
@@ -24158,7 +24244,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="556"/>
+      <c r="A24" s="558"/>
       <c r="B24" s="69">
         <v>2021</v>
       </c>
@@ -24176,7 +24262,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="421" t="s">
+      <c r="A25" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="20">
@@ -24196,7 +24282,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="422"/>
+      <c r="A26" s="424"/>
       <c r="B26" s="20">
         <v>2007</v>
       </c>
@@ -24214,7 +24300,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="422"/>
+      <c r="A27" s="424"/>
       <c r="B27" s="20">
         <v>2014</v>
       </c>
@@ -24232,7 +24318,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="437"/>
+      <c r="A28" s="439"/>
       <c r="B28" s="20">
         <v>2021</v>
       </c>
@@ -24250,7 +24336,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="418" t="s">
+      <c r="A29" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B29" s="7">
@@ -24270,7 +24356,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="419"/>
+      <c r="A30" s="421"/>
       <c r="B30" s="7">
         <v>2007</v>
       </c>
@@ -24288,7 +24374,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="419"/>
+      <c r="A31" s="421"/>
       <c r="B31" s="7">
         <v>2014</v>
       </c>
@@ -24306,7 +24392,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="420"/>
+      <c r="A32" s="422"/>
       <c r="B32" s="69">
         <v>2021</v>
       </c>
@@ -24324,7 +24410,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A33" s="480" t="s">
+      <c r="A33" s="482" t="s">
         <v>19</v>
       </c>
       <c r="B33" s="20">
@@ -24344,7 +24430,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="481"/>
+      <c r="A34" s="483"/>
       <c r="B34" s="20">
         <v>2007</v>
       </c>
@@ -24362,7 +24448,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A35" s="481"/>
+      <c r="A35" s="483"/>
       <c r="B35" s="20">
         <v>2014</v>
       </c>
@@ -24380,7 +24466,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A36" s="482"/>
+      <c r="A36" s="484"/>
       <c r="B36" s="20">
         <v>2021</v>
       </c>
@@ -24397,8 +24483,8 @@
         <v>723</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="36.75" thickBot="1">
-      <c r="A37" s="418" t="s">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A37" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B37" s="7">
@@ -24418,7 +24504,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A38" s="419"/>
+      <c r="A38" s="421"/>
       <c r="B38" s="7">
         <v>2007</v>
       </c>
@@ -24436,7 +24522,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A39" s="419"/>
+      <c r="A39" s="421"/>
       <c r="B39" s="7">
         <v>2014</v>
       </c>
@@ -24454,7 +24540,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A40" s="420"/>
+      <c r="A40" s="422"/>
       <c r="B40" s="69">
         <v>2021</v>
       </c>
@@ -24471,8 +24557,8 @@
         <v>723</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="36.75" thickBot="1">
-      <c r="A41" s="421" t="s">
+    <row r="41" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A41" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="20">
@@ -24492,12 +24578,12 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A42" s="422"/>
+      <c r="A42" s="424"/>
       <c r="B42" s="20">
         <v>2007</v>
       </c>
-      <c r="C42" s="109">
-        <v>12334</v>
+      <c r="C42" s="109" t="s">
+        <v>1344</v>
       </c>
       <c r="D42" s="297">
         <v>37000</v>
@@ -24509,8 +24595,8 @@
         <v>723</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="24.75" thickBot="1">
-      <c r="A43" s="422"/>
+    <row r="43" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A43" s="424"/>
       <c r="B43" s="20">
         <v>2014</v>
       </c>
@@ -24527,8 +24613,8 @@
         <v>723</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="24.75" thickBot="1">
-      <c r="A44" s="423"/>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A44" s="425"/>
       <c r="B44" s="24">
         <v>2021</v>
       </c>
@@ -24590,7 +24676,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24.75" thickBot="1">
+    <row r="48" spans="1:7" ht="15.75" thickBot="1">
       <c r="A48" s="40" t="s">
         <v>735</v>
       </c>
@@ -24613,7 +24699,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="48.75" thickBot="1">
+    <row r="49" spans="1:7" ht="15.75" thickBot="1">
       <c r="A49" s="42" t="s">
         <v>736</v>
       </c>
@@ -24658,7 +24744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="48.75" thickBot="1">
+    <row r="52" spans="1:7" ht="24.75" thickBot="1">
       <c r="A52" s="6" t="s">
         <v>738</v>
       </c>
@@ -24673,7 +24759,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="84.75" thickBot="1">
+    <row r="53" spans="1:7" ht="24.75" thickBot="1">
       <c r="A53" s="188" t="s">
         <v>739</v>
       </c>
@@ -24696,7 +24782,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="84.75" thickBot="1">
+    <row r="54" spans="1:7" ht="36.75" thickBot="1">
       <c r="A54" s="188" t="s">
         <v>740</v>
       </c>
@@ -24719,7 +24805,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="48.75" thickBot="1">
+    <row r="55" spans="1:7" ht="24.75" thickBot="1">
       <c r="A55" s="6" t="s">
         <v>741</v>
       </c>
@@ -24742,7 +24828,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="60.75" thickBot="1">
+    <row r="56" spans="1:7" ht="24.75" thickBot="1">
       <c r="A56" s="6" t="s">
         <v>742</v>
       </c>
@@ -24757,7 +24843,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60.75" thickBot="1">
+    <row r="57" spans="1:7" ht="24.75" thickBot="1">
       <c r="A57" s="188" t="s">
         <v>743</v>
       </c>
@@ -24780,7 +24866,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="72.75" thickBot="1">
+    <row r="58" spans="1:7" ht="24.75" thickBot="1">
       <c r="A58" s="188" t="s">
         <v>744</v>
       </c>
@@ -24803,7 +24889,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="36.75" thickBot="1">
+    <row r="59" spans="1:7" ht="15.75" thickBot="1">
       <c r="A59" s="6" t="s">
         <v>745</v>
       </c>
@@ -24826,7 +24912,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24.75" thickBot="1">
+    <row r="60" spans="1:7" ht="15.75" thickBot="1">
       <c r="A60" s="6" t="s">
         <v>290</v>
       </c>
@@ -24841,7 +24927,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60.75" thickBot="1">
+    <row r="61" spans="1:7" ht="15.75" thickBot="1">
       <c r="A61" s="188" t="s">
         <v>746</v>
       </c>
@@ -24864,7 +24950,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="84.75" thickBot="1">
+    <row r="62" spans="1:7" ht="24.75" thickBot="1">
       <c r="A62" s="188" t="s">
         <v>747</v>
       </c>
@@ -24887,7 +24973,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="60.75" thickBot="1">
+    <row r="63" spans="1:7" ht="24.75" thickBot="1">
       <c r="A63" s="6" t="s">
         <v>748</v>
       </c>
@@ -24911,7 +24997,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" thickBot="1"/>
-    <row r="65" spans="1:6" ht="48.75" thickBot="1">
+    <row r="65" spans="1:6" ht="24.75" thickBot="1">
       <c r="A65" s="71" t="s">
         <v>12</v>
       </c>
@@ -24931,7 +25017,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="36.75" thickBot="1">
+    <row r="66" spans="1:6" ht="15.75" thickBot="1">
       <c r="A66" s="40" t="s">
         <v>16</v>
       </c>
@@ -24951,7 +25037,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="36.75" thickBot="1">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1">
       <c r="A67" s="40" t="s">
         <v>47</v>
       </c>
@@ -24971,7 +25057,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="36.75" thickBot="1">
+    <row r="68" spans="1:6" ht="15.75" thickBot="1">
       <c r="A68" s="40" t="s">
         <v>753</v>
       </c>
@@ -24991,7 +25077,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="24.75" thickBot="1">
+    <row r="69" spans="1:6" ht="15.75" thickBot="1">
       <c r="A69" s="40" t="s">
         <v>20</v>
       </c>
@@ -25011,7 +25097,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="24.75" thickBot="1">
+    <row r="70" spans="1:6" ht="15.75" thickBot="1">
       <c r="A70" s="40" t="s">
         <v>48</v>
       </c>
@@ -25086,7 +25172,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="60">
+    <row r="75" spans="1:6" ht="24">
       <c r="A75" s="305" t="s">
         <v>757</v>
       </c>
@@ -25103,7 +25189,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="48">
+    <row r="76" spans="1:6">
       <c r="A76" s="305" t="s">
         <v>758</v>
       </c>
@@ -25120,7 +25206,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="36">
+    <row r="77" spans="1:6">
       <c r="A77" s="305" t="s">
         <v>759</v>
       </c>
@@ -25137,7 +25223,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="72">
+    <row r="78" spans="1:6" ht="24">
       <c r="A78" s="184" t="s">
         <v>760</v>
       </c>
@@ -25154,7 +25240,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="36.75" thickBot="1">
+    <row r="79" spans="1:6" ht="15.75" thickBot="1">
       <c r="A79" s="40" t="s">
         <v>761</v>
       </c>
@@ -25171,7 +25257,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="48.75" thickBot="1">
+    <row r="80" spans="1:6" ht="24.75" thickBot="1">
       <c r="A80" s="40" t="s">
         <v>762</v>
       </c>
@@ -25188,7 +25274,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="36.75" thickBot="1">
+    <row r="81" spans="1:10" ht="15.75" thickBot="1">
       <c r="A81" s="40" t="s">
         <v>763</v>
       </c>
@@ -25205,7 +25291,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="60.75" thickBot="1">
+    <row r="82" spans="1:10" ht="24.75" thickBot="1">
       <c r="A82" s="42" t="s">
         <v>764</v>
       </c>
@@ -25224,24 +25310,24 @@
     </row>
     <row r="84" spans="1:10" ht="15.75" thickBot="1"/>
     <row r="85" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A85" s="453" t="s">
+      <c r="A85" s="455" t="s">
         <v>767</v>
       </c>
       <c r="B85" s="227" t="s">
         <v>76</v>
       </c>
-      <c r="C85" s="461" t="s">
+      <c r="C85" s="463" t="s">
         <v>768</v>
       </c>
-      <c r="D85" s="463"/>
-      <c r="E85" s="461" t="s">
+      <c r="D85" s="465"/>
+      <c r="E85" s="463" t="s">
         <v>769</v>
       </c>
-      <c r="F85" s="464"/>
-      <c r="G85" s="464" t="s">
+      <c r="F85" s="466"/>
+      <c r="G85" s="466" t="s">
         <v>770</v>
       </c>
-      <c r="H85" s="462"/>
+      <c r="H85" s="464"/>
       <c r="I85" s="11" t="s">
         <v>8</v>
       </c>
@@ -25250,26 +25336,26 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="27" customHeight="1">
-      <c r="A86" s="535"/>
-      <c r="B86" s="545" t="s">
+      <c r="A86" s="537"/>
+      <c r="B86" s="547" t="s">
         <v>771</v>
       </c>
-      <c r="C86" s="547" t="s">
+      <c r="C86" s="549" t="s">
         <v>772</v>
       </c>
       <c r="D86" s="309" t="s">
         <v>773</v>
       </c>
-      <c r="E86" s="547" t="s">
+      <c r="E86" s="549" t="s">
         <v>772</v>
       </c>
-      <c r="F86" s="549" t="s">
+      <c r="F86" s="551" t="s">
         <v>775</v>
       </c>
-      <c r="G86" s="551" t="s">
+      <c r="G86" s="553" t="s">
         <v>772</v>
       </c>
-      <c r="H86" s="553" t="s">
+      <c r="H86" s="555" t="s">
         <v>775</v>
       </c>
       <c r="I86" s="30" t="s">
@@ -25280,16 +25366,16 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A87" s="454"/>
-      <c r="B87" s="546"/>
-      <c r="C87" s="548"/>
+      <c r="A87" s="456"/>
+      <c r="B87" s="548"/>
+      <c r="C87" s="550"/>
       <c r="D87" s="310" t="s">
         <v>774</v>
       </c>
-      <c r="E87" s="548"/>
-      <c r="F87" s="550"/>
-      <c r="G87" s="552"/>
-      <c r="H87" s="554"/>
+      <c r="E87" s="550"/>
+      <c r="F87" s="552"/>
+      <c r="G87" s="554"/>
+      <c r="H87" s="556"/>
       <c r="I87" s="30" t="s">
         <v>782</v>
       </c>
@@ -25329,7 +25415,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="36.75" thickBot="1">
+    <row r="89" spans="1:10" ht="15.75" thickBot="1">
       <c r="A89" s="40" t="s">
         <v>777</v>
       </c>
@@ -25490,7 +25576,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="15.75" thickBot="1"/>
-    <row r="95" spans="1:10" ht="48.75" thickBot="1">
+    <row r="95" spans="1:10" ht="24.75" thickBot="1">
       <c r="A95" s="52" t="s">
         <v>36</v>
       </c>
@@ -25740,6 +25826,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8DA15B-44CD-4542-B40F-5C83D8DBD48E}">
   <dimension ref="A1:I73"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1" s="71" t="s">
@@ -25767,7 +25864,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24.75" thickBot="1">
+    <row r="2" spans="1:8" ht="15.75" thickBot="1">
       <c r="A2" s="40" t="s">
         <v>579</v>
       </c>
@@ -25793,7 +25890,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24.75" thickBot="1">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1">
       <c r="A3" s="40" t="s">
         <v>466</v>
       </c>
@@ -25819,7 +25916,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="24.75" thickBot="1">
+    <row r="4" spans="1:8" ht="15.75" thickBot="1">
       <c r="A4" s="40" t="s">
         <v>467</v>
       </c>
@@ -25845,7 +25942,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="24.75" thickBot="1">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1">
       <c r="A5" s="40" t="s">
         <v>580</v>
       </c>
@@ -25950,7 +26047,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1"/>
-    <row r="10" spans="1:8" ht="24.75" thickBot="1">
+    <row r="10" spans="1:8" ht="15.75" thickBot="1">
       <c r="A10" s="71" t="s">
         <v>12</v>
       </c>
@@ -25967,7 +26064,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="36.75" thickBot="1">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1">
       <c r="A11" s="40" t="s">
         <v>16</v>
       </c>
@@ -25984,7 +26081,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="36.75" thickBot="1">
+    <row r="12" spans="1:8" ht="15.75" thickBot="1">
       <c r="A12" s="40" t="s">
         <v>47</v>
       </c>
@@ -26001,7 +26098,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="36.75" thickBot="1">
+    <row r="13" spans="1:8" ht="15.75" thickBot="1">
       <c r="A13" s="40" t="s">
         <v>18</v>
       </c>
@@ -26018,7 +26115,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="36.75" thickBot="1">
+    <row r="14" spans="1:8" ht="15.75" thickBot="1">
       <c r="A14" s="40" t="s">
         <v>19</v>
       </c>
@@ -26035,7 +26132,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="24.75" thickBot="1">
+    <row r="15" spans="1:8" ht="15.75" thickBot="1">
       <c r="A15" s="40" t="s">
         <v>20</v>
       </c>
@@ -26052,7 +26149,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="24.75" thickBot="1">
+    <row r="16" spans="1:8" ht="15.75" thickBot="1">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
@@ -26069,7 +26166,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="36.75" thickBot="1">
+    <row r="17" spans="1:6" ht="15.75" thickBot="1">
       <c r="A17" s="42" t="s">
         <v>76</v>
       </c>
@@ -26087,11 +26184,11 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="19" spans="1:6" ht="24">
-      <c r="A19" s="453" t="s">
+    <row r="19" spans="1:6">
+      <c r="A19" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="426" t="s">
+      <c r="B19" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="46" t="s">
@@ -26107,9 +26204,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A20" s="454"/>
-      <c r="B20" s="427"/>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A20" s="456"/>
+      <c r="B20" s="429"/>
       <c r="C20" s="135" t="s">
         <v>591</v>
       </c>
@@ -26124,7 +26221,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="514" t="s">
+      <c r="A21" s="516" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="7">
@@ -26144,7 +26241,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="515"/>
+      <c r="A22" s="517"/>
       <c r="B22" s="7">
         <v>2007</v>
       </c>
@@ -26162,7 +26259,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="515"/>
+      <c r="A23" s="517"/>
       <c r="B23" s="7">
         <v>2014</v>
       </c>
@@ -26180,7 +26277,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="516"/>
+      <c r="A24" s="518"/>
       <c r="B24" s="69">
         <v>2021</v>
       </c>
@@ -26198,7 +26295,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="557" t="s">
+      <c r="A25" s="559" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="20">
@@ -26218,7 +26315,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="558"/>
+      <c r="A26" s="560"/>
       <c r="B26" s="20">
         <v>2007</v>
       </c>
@@ -26236,7 +26333,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="558"/>
+      <c r="A27" s="560"/>
       <c r="B27" s="20">
         <v>2014</v>
       </c>
@@ -26254,7 +26351,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="559"/>
+      <c r="A28" s="561"/>
       <c r="B28" s="20">
         <v>2021</v>
       </c>
@@ -26272,7 +26369,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="418" t="s">
+      <c r="A29" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B29" s="7">
@@ -26292,7 +26389,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="419"/>
+      <c r="A30" s="421"/>
       <c r="B30" s="7">
         <v>2007</v>
       </c>
@@ -26310,7 +26407,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="419"/>
+      <c r="A31" s="421"/>
       <c r="B31" s="7">
         <v>2014</v>
       </c>
@@ -26328,7 +26425,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="420"/>
+      <c r="A32" s="422"/>
       <c r="B32" s="69">
         <v>2021</v>
       </c>
@@ -26346,7 +26443,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="421" t="s">
+      <c r="A33" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B33" s="20">
@@ -26366,7 +26463,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A34" s="422"/>
+      <c r="A34" s="424"/>
       <c r="B34" s="20">
         <v>2007</v>
       </c>
@@ -26384,7 +26481,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A35" s="422"/>
+      <c r="A35" s="424"/>
       <c r="B35" s="20">
         <v>2014</v>
       </c>
@@ -26402,7 +26499,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A36" s="437"/>
+      <c r="A36" s="439"/>
       <c r="B36" s="20">
         <v>2021</v>
       </c>
@@ -26420,7 +26517,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A37" s="418" t="s">
+      <c r="A37" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B37" s="7">
@@ -26440,7 +26537,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A38" s="419"/>
+      <c r="A38" s="421"/>
       <c r="B38" s="7">
         <v>2007</v>
       </c>
@@ -26458,7 +26555,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A39" s="419"/>
+      <c r="A39" s="421"/>
       <c r="B39" s="7">
         <v>2014</v>
       </c>
@@ -26476,7 +26573,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A40" s="420"/>
+      <c r="A40" s="422"/>
       <c r="B40" s="69">
         <v>2021</v>
       </c>
@@ -26494,7 +26591,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A41" s="421" t="s">
+      <c r="A41" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="20">
@@ -26514,12 +26611,12 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A42" s="422"/>
+      <c r="A42" s="424"/>
       <c r="B42" s="20">
         <v>2007</v>
       </c>
-      <c r="C42" s="20">
-        <v>12</v>
+      <c r="C42" s="20" t="s">
+        <v>1341</v>
       </c>
       <c r="D42" s="21">
         <v>66000</v>
@@ -26532,12 +26629,12 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A43" s="422"/>
+      <c r="A43" s="424"/>
       <c r="B43" s="20">
         <v>2014</v>
       </c>
-      <c r="C43" s="20">
-        <v>10</v>
+      <c r="C43" s="20" t="s">
+        <v>1342</v>
       </c>
       <c r="D43" s="21">
         <v>87000</v>
@@ -26549,8 +26646,8 @@
         <v>594</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="24.75" thickBot="1">
-      <c r="A44" s="423"/>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A44" s="425"/>
       <c r="B44" s="24">
         <v>2021</v>
       </c>
@@ -26620,7 +26717,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="24.75" thickBot="1">
+    <row r="49" spans="1:8" ht="15.75" thickBot="1">
       <c r="A49" s="40" t="s">
         <v>600</v>
       </c>
@@ -26646,7 +26743,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="36.75" thickBot="1">
+    <row r="50" spans="1:8" ht="15.75" thickBot="1">
       <c r="A50" s="42" t="s">
         <v>11</v>
       </c>
@@ -26673,17 +26770,17 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.75" thickBot="1"/>
-    <row r="52" spans="1:8" ht="48">
-      <c r="A52" s="453" t="s">
+    <row r="52" spans="1:8" ht="24">
+      <c r="A52" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B52" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="C52" s="426" t="s">
+      <c r="C52" s="428" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="428" t="s">
+      <c r="D52" s="430" t="s">
         <v>603</v>
       </c>
       <c r="E52" s="11" t="s">
@@ -26693,13 +26790,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18.75" thickBot="1">
-      <c r="A53" s="454"/>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A53" s="456"/>
       <c r="B53" s="135" t="s">
         <v>602</v>
       </c>
-      <c r="C53" s="427"/>
-      <c r="D53" s="429"/>
+      <c r="C53" s="429"/>
+      <c r="D53" s="431"/>
       <c r="E53" s="30" t="s">
         <v>51</v>
       </c>
@@ -26707,7 +26804,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="36.75" thickBot="1">
+    <row r="54" spans="1:8" ht="15.75" thickBot="1">
       <c r="A54" s="6" t="s">
         <v>16</v>
       </c>
@@ -26727,7 +26824,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="36.75" thickBot="1">
+    <row r="55" spans="1:8" ht="15.75" thickBot="1">
       <c r="A55" s="6" t="s">
         <v>47</v>
       </c>
@@ -26747,7 +26844,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="45.75" thickBot="1">
+    <row r="56" spans="1:8" ht="30.75" thickBot="1">
       <c r="A56" s="249" t="s">
         <v>604</v>
       </c>
@@ -26767,7 +26864,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="24.75" thickBot="1">
+    <row r="57" spans="1:8" ht="15.75" thickBot="1">
       <c r="A57" s="6" t="s">
         <v>20</v>
       </c>
@@ -26787,7 +26884,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="24.75" thickBot="1">
+    <row r="58" spans="1:8" ht="15.75" thickBot="1">
       <c r="A58" s="6" t="s">
         <v>48</v>
       </c>
@@ -26846,7 +26943,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="48.75" thickBot="1">
+    <row r="62" spans="1:8" ht="24.75" thickBot="1">
       <c r="A62" s="40" t="s">
         <v>607</v>
       </c>
@@ -26866,7 +26963,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="24.75" thickBot="1">
+    <row r="63" spans="1:8" ht="15.75" thickBot="1">
       <c r="A63" s="40" t="s">
         <v>608</v>
       </c>
@@ -26886,7 +26983,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="72.75" thickBot="1">
+    <row r="64" spans="1:8" ht="36.75" thickBot="1">
       <c r="A64" s="42" t="s">
         <v>609</v>
       </c>
@@ -27445,7 +27542,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A14" s="447" t="s">
+      <c r="A14" s="449" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="7">
@@ -27465,7 +27562,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A15" s="448"/>
+      <c r="A15" s="450"/>
       <c r="B15" s="7">
         <v>2007</v>
       </c>
@@ -27483,7 +27580,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A16" s="448"/>
+      <c r="A16" s="450"/>
       <c r="B16" s="7">
         <v>2014</v>
       </c>
@@ -27501,7 +27598,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="449"/>
+      <c r="A17" s="451"/>
       <c r="B17" s="7">
         <v>2021</v>
       </c>
@@ -27519,7 +27616,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="450" t="s">
+      <c r="A18" s="452" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="20">
@@ -27539,7 +27636,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="451"/>
+      <c r="A19" s="453"/>
       <c r="B19" s="20">
         <v>2007</v>
       </c>
@@ -27557,7 +27654,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="451"/>
+      <c r="A20" s="453"/>
       <c r="B20" s="20">
         <v>2014</v>
       </c>
@@ -27575,7 +27672,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="452"/>
+      <c r="A21" s="454"/>
       <c r="B21" s="20">
         <v>2021</v>
       </c>
@@ -27593,7 +27690,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="418" t="s">
+      <c r="A22" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="7">
@@ -27613,7 +27710,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="419"/>
+      <c r="A23" s="421"/>
       <c r="B23" s="7">
         <v>2007</v>
       </c>
@@ -27631,7 +27728,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="419"/>
+      <c r="A24" s="421"/>
       <c r="B24" s="7">
         <v>2014</v>
       </c>
@@ -27649,7 +27746,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="442"/>
+      <c r="A25" s="444"/>
       <c r="B25" s="7">
         <v>2021</v>
       </c>
@@ -27667,7 +27764,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="450" t="s">
+      <c r="A26" s="452" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="20">
@@ -27687,7 +27784,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="451"/>
+      <c r="A27" s="453"/>
       <c r="B27" s="20">
         <v>2007</v>
       </c>
@@ -27705,7 +27802,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A28" s="451"/>
+      <c r="A28" s="453"/>
       <c r="B28" s="20">
         <v>2014</v>
       </c>
@@ -27723,7 +27820,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="452"/>
+      <c r="A29" s="454"/>
       <c r="B29" s="20">
         <v>2021</v>
       </c>
@@ -27741,7 +27838,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="418" t="s">
+      <c r="A30" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="7">
@@ -27761,7 +27858,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="419"/>
+      <c r="A31" s="421"/>
       <c r="B31" s="7">
         <v>2007</v>
       </c>
@@ -27779,7 +27876,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A32" s="419"/>
+      <c r="A32" s="421"/>
       <c r="B32" s="7">
         <v>2014</v>
       </c>
@@ -27797,7 +27894,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="442"/>
+      <c r="A33" s="444"/>
       <c r="B33" s="7">
         <v>2021</v>
       </c>
@@ -27815,7 +27912,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A34" s="443" t="s">
+      <c r="A34" s="445" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="20">
@@ -27835,7 +27932,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A35" s="422"/>
+      <c r="A35" s="424"/>
       <c r="B35" s="20">
         <v>2007</v>
       </c>
@@ -27853,7 +27950,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A36" s="422"/>
+      <c r="A36" s="424"/>
       <c r="B36" s="20">
         <v>2014</v>
       </c>
@@ -27871,7 +27968,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A37" s="423"/>
+      <c r="A37" s="425"/>
       <c r="B37" s="24">
         <v>2021</v>
       </c>
@@ -28118,13 +28215,13 @@
       <c r="H50" s="31"/>
     </row>
     <row r="51" spans="1:10" ht="24">
-      <c r="A51" s="424" t="s">
+      <c r="A51" s="426" t="s">
         <v>12</v>
       </c>
       <c r="B51" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C51" s="445" t="s">
+      <c r="C51" s="447" t="s">
         <v>44</v>
       </c>
       <c r="D51" s="47" t="s">
@@ -28140,11 +28237,11 @@
       <c r="H51" s="31"/>
     </row>
     <row r="52" spans="1:10" ht="18.75" thickBot="1">
-      <c r="A52" s="444"/>
+      <c r="A52" s="446"/>
       <c r="B52" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="446"/>
+      <c r="C52" s="448"/>
       <c r="D52" s="48" t="s">
         <v>46</v>
       </c>
@@ -28833,19 +28930,19 @@
       <c r="A81" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="438">
+      <c r="B81" s="440">
         <v>0.248</v>
       </c>
-      <c r="C81" s="438">
+      <c r="C81" s="440">
         <v>0.08</v>
       </c>
-      <c r="D81" s="438">
+      <c r="D81" s="440">
         <v>0.152</v>
       </c>
-      <c r="E81" s="438">
+      <c r="E81" s="440">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F81" s="440">
+      <c r="F81" s="442">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="G81" s="30" t="s">
@@ -28859,11 +28956,11 @@
       <c r="A82" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="B82" s="439"/>
-      <c r="C82" s="439"/>
-      <c r="D82" s="439"/>
-      <c r="E82" s="439"/>
-      <c r="F82" s="441"/>
+      <c r="B82" s="441"/>
+      <c r="C82" s="441"/>
+      <c r="D82" s="441"/>
+      <c r="E82" s="441"/>
+      <c r="F82" s="443"/>
       <c r="G82" s="30" t="s">
         <v>69</v>
       </c>
@@ -29275,10 +29372,10 @@
     </row>
     <row r="16" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:6" ht="24">
-      <c r="A17" s="453" t="s">
+      <c r="A17" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="426" t="s">
+      <c r="B17" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="46" t="s">
@@ -29295,8 +29392,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="454"/>
-      <c r="B18" s="427"/>
+      <c r="A18" s="456"/>
+      <c r="B18" s="429"/>
       <c r="C18" s="135" t="s">
         <v>808</v>
       </c>
@@ -29311,7 +29408,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="492" t="s">
+      <c r="A19" s="494" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="7">
@@ -29331,7 +29428,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="493"/>
+      <c r="A20" s="495"/>
       <c r="B20" s="7">
         <v>2007</v>
       </c>
@@ -29349,7 +29446,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="493"/>
+      <c r="A21" s="495"/>
       <c r="B21" s="7">
         <v>2014</v>
       </c>
@@ -29367,7 +29464,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="494"/>
+      <c r="A22" s="496"/>
       <c r="B22" s="69">
         <v>2021</v>
       </c>
@@ -29385,7 +29482,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="489" t="s">
+      <c r="A23" s="491" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="20">
@@ -29405,7 +29502,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="490"/>
+      <c r="A24" s="492"/>
       <c r="B24" s="20">
         <v>2007</v>
       </c>
@@ -29423,7 +29520,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="490"/>
+      <c r="A25" s="492"/>
       <c r="B25" s="20">
         <v>2014</v>
       </c>
@@ -29441,7 +29538,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="491"/>
+      <c r="A26" s="493"/>
       <c r="B26" s="20">
         <v>2021</v>
       </c>
@@ -29459,7 +29556,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="492" t="s">
+      <c r="A27" s="494" t="s">
         <v>18</v>
       </c>
       <c r="B27" s="7">
@@ -29479,7 +29576,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="493"/>
+      <c r="A28" s="495"/>
       <c r="B28" s="7">
         <v>2007</v>
       </c>
@@ -29497,7 +29594,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="493"/>
+      <c r="A29" s="495"/>
       <c r="B29" s="7">
         <v>2014</v>
       </c>
@@ -29515,7 +29612,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="494"/>
+      <c r="A30" s="496"/>
       <c r="B30" s="69">
         <v>2021</v>
       </c>
@@ -29533,7 +29630,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="489" t="s">
+      <c r="A31" s="491" t="s">
         <v>19</v>
       </c>
       <c r="B31" s="20">
@@ -29553,7 +29650,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="490"/>
+      <c r="A32" s="492"/>
       <c r="B32" s="20">
         <v>2007</v>
       </c>
@@ -29571,7 +29668,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A33" s="490"/>
+      <c r="A33" s="492"/>
       <c r="B33" s="20">
         <v>2014</v>
       </c>
@@ -29589,7 +29686,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="491"/>
+      <c r="A34" s="493"/>
       <c r="B34" s="20">
         <v>2021</v>
       </c>
@@ -29607,7 +29704,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A35" s="492" t="s">
+      <c r="A35" s="494" t="s">
         <v>20</v>
       </c>
       <c r="B35" s="7">
@@ -29627,7 +29724,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A36" s="493"/>
+      <c r="A36" s="495"/>
       <c r="B36" s="7">
         <v>2007</v>
       </c>
@@ -29645,7 +29742,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A37" s="493"/>
+      <c r="A37" s="495"/>
       <c r="B37" s="7">
         <v>2014</v>
       </c>
@@ -29663,7 +29760,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A38" s="494"/>
+      <c r="A38" s="496"/>
       <c r="B38" s="69">
         <v>2021</v>
       </c>
@@ -29681,7 +29778,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A39" s="489" t="s">
+      <c r="A39" s="491" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="20">
@@ -29701,7 +29798,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A40" s="490"/>
+      <c r="A40" s="492"/>
       <c r="B40" s="20">
         <v>2007</v>
       </c>
@@ -29719,7 +29816,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A41" s="490"/>
+      <c r="A41" s="492"/>
       <c r="B41" s="20">
         <v>2014</v>
       </c>
@@ -29737,7 +29834,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A42" s="491"/>
+      <c r="A42" s="493"/>
       <c r="B42" s="20">
         <v>2021</v>
       </c>
@@ -29850,16 +29947,16 @@
     </row>
     <row r="49" spans="1:10" ht="15.75" thickBot="1"/>
     <row r="50" spans="1:10" ht="48">
-      <c r="A50" s="453" t="s">
+      <c r="A50" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="C50" s="426" t="s">
+      <c r="C50" s="428" t="s">
         <v>44</v>
       </c>
-      <c r="D50" s="428" t="s">
+      <c r="D50" s="430" t="s">
         <v>814</v>
       </c>
       <c r="E50" s="11" t="s">
@@ -29870,12 +29967,12 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" thickBot="1">
-      <c r="A51" s="454"/>
+      <c r="A51" s="456"/>
       <c r="B51" s="135" t="s">
         <v>813</v>
       </c>
-      <c r="C51" s="427"/>
-      <c r="D51" s="429"/>
+      <c r="C51" s="429"/>
+      <c r="D51" s="431"/>
       <c r="E51" s="30" t="s">
         <v>51</v>
       </c>
@@ -30294,13 +30391,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="453" t="s">
+      <c r="A1" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="428" t="s">
+      <c r="C1" s="430" t="s">
         <v>826</v>
       </c>
       <c r="D1" s="11" t="s">
@@ -30311,11 +30408,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A2" s="454"/>
+      <c r="A2" s="456"/>
       <c r="B2" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="429"/>
+      <c r="C2" s="431"/>
       <c r="D2" s="30" t="s">
         <v>829</v>
       </c>
@@ -30444,14 +30541,14 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="12" spans="1:6">
-      <c r="A12" s="560" t="s">
+      <c r="A12" s="562" t="s">
         <v>171</v>
       </c>
-      <c r="B12" s="526"/>
+      <c r="B12" s="528"/>
       <c r="C12" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="428" t="s">
+      <c r="D12" s="430" t="s">
         <v>831</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -30462,12 +30559,12 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A13" s="561"/>
-      <c r="B13" s="528"/>
+      <c r="A13" s="563"/>
+      <c r="B13" s="530"/>
       <c r="C13" s="135" t="s">
         <v>830</v>
       </c>
-      <c r="D13" s="429"/>
+      <c r="D13" s="431"/>
       <c r="E13" s="30" t="s">
         <v>26</v>
       </c>
@@ -30476,7 +30573,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A14" s="492" t="s">
+      <c r="A14" s="494" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="7">
@@ -30496,7 +30593,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A15" s="493"/>
+      <c r="A15" s="495"/>
       <c r="B15" s="7">
         <v>2007</v>
       </c>
@@ -30514,7 +30611,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A16" s="493"/>
+      <c r="A16" s="495"/>
       <c r="B16" s="7">
         <v>2014</v>
       </c>
@@ -30532,7 +30629,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="494"/>
+      <c r="A17" s="496"/>
       <c r="B17" s="69">
         <v>2021</v>
       </c>
@@ -30550,7 +30647,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="489" t="s">
+      <c r="A18" s="491" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="20">
@@ -30570,7 +30667,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="490"/>
+      <c r="A19" s="492"/>
       <c r="B19" s="20">
         <v>2007</v>
       </c>
@@ -30588,7 +30685,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="490"/>
+      <c r="A20" s="492"/>
       <c r="B20" s="20">
         <v>2014</v>
       </c>
@@ -30606,7 +30703,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="491"/>
+      <c r="A21" s="493"/>
       <c r="B21" s="20">
         <v>2021</v>
       </c>
@@ -30624,7 +30721,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="492" t="s">
+      <c r="A22" s="494" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="7">
@@ -30644,7 +30741,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="493"/>
+      <c r="A23" s="495"/>
       <c r="B23" s="7">
         <v>2007</v>
       </c>
@@ -30662,7 +30759,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="493"/>
+      <c r="A24" s="495"/>
       <c r="B24" s="7">
         <v>2014</v>
       </c>
@@ -30680,7 +30777,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="494"/>
+      <c r="A25" s="496"/>
       <c r="B25" s="69">
         <v>2021</v>
       </c>
@@ -30698,7 +30795,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="489" t="s">
+      <c r="A26" s="491" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="20">
@@ -30718,7 +30815,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="490"/>
+      <c r="A27" s="492"/>
       <c r="B27" s="20">
         <v>2007</v>
       </c>
@@ -30736,7 +30833,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="490"/>
+      <c r="A28" s="492"/>
       <c r="B28" s="20">
         <v>2014</v>
       </c>
@@ -30754,7 +30851,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="491"/>
+      <c r="A29" s="493"/>
       <c r="B29" s="20">
         <v>2021</v>
       </c>
@@ -30772,7 +30869,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A30" s="492" t="s">
+      <c r="A30" s="494" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="7">
@@ -30792,7 +30889,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="493"/>
+      <c r="A31" s="495"/>
       <c r="B31" s="7">
         <v>2007</v>
       </c>
@@ -30810,7 +30907,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="493"/>
+      <c r="A32" s="495"/>
       <c r="B32" s="7">
         <v>2014</v>
       </c>
@@ -30828,7 +30925,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A33" s="494"/>
+      <c r="A33" s="496"/>
       <c r="B33" s="69">
         <v>2021</v>
       </c>
@@ -30846,7 +30943,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="36.75" thickBot="1">
-      <c r="A34" s="489" t="s">
+      <c r="A34" s="491" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="20">
@@ -30866,7 +30963,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="48.75" thickBot="1">
-      <c r="A35" s="490"/>
+      <c r="A35" s="492"/>
       <c r="B35" s="20">
         <v>2007</v>
       </c>
@@ -30884,7 +30981,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="48.75" thickBot="1">
-      <c r="A36" s="490"/>
+      <c r="A36" s="492"/>
       <c r="B36" s="20">
         <v>2014</v>
       </c>
@@ -30902,7 +30999,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="48.75" thickBot="1">
-      <c r="A37" s="491"/>
+      <c r="A37" s="493"/>
       <c r="B37" s="20">
         <v>2021</v>
       </c>
@@ -31362,10 +31459,10 @@
     </row>
     <row r="60" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="61" spans="1:9" ht="24.75" thickBot="1">
-      <c r="A61" s="512" t="s">
+      <c r="A61" s="514" t="s">
         <v>851</v>
       </c>
-      <c r="B61" s="513"/>
+      <c r="B61" s="515"/>
       <c r="C61" s="232" t="s">
         <v>852</v>
       </c>
@@ -31593,10 +31690,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="564" t="s">
+      <c r="B1" s="566" t="s">
         <v>1174</v>
       </c>
-      <c r="C1" s="507"/>
+      <c r="C1" s="509"/>
       <c r="D1" s="3">
         <v>2018</v>
       </c>
@@ -31966,14 +32063,14 @@
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="16" spans="1:9" ht="24">
-      <c r="A16" s="465"/>
-      <c r="B16" s="565" t="s">
+      <c r="A16" s="467"/>
+      <c r="B16" s="567" t="s">
         <v>1188</v>
       </c>
       <c r="C16" s="46" t="s">
         <v>1189</v>
       </c>
-      <c r="D16" s="567" t="s">
+      <c r="D16" s="569" t="s">
         <v>1191</v>
       </c>
       <c r="E16" s="11" t="s">
@@ -31984,12 +32081,12 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="477"/>
-      <c r="B17" s="566"/>
+      <c r="A17" s="479"/>
+      <c r="B17" s="568"/>
       <c r="C17" s="135" t="s">
         <v>1190</v>
       </c>
-      <c r="D17" s="568"/>
+      <c r="D17" s="570"/>
       <c r="E17" s="30" t="s">
         <v>1192</v>
       </c>
@@ -32423,7 +32520,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="569" t="s">
+      <c r="A47" s="571" t="s">
         <v>16</v>
       </c>
       <c r="B47" s="219">
@@ -32443,7 +32540,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="555"/>
+      <c r="A48" s="557"/>
       <c r="B48" s="7">
         <v>2007</v>
       </c>
@@ -32461,7 +32558,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="555"/>
+      <c r="A49" s="557"/>
       <c r="B49" s="7">
         <v>2014</v>
       </c>
@@ -32479,7 +32576,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="556"/>
+      <c r="A50" s="558"/>
       <c r="B50" s="69">
         <v>2021</v>
       </c>
@@ -32497,7 +32594,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="421" t="s">
+      <c r="A51" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B51" s="20">
@@ -32517,7 +32614,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="422"/>
+      <c r="A52" s="424"/>
       <c r="B52" s="20">
         <v>2007</v>
       </c>
@@ -32535,7 +32632,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="422"/>
+      <c r="A53" s="424"/>
       <c r="B53" s="20">
         <v>2014</v>
       </c>
@@ -32553,7 +32650,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="437"/>
+      <c r="A54" s="439"/>
       <c r="B54" s="20">
         <v>2021</v>
       </c>
@@ -32571,7 +32668,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="418" t="s">
+      <c r="A55" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B55" s="7">
@@ -32591,7 +32688,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="419"/>
+      <c r="A56" s="421"/>
       <c r="B56" s="7">
         <v>2007</v>
       </c>
@@ -32609,7 +32706,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="419"/>
+      <c r="A57" s="421"/>
       <c r="B57" s="7">
         <v>2014</v>
       </c>
@@ -32627,7 +32724,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="420"/>
+      <c r="A58" s="422"/>
       <c r="B58" s="69">
         <v>2021</v>
       </c>
@@ -32645,7 +32742,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="421" t="s">
+      <c r="A59" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B59" s="20">
@@ -32665,7 +32762,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="422"/>
+      <c r="A60" s="424"/>
       <c r="B60" s="20">
         <v>2007</v>
       </c>
@@ -32683,7 +32780,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="422"/>
+      <c r="A61" s="424"/>
       <c r="B61" s="20">
         <v>2014</v>
       </c>
@@ -32701,7 +32798,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="437"/>
+      <c r="A62" s="439"/>
       <c r="B62" s="20">
         <v>2021</v>
       </c>
@@ -32719,7 +32816,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="418" t="s">
+      <c r="A63" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="7">
@@ -32739,7 +32836,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="419"/>
+      <c r="A64" s="421"/>
       <c r="B64" s="7">
         <v>2007</v>
       </c>
@@ -32757,7 +32854,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A65" s="419"/>
+      <c r="A65" s="421"/>
       <c r="B65" s="7">
         <v>2014</v>
       </c>
@@ -32775,7 +32872,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A66" s="420"/>
+      <c r="A66" s="422"/>
       <c r="B66" s="69">
         <v>2021</v>
       </c>
@@ -32793,7 +32890,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A67" s="421" t="s">
+      <c r="A67" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="20">
@@ -32813,7 +32910,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A68" s="422"/>
+      <c r="A68" s="424"/>
       <c r="B68" s="20">
         <v>2007</v>
       </c>
@@ -32831,7 +32928,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A69" s="422"/>
+      <c r="A69" s="424"/>
       <c r="B69" s="20">
         <v>2014</v>
       </c>
@@ -32849,7 +32946,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A70" s="423"/>
+      <c r="A70" s="425"/>
       <c r="B70" s="24">
         <v>2021</v>
       </c>
@@ -32868,16 +32965,16 @@
     </row>
     <row r="72" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="73" spans="1:6" ht="36">
-      <c r="A73" s="453" t="s">
+      <c r="A73" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B73" s="358" t="s">
         <v>285</v>
       </c>
-      <c r="C73" s="499" t="s">
+      <c r="C73" s="501" t="s">
         <v>44</v>
       </c>
-      <c r="D73" s="562" t="s">
+      <c r="D73" s="564" t="s">
         <v>1204</v>
       </c>
       <c r="E73" s="11" t="s">
@@ -32888,12 +32985,12 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="18.75" thickBot="1">
-      <c r="A74" s="454"/>
+      <c r="A74" s="456"/>
       <c r="B74" s="135" t="s">
         <v>1203</v>
       </c>
-      <c r="C74" s="500"/>
-      <c r="D74" s="563"/>
+      <c r="C74" s="502"/>
+      <c r="D74" s="565"/>
       <c r="E74" s="30" t="s">
         <v>1205</v>
       </c>
@@ -33023,10 +33120,10 @@
     </row>
     <row r="82" spans="1:5" ht="15.75" thickBot="1"/>
     <row r="83" spans="1:5" ht="120">
-      <c r="A83" s="453" t="s">
+      <c r="A83" s="455" t="s">
         <v>556</v>
       </c>
-      <c r="B83" s="426" t="s">
+      <c r="B83" s="428" t="s">
         <v>1207</v>
       </c>
       <c r="C83" s="359" t="s">
@@ -33040,8 +33137,8 @@
       </c>
     </row>
     <row r="84" spans="1:5" ht="36.75" thickBot="1">
-      <c r="A84" s="454"/>
-      <c r="B84" s="427"/>
+      <c r="A84" s="456"/>
+      <c r="B84" s="429"/>
       <c r="C84" s="38" t="s">
         <v>1209</v>
       </c>
@@ -33621,29 +33718,29 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11" ht="22.5">
-      <c r="A1" s="583"/>
+      <c r="A1" s="585"/>
       <c r="B1" s="308" t="s">
         <v>199</v>
       </c>
-      <c r="C1" s="570" t="s">
+      <c r="C1" s="572" t="s">
         <v>174</v>
       </c>
       <c r="D1" s="308" t="s">
         <v>1237</v>
       </c>
-      <c r="E1" s="570" t="s">
+      <c r="E1" s="572" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="570" t="s">
+      <c r="F1" s="572" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="584" t="s">
+      <c r="G1" s="586" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="570" t="s">
+      <c r="H1" s="572" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="570"/>
+      <c r="I1" s="572"/>
       <c r="J1" s="11" t="s">
         <v>8</v>
       </c>
@@ -33652,17 +33749,17 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="583"/>
+      <c r="A2" s="585"/>
       <c r="B2" s="308" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="570"/>
+      <c r="C2" s="572"/>
       <c r="D2" s="308" t="s">
         <v>1238</v>
       </c>
-      <c r="E2" s="570"/>
-      <c r="F2" s="570"/>
-      <c r="G2" s="584"/>
+      <c r="E2" s="572"/>
+      <c r="F2" s="572"/>
+      <c r="G2" s="586"/>
       <c r="H2" s="308" t="s">
         <v>1239</v>
       </c>
@@ -35280,7 +35377,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A55" s="579" t="s">
+      <c r="A55" s="581" t="s">
         <v>1242</v>
       </c>
       <c r="B55" s="382">
@@ -35312,7 +35409,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A56" s="580"/>
+      <c r="A56" s="582"/>
       <c r="B56" s="376">
         <v>2014</v>
       </c>
@@ -35342,7 +35439,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A57" s="581"/>
+      <c r="A57" s="583"/>
       <c r="B57" s="376">
         <v>2021</v>
       </c>
@@ -35372,7 +35469,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A58" s="577" t="s">
+      <c r="A58" s="579" t="s">
         <v>1247</v>
       </c>
       <c r="B58" s="378">
@@ -35404,7 +35501,7 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A59" s="572"/>
+      <c r="A59" s="574"/>
       <c r="B59" s="378">
         <v>2014</v>
       </c>
@@ -35434,7 +35531,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A60" s="578"/>
+      <c r="A60" s="580"/>
       <c r="B60" s="380">
         <v>2021</v>
       </c>
@@ -35464,7 +35561,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A61" s="579" t="s">
+      <c r="A61" s="581" t="s">
         <v>1244</v>
       </c>
       <c r="B61" s="376">
@@ -35496,7 +35593,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A62" s="580"/>
+      <c r="A62" s="582"/>
       <c r="B62" s="376">
         <v>2014</v>
       </c>
@@ -35526,7 +35623,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A63" s="581"/>
+      <c r="A63" s="583"/>
       <c r="B63" s="376">
         <v>2021</v>
       </c>
@@ -35556,7 +35653,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A64" s="577" t="s">
+      <c r="A64" s="579" t="s">
         <v>1240</v>
       </c>
       <c r="B64" s="378">
@@ -35588,7 +35685,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A65" s="572"/>
+      <c r="A65" s="574"/>
       <c r="B65" s="378">
         <v>2014</v>
       </c>
@@ -35618,7 +35715,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A66" s="578"/>
+      <c r="A66" s="580"/>
       <c r="B66" s="380">
         <v>2021</v>
       </c>
@@ -35648,7 +35745,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A67" s="579" t="s">
+      <c r="A67" s="581" t="s">
         <v>1249</v>
       </c>
       <c r="B67" s="376">
@@ -35680,7 +35777,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A68" s="580"/>
+      <c r="A68" s="582"/>
       <c r="B68" s="376">
         <v>2014</v>
       </c>
@@ -35710,7 +35807,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A69" s="581"/>
+      <c r="A69" s="583"/>
       <c r="B69" s="376">
         <v>2021</v>
       </c>
@@ -35740,7 +35837,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A70" s="577" t="s">
+      <c r="A70" s="579" t="s">
         <v>1243</v>
       </c>
       <c r="B70" s="378">
@@ -35772,7 +35869,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A71" s="572"/>
+      <c r="A71" s="574"/>
       <c r="B71" s="378">
         <v>2014</v>
       </c>
@@ -35802,7 +35899,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A72" s="578"/>
+      <c r="A72" s="580"/>
       <c r="B72" s="380">
         <v>2021</v>
       </c>
@@ -35832,7 +35929,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A73" s="579" t="s">
+      <c r="A73" s="581" t="s">
         <v>1251</v>
       </c>
       <c r="B73" s="376">
@@ -35864,7 +35961,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A74" s="580"/>
+      <c r="A74" s="582"/>
       <c r="B74" s="376">
         <v>2014</v>
       </c>
@@ -35894,7 +35991,7 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A75" s="581"/>
+      <c r="A75" s="583"/>
       <c r="B75" s="376">
         <v>2021</v>
       </c>
@@ -35924,7 +36021,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A76" s="577" t="s">
+      <c r="A76" s="579" t="s">
         <v>1241</v>
       </c>
       <c r="B76" s="378">
@@ -35956,7 +36053,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A77" s="572"/>
+      <c r="A77" s="574"/>
       <c r="B77" s="378">
         <v>2014</v>
       </c>
@@ -35986,7 +36083,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A78" s="578"/>
+      <c r="A78" s="580"/>
       <c r="B78" s="380">
         <v>2021</v>
       </c>
@@ -36016,7 +36113,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A79" s="579" t="s">
+      <c r="A79" s="581" t="s">
         <v>1259</v>
       </c>
       <c r="B79" s="376">
@@ -36048,7 +36145,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A80" s="580"/>
+      <c r="A80" s="582"/>
       <c r="B80" s="376">
         <v>2014</v>
       </c>
@@ -36078,7 +36175,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A81" s="581"/>
+      <c r="A81" s="583"/>
       <c r="B81" s="376">
         <v>2021</v>
       </c>
@@ -36108,7 +36205,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A82" s="577" t="s">
+      <c r="A82" s="579" t="s">
         <v>66</v>
       </c>
       <c r="B82" s="378">
@@ -36140,7 +36237,7 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A83" s="572"/>
+      <c r="A83" s="574"/>
       <c r="B83" s="378">
         <v>2014</v>
       </c>
@@ -36170,7 +36267,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A84" s="578"/>
+      <c r="A84" s="580"/>
       <c r="B84" s="380">
         <v>2021</v>
       </c>
@@ -36200,7 +36297,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A85" s="579" t="s">
+      <c r="A85" s="581" t="s">
         <v>1252</v>
       </c>
       <c r="B85" s="376">
@@ -36232,7 +36329,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A86" s="580"/>
+      <c r="A86" s="582"/>
       <c r="B86" s="376">
         <v>2014</v>
       </c>
@@ -36262,7 +36359,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A87" s="581"/>
+      <c r="A87" s="583"/>
       <c r="B87" s="376">
         <v>2021</v>
       </c>
@@ -36292,7 +36389,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A88" s="579" t="s">
+      <c r="A88" s="581" t="s">
         <v>1254</v>
       </c>
       <c r="B88" s="382">
@@ -36324,7 +36421,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A89" s="580"/>
+      <c r="A89" s="582"/>
       <c r="B89" s="376">
         <v>2014</v>
       </c>
@@ -36354,7 +36451,7 @@
       </c>
     </row>
     <row r="90" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A90" s="581"/>
+      <c r="A90" s="583"/>
       <c r="B90" s="376">
         <v>2021</v>
       </c>
@@ -36384,7 +36481,7 @@
       </c>
     </row>
     <row r="91" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A91" s="577" t="s">
+      <c r="A91" s="579" t="s">
         <v>1248</v>
       </c>
       <c r="B91" s="378">
@@ -36416,7 +36513,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A92" s="572"/>
+      <c r="A92" s="574"/>
       <c r="B92" s="378">
         <v>2014</v>
       </c>
@@ -36446,7 +36543,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A93" s="578"/>
+      <c r="A93" s="580"/>
       <c r="B93" s="380">
         <v>2021</v>
       </c>
@@ -36476,7 +36573,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A94" s="579" t="s">
+      <c r="A94" s="581" t="s">
         <v>1250</v>
       </c>
       <c r="B94" s="376">
@@ -36508,7 +36605,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A95" s="580"/>
+      <c r="A95" s="582"/>
       <c r="B95" s="376">
         <v>2014</v>
       </c>
@@ -36538,7 +36635,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A96" s="581"/>
+      <c r="A96" s="583"/>
       <c r="B96" s="376">
         <v>2021</v>
       </c>
@@ -36568,7 +36665,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A97" s="577" t="s">
+      <c r="A97" s="579" t="s">
         <v>1246</v>
       </c>
       <c r="B97" s="378">
@@ -36600,7 +36697,7 @@
       </c>
     </row>
     <row r="98" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A98" s="572"/>
+      <c r="A98" s="574"/>
       <c r="B98" s="378">
         <v>2014</v>
       </c>
@@ -36630,7 +36727,7 @@
       </c>
     </row>
     <row r="99" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A99" s="578"/>
+      <c r="A99" s="580"/>
       <c r="B99" s="380">
         <v>2021</v>
       </c>
@@ -36754,7 +36851,7 @@
       </c>
     </row>
     <row r="103" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A103" s="577" t="s">
+      <c r="A103" s="579" t="s">
         <v>1253</v>
       </c>
       <c r="B103" s="378">
@@ -36786,7 +36883,7 @@
       </c>
     </row>
     <row r="104" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A104" s="572"/>
+      <c r="A104" s="574"/>
       <c r="B104" s="378">
         <v>2014</v>
       </c>
@@ -36816,7 +36913,7 @@
       </c>
     </row>
     <row r="105" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A105" s="578"/>
+      <c r="A105" s="580"/>
       <c r="B105" s="380">
         <v>2021</v>
       </c>
@@ -36846,7 +36943,7 @@
       </c>
     </row>
     <row r="106" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A106" s="579" t="s">
+      <c r="A106" s="581" t="s">
         <v>1264</v>
       </c>
       <c r="B106" s="376">
@@ -36878,7 +36975,7 @@
       </c>
     </row>
     <row r="107" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A107" s="580"/>
+      <c r="A107" s="582"/>
       <c r="B107" s="376">
         <v>2014</v>
       </c>
@@ -36908,7 +37005,7 @@
       </c>
     </row>
     <row r="108" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A108" s="581"/>
+      <c r="A108" s="583"/>
       <c r="B108" s="376">
         <v>2021</v>
       </c>
@@ -36938,7 +37035,7 @@
       </c>
     </row>
     <row r="109" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A109" s="577" t="s">
+      <c r="A109" s="579" t="s">
         <v>1245</v>
       </c>
       <c r="B109" s="378">
@@ -36970,7 +37067,7 @@
       </c>
     </row>
     <row r="110" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A110" s="572"/>
+      <c r="A110" s="574"/>
       <c r="B110" s="378">
         <v>2014</v>
       </c>
@@ -37000,7 +37097,7 @@
       </c>
     </row>
     <row r="111" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A111" s="578"/>
+      <c r="A111" s="580"/>
       <c r="B111" s="380">
         <v>2021</v>
       </c>
@@ -37030,7 +37127,7 @@
       </c>
     </row>
     <row r="112" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A112" s="579" t="s">
+      <c r="A112" s="581" t="s">
         <v>1276</v>
       </c>
       <c r="B112" s="376">
@@ -37062,7 +37159,7 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A113" s="580"/>
+      <c r="A113" s="582"/>
       <c r="B113" s="376">
         <v>2014</v>
       </c>
@@ -37092,7 +37189,7 @@
       </c>
     </row>
     <row r="114" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A114" s="581"/>
+      <c r="A114" s="583"/>
       <c r="B114" s="376">
         <v>2021</v>
       </c>
@@ -37122,7 +37219,7 @@
       </c>
     </row>
     <row r="115" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A115" s="577" t="s">
+      <c r="A115" s="579" t="s">
         <v>1255</v>
       </c>
       <c r="B115" s="378">
@@ -37154,7 +37251,7 @@
       </c>
     </row>
     <row r="116" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A116" s="572"/>
+      <c r="A116" s="574"/>
       <c r="B116" s="378">
         <v>2014</v>
       </c>
@@ -37184,7 +37281,7 @@
       </c>
     </row>
     <row r="117" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A117" s="578"/>
+      <c r="A117" s="580"/>
       <c r="B117" s="380">
         <v>2021</v>
       </c>
@@ -37214,7 +37311,7 @@
       </c>
     </row>
     <row r="118" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A118" s="579" t="s">
+      <c r="A118" s="581" t="s">
         <v>1277</v>
       </c>
       <c r="B118" s="376">
@@ -37246,7 +37343,7 @@
       </c>
     </row>
     <row r="119" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A119" s="580"/>
+      <c r="A119" s="582"/>
       <c r="B119" s="376">
         <v>2014</v>
       </c>
@@ -37276,7 +37373,7 @@
       </c>
     </row>
     <row r="120" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A120" s="581"/>
+      <c r="A120" s="583"/>
       <c r="B120" s="376">
         <v>2021</v>
       </c>
@@ -37306,11 +37403,11 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="582"/>
+      <c r="A123" s="584"/>
       <c r="B123" s="308" t="s">
         <v>1278</v>
       </c>
-      <c r="C123" s="576" t="s">
+      <c r="C123" s="578" t="s">
         <v>1280</v>
       </c>
       <c r="D123" s="308" t="s">
@@ -37322,10 +37419,10 @@
       <c r="F123" s="308" t="s">
         <v>1285</v>
       </c>
-      <c r="G123" s="570" t="s">
+      <c r="G123" s="572" t="s">
         <v>1287</v>
       </c>
-      <c r="H123" s="570" t="s">
+      <c r="H123" s="572" t="s">
         <v>1288</v>
       </c>
       <c r="I123" s="11" t="s">
@@ -37336,11 +37433,11 @@
       </c>
     </row>
     <row r="124" spans="1:10" ht="47.25">
-      <c r="A124" s="582"/>
+      <c r="A124" s="584"/>
       <c r="B124" s="386" t="s">
         <v>1279</v>
       </c>
-      <c r="C124" s="576"/>
+      <c r="C124" s="578"/>
       <c r="D124" s="313" t="s">
         <v>1282</v>
       </c>
@@ -37350,8 +37447,8 @@
       <c r="F124" s="308" t="s">
         <v>1286</v>
       </c>
-      <c r="G124" s="570"/>
-      <c r="H124" s="570"/>
+      <c r="G124" s="572"/>
+      <c r="H124" s="572"/>
       <c r="I124" s="30" t="s">
         <v>1297</v>
       </c>
@@ -37360,16 +37457,16 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="582"/>
+      <c r="A125" s="584"/>
       <c r="B125" s="387"/>
-      <c r="C125" s="576"/>
+      <c r="C125" s="578"/>
       <c r="D125" s="388"/>
       <c r="E125" s="313" t="s">
         <v>1282</v>
       </c>
       <c r="F125" s="388"/>
-      <c r="G125" s="570"/>
-      <c r="H125" s="570"/>
+      <c r="G125" s="572"/>
+      <c r="H125" s="572"/>
       <c r="I125" s="30" t="s">
         <v>1297</v>
       </c>
@@ -37823,25 +37920,25 @@
       <c r="A140" s="389" t="s">
         <v>1303</v>
       </c>
-      <c r="B140" s="571">
+      <c r="B140" s="573">
         <v>1182000</v>
       </c>
-      <c r="C140" s="572" t="s">
+      <c r="C140" s="574" t="s">
         <v>50</v>
       </c>
-      <c r="D140" s="573">
+      <c r="D140" s="575">
         <v>1182000</v>
       </c>
-      <c r="E140" s="574" t="s">
+      <c r="E140" s="576" t="s">
         <v>50</v>
       </c>
-      <c r="F140" s="574" t="s">
+      <c r="F140" s="576" t="s">
         <v>217</v>
       </c>
-      <c r="G140" s="574">
+      <c r="G140" s="576">
         <v>2019</v>
       </c>
-      <c r="H140" s="575" t="s">
+      <c r="H140" s="577" t="s">
         <v>1300</v>
       </c>
       <c r="I140" s="30" t="s">
@@ -37855,13 +37952,13 @@
       <c r="A141" s="389" t="s">
         <v>1304</v>
       </c>
-      <c r="B141" s="571"/>
-      <c r="C141" s="572"/>
-      <c r="D141" s="573"/>
-      <c r="E141" s="574"/>
-      <c r="F141" s="574"/>
-      <c r="G141" s="574"/>
-      <c r="H141" s="575"/>
+      <c r="B141" s="573"/>
+      <c r="C141" s="574"/>
+      <c r="D141" s="575"/>
+      <c r="E141" s="576"/>
+      <c r="F141" s="576"/>
+      <c r="G141" s="576"/>
+      <c r="H141" s="577"/>
       <c r="I141" s="30" t="s">
         <v>1297</v>
       </c>
@@ -38010,6 +38107,1081 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1DFE33-9B13-4B15-944C-27A708967146}">
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="9" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="416" customFormat="1">
+      <c r="A1" s="416" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1" s="413">
+        <v>2000</v>
+      </c>
+      <c r="C1" s="413">
+        <v>2001</v>
+      </c>
+      <c r="D1" s="413">
+        <v>2002</v>
+      </c>
+      <c r="E1" s="413">
+        <v>2003</v>
+      </c>
+      <c r="F1" s="413">
+        <v>2004</v>
+      </c>
+      <c r="G1" s="413">
+        <v>2005</v>
+      </c>
+      <c r="H1" s="413">
+        <v>2006</v>
+      </c>
+      <c r="I1" s="413">
+        <v>2007</v>
+      </c>
+      <c r="J1" s="413">
+        <v>2008</v>
+      </c>
+      <c r="K1" s="413">
+        <v>2009</v>
+      </c>
+      <c r="L1" s="413">
+        <v>2010</v>
+      </c>
+      <c r="M1" s="413">
+        <v>2011</v>
+      </c>
+      <c r="N1" s="413">
+        <v>2012</v>
+      </c>
+      <c r="O1" s="413">
+        <v>2013</v>
+      </c>
+      <c r="P1" s="413">
+        <v>2014</v>
+      </c>
+      <c r="Q1" s="413">
+        <v>2015</v>
+      </c>
+      <c r="R1" s="413">
+        <v>2016</v>
+      </c>
+      <c r="S1" s="413">
+        <v>2017</v>
+      </c>
+      <c r="T1" s="413">
+        <v>2018</v>
+      </c>
+      <c r="U1" s="413">
+        <v>2019</v>
+      </c>
+      <c r="V1" s="413">
+        <v>2020</v>
+      </c>
+      <c r="W1" s="413">
+        <v>2021</v>
+      </c>
+      <c r="X1" s="413">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B2" s="419">
+        <v>2.19</v>
+      </c>
+      <c r="C2" s="419">
+        <v>2.38</v>
+      </c>
+      <c r="D2" s="419">
+        <v>2.15</v>
+      </c>
+      <c r="E2" s="419">
+        <v>1.72</v>
+      </c>
+      <c r="F2" s="419">
+        <v>1.51</v>
+      </c>
+      <c r="G2" s="419">
+        <v>1.42</v>
+      </c>
+      <c r="H2" s="419">
+        <v>1.54</v>
+      </c>
+      <c r="I2" s="419">
+        <v>1.36</v>
+      </c>
+      <c r="J2" s="419">
+        <v>1.32</v>
+      </c>
+      <c r="K2" s="419">
+        <v>1.39</v>
+      </c>
+      <c r="L2" s="419">
+        <v>1.3</v>
+      </c>
+      <c r="M2" s="419">
+        <v>1.29</v>
+      </c>
+      <c r="N2" s="419">
+        <v>1.21</v>
+      </c>
+      <c r="O2" s="419">
+        <v>1.22</v>
+      </c>
+      <c r="P2" s="419">
+        <v>1.28</v>
+      </c>
+      <c r="Q2" s="419">
+        <v>1.47</v>
+      </c>
+      <c r="R2" s="419">
+        <v>1.44</v>
+      </c>
+      <c r="S2" s="419">
+        <v>1.42</v>
+      </c>
+      <c r="T2" s="419">
+        <v>1.48</v>
+      </c>
+      <c r="U2" s="419">
+        <v>1.5</v>
+      </c>
+      <c r="V2" s="419">
+        <v>1.4</v>
+      </c>
+      <c r="W2" s="419">
+        <v>1.47</v>
+      </c>
+      <c r="X2" s="419">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B3" s="419">
+        <v>2.13</v>
+      </c>
+      <c r="C3" s="419">
+        <v>2.33</v>
+      </c>
+      <c r="D3" s="419">
+        <v>2.15</v>
+      </c>
+      <c r="E3" s="419">
+        <v>1.85</v>
+      </c>
+      <c r="F3" s="419">
+        <v>1.73</v>
+      </c>
+      <c r="G3" s="419">
+        <v>1.7</v>
+      </c>
+      <c r="H3" s="419">
+        <v>1.73</v>
+      </c>
+      <c r="I3" s="419">
+        <v>1.6</v>
+      </c>
+      <c r="J3" s="419">
+        <v>1.51</v>
+      </c>
+      <c r="K3" s="419">
+        <v>1.92</v>
+      </c>
+      <c r="L3" s="419">
+        <v>1.81</v>
+      </c>
+      <c r="M3" s="419">
+        <v>1.84</v>
+      </c>
+      <c r="N3" s="419">
+        <v>1.79</v>
+      </c>
+      <c r="O3" s="419">
+        <v>1.88</v>
+      </c>
+      <c r="P3" s="419">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" s="419">
+        <v>2.13</v>
+      </c>
+      <c r="R3" s="419">
+        <v>2.13</v>
+      </c>
+      <c r="S3" s="419">
+        <v>2.06</v>
+      </c>
+      <c r="T3" s="419">
+        <v>2.13</v>
+      </c>
+      <c r="U3" s="419">
+        <v>2.16</v>
+      </c>
+      <c r="V3" s="419">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="W3" s="419">
+        <v>2.12</v>
+      </c>
+      <c r="X3" s="419">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B4" s="419">
+        <v>1.74</v>
+      </c>
+      <c r="C4" s="419">
+        <v>1.95</v>
+      </c>
+      <c r="D4" s="419">
+        <v>1.83</v>
+      </c>
+      <c r="E4" s="419">
+        <v>1.52</v>
+      </c>
+      <c r="F4" s="419">
+        <v>1.36</v>
+      </c>
+      <c r="G4" s="419">
+        <v>1.31</v>
+      </c>
+      <c r="H4" s="419">
+        <v>1.32</v>
+      </c>
+      <c r="I4" s="419">
+        <v>1.19</v>
+      </c>
+      <c r="J4" s="419">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K4" s="419">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L4" s="419">
+        <v>0.1</v>
+      </c>
+      <c r="M4" s="419">
+        <v>0.98</v>
+      </c>
+      <c r="N4" s="419">
+        <v>0.96</v>
+      </c>
+      <c r="O4" s="419">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="P4" s="419">
+        <v>1.22</v>
+      </c>
+      <c r="Q4" s="419">
+        <v>1.37</v>
+      </c>
+      <c r="R4" s="419">
+        <v>1.37</v>
+      </c>
+      <c r="S4" s="419">
+        <v>1.29</v>
+      </c>
+      <c r="T4" s="419">
+        <v>1.42</v>
+      </c>
+      <c r="U4" s="419">
+        <v>1.44</v>
+      </c>
+      <c r="V4" s="419">
+        <v>1.32</v>
+      </c>
+      <c r="W4" s="419">
+        <v>1.38</v>
+      </c>
+      <c r="X4" s="419">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B5" s="419">
+        <v>2.76</v>
+      </c>
+      <c r="C5" s="419">
+        <v>3.36</v>
+      </c>
+      <c r="D5" s="419">
+        <v>3.89</v>
+      </c>
+      <c r="E5" s="419">
+        <v>3.55</v>
+      </c>
+      <c r="F5" s="419">
+        <v>3.22</v>
+      </c>
+      <c r="G5" s="419">
+        <v>3.1</v>
+      </c>
+      <c r="H5" s="419">
+        <v>3.06</v>
+      </c>
+      <c r="I5" s="419">
+        <v>2.96</v>
+      </c>
+      <c r="J5" s="419">
+        <v>2.77</v>
+      </c>
+      <c r="K5" s="419">
+        <v>2.65</v>
+      </c>
+      <c r="L5" s="419">
+        <v>2.63</v>
+      </c>
+      <c r="M5" s="419">
+        <v>2.13</v>
+      </c>
+      <c r="N5" s="419">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="O5" s="419">
+        <v>2.42</v>
+      </c>
+      <c r="P5" s="419">
+        <v>2.57</v>
+      </c>
+      <c r="Q5" s="419">
+        <v>2.98</v>
+      </c>
+      <c r="R5" s="419">
+        <v>3.25</v>
+      </c>
+      <c r="S5" s="419">
+        <v>3.25</v>
+      </c>
+      <c r="T5" s="419">
+        <v>3.25</v>
+      </c>
+      <c r="U5" s="419">
+        <v>3.41</v>
+      </c>
+      <c r="V5" s="419">
+        <v>3.51</v>
+      </c>
+      <c r="W5" s="419">
+        <v>3.51</v>
+      </c>
+      <c r="X5" s="419">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B6" s="419">
+        <v>3.27</v>
+      </c>
+      <c r="C6" s="419">
+        <v>3.47</v>
+      </c>
+      <c r="D6" s="419">
+        <v>3.37</v>
+      </c>
+      <c r="E6" s="419">
+        <v>3</v>
+      </c>
+      <c r="F6" s="419">
+        <v>2.78</v>
+      </c>
+      <c r="G6" s="419">
+        <v>2.71</v>
+      </c>
+      <c r="H6" s="419">
+        <v>2.78</v>
+      </c>
+      <c r="I6" s="419">
+        <v>2.62</v>
+      </c>
+      <c r="J6" s="419">
+        <v>2.52</v>
+      </c>
+      <c r="K6" s="419">
+        <v>2.5</v>
+      </c>
+      <c r="L6" s="419">
+        <v>2.35</v>
+      </c>
+      <c r="M6" s="419">
+        <v>2.36</v>
+      </c>
+      <c r="N6" s="419">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="O6" s="419">
+        <v>2.33</v>
+      </c>
+      <c r="P6" s="419">
+        <v>2.39</v>
+      </c>
+      <c r="Q6" s="419">
+        <v>2.58</v>
+      </c>
+      <c r="R6" s="419">
+        <v>2.61</v>
+      </c>
+      <c r="S6" s="419">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="T6" s="419">
+        <v>2.62</v>
+      </c>
+      <c r="U6" s="419">
+        <v>2.67</v>
+      </c>
+      <c r="V6" s="419">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="W6" s="419">
+        <v>2.59</v>
+      </c>
+      <c r="X6" s="419">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B7" s="419">
+        <v>5.09</v>
+      </c>
+      <c r="C7" s="419">
+        <v>5.28</v>
+      </c>
+      <c r="D7" s="419">
+        <v>6.75</v>
+      </c>
+      <c r="E7" s="419">
+        <v>7.51</v>
+      </c>
+      <c r="F7" s="419">
+        <v>7.48</v>
+      </c>
+      <c r="G7" s="419">
+        <v>7.53</v>
+      </c>
+      <c r="H7" s="419">
+        <v>7.61</v>
+      </c>
+      <c r="I7" s="419">
+        <v>7.65</v>
+      </c>
+      <c r="J7" s="419">
+        <v>7.67</v>
+      </c>
+      <c r="K7" s="419">
+        <v>7.88</v>
+      </c>
+      <c r="L7" s="419">
+        <v>7.85</v>
+      </c>
+      <c r="M7" s="419">
+        <v>7.24</v>
+      </c>
+      <c r="N7" s="419">
+        <v>7.07</v>
+      </c>
+      <c r="O7" s="419">
+        <v>7.19</v>
+      </c>
+      <c r="P7" s="419">
+        <v>7.63</v>
+      </c>
+      <c r="Q7" s="419">
+        <v>8.16</v>
+      </c>
+      <c r="R7" s="419">
+        <v>7.99</v>
+      </c>
+      <c r="S7" s="419">
+        <v>7.75</v>
+      </c>
+      <c r="T7" s="419">
+        <v>8.02</v>
+      </c>
+      <c r="U7" s="419">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="V7" s="419">
+        <v>8.02</v>
+      </c>
+      <c r="W7" s="419">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="X7" s="419">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B8" s="419">
+        <v>1.64</v>
+      </c>
+      <c r="C8" s="419">
+        <v>1.95</v>
+      </c>
+      <c r="D8" s="419">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="E8" s="419">
+        <v>2.19</v>
+      </c>
+      <c r="F8" s="419">
+        <v>2.04</v>
+      </c>
+      <c r="G8" s="419">
+        <v>1.93</v>
+      </c>
+      <c r="H8" s="419">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="I8" s="419">
+        <v>2.02</v>
+      </c>
+      <c r="J8" s="419">
+        <v>1.85</v>
+      </c>
+      <c r="K8" s="419">
+        <v>1.9</v>
+      </c>
+      <c r="L8" s="419">
+        <v>1.81</v>
+      </c>
+      <c r="M8" s="419">
+        <v>1.73</v>
+      </c>
+      <c r="N8" s="419">
+        <v>1.74</v>
+      </c>
+      <c r="O8" s="419">
+        <v>1.85</v>
+      </c>
+      <c r="P8" s="419">
+        <v>1.86</v>
+      </c>
+      <c r="Q8" s="419">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R8" s="419">
+        <v>2.31</v>
+      </c>
+      <c r="S8" s="419">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="T8" s="419">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="U8" s="419">
+        <v>2.35</v>
+      </c>
+      <c r="V8" s="419">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="W8" s="419">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="X8" s="419">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B9" s="419">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="C9" s="419">
+        <v>145.69999999999999</v>
+      </c>
+      <c r="D9" s="419">
+        <v>139.1</v>
+      </c>
+      <c r="E9" s="419">
+        <v>122.2</v>
+      </c>
+      <c r="F9" s="419">
+        <v>111.9</v>
+      </c>
+      <c r="G9" s="419">
+        <v>109</v>
+      </c>
+      <c r="H9" s="419">
+        <v>110</v>
+      </c>
+      <c r="I9" s="419">
+        <v>104</v>
+      </c>
+      <c r="J9" s="419">
+        <v>96.77</v>
+      </c>
+      <c r="K9" s="419">
+        <v>99.72</v>
+      </c>
+      <c r="L9" s="419">
+        <v>95.24</v>
+      </c>
+      <c r="M9" s="419">
+        <v>95.43</v>
+      </c>
+      <c r="N9" s="419">
+        <v>93.51</v>
+      </c>
+      <c r="O9" s="419">
+        <v>96.02</v>
+      </c>
+      <c r="P9" s="419">
+        <v>102.51</v>
+      </c>
+      <c r="Q9" s="419">
+        <v>109.57</v>
+      </c>
+      <c r="R9" s="419">
+        <v>110.5</v>
+      </c>
+      <c r="S9" s="419">
+        <v>105.92</v>
+      </c>
+      <c r="T9" s="419">
+        <v>113.97</v>
+      </c>
+      <c r="U9" s="419">
+        <v>116.05</v>
+      </c>
+      <c r="V9" s="419">
+        <v>109.3</v>
+      </c>
+      <c r="W9" s="419">
+        <v>113.07</v>
+      </c>
+      <c r="X9" s="419">
+        <v>122.77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" t="s">
+        <v>954</v>
+      </c>
+      <c r="B10" s="419">
+        <v>130</v>
+      </c>
+      <c r="C10" s="419">
+        <v>133</v>
+      </c>
+      <c r="D10" s="419">
+        <v>127</v>
+      </c>
+      <c r="E10" s="419">
+        <v>106</v>
+      </c>
+      <c r="F10" s="419">
+        <v>96</v>
+      </c>
+      <c r="G10" s="419">
+        <v>96</v>
+      </c>
+      <c r="H10" s="419">
+        <v>95</v>
+      </c>
+      <c r="I10" s="419">
+        <v>87</v>
+      </c>
+      <c r="J10" s="419">
+        <v>80</v>
+      </c>
+      <c r="K10" s="419">
+        <v>83.22</v>
+      </c>
+      <c r="L10" s="419">
+        <v>90.27</v>
+      </c>
+      <c r="M10" s="419">
+        <v>92.16</v>
+      </c>
+      <c r="N10" s="419">
+        <v>89.88</v>
+      </c>
+      <c r="O10" s="419">
+        <v>86.01</v>
+      </c>
+      <c r="P10" s="419">
+        <v>98.13</v>
+      </c>
+      <c r="Q10" s="419">
+        <v>108.81</v>
+      </c>
+      <c r="R10" s="419">
+        <v>114.17</v>
+      </c>
+      <c r="S10" s="419">
+        <v>99.42</v>
+      </c>
+      <c r="T10" s="419">
+        <v>104.39</v>
+      </c>
+      <c r="U10" s="419">
+        <v>106.78</v>
+      </c>
+      <c r="V10" s="419">
+        <v>98</v>
+      </c>
+      <c r="W10" s="419">
+        <v>105.37</v>
+      </c>
+      <c r="X10" s="419">
+        <v>120.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="P13" s="418">
+        <v>2000</v>
+      </c>
+      <c r="Q13" s="419"/>
+      <c r="R13" s="419"/>
+      <c r="S13" s="419"/>
+      <c r="T13" s="419"/>
+      <c r="U13" s="419"/>
+      <c r="V13" s="419"/>
+      <c r="W13" s="419"/>
+      <c r="X13" s="419"/>
+      <c r="Y13" s="419"/>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="P14" s="418">
+        <v>2001</v>
+      </c>
+      <c r="Q14" s="419"/>
+      <c r="R14" s="419"/>
+      <c r="S14" s="419"/>
+      <c r="T14" s="419"/>
+      <c r="U14" s="419"/>
+      <c r="V14" s="419"/>
+      <c r="W14" s="419"/>
+      <c r="X14" s="419"/>
+      <c r="Y14" s="419"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="P15" s="418">
+        <v>2002</v>
+      </c>
+      <c r="Q15" s="419"/>
+      <c r="R15" s="419"/>
+      <c r="S15" s="419"/>
+      <c r="T15" s="419"/>
+      <c r="U15" s="419"/>
+      <c r="V15" s="419"/>
+      <c r="W15" s="419"/>
+      <c r="X15" s="419"/>
+      <c r="Y15" s="419"/>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="P16" s="418">
+        <v>2003</v>
+      </c>
+      <c r="Q16" s="419"/>
+      <c r="R16" s="419"/>
+      <c r="S16" s="419"/>
+      <c r="T16" s="419"/>
+      <c r="U16" s="419"/>
+      <c r="V16" s="419"/>
+      <c r="W16" s="419"/>
+      <c r="X16" s="419"/>
+      <c r="Y16" s="419"/>
+    </row>
+    <row r="17" spans="16:25">
+      <c r="P17" s="418">
+        <v>2004</v>
+      </c>
+      <c r="Q17" s="419"/>
+      <c r="R17" s="419"/>
+      <c r="S17" s="419"/>
+      <c r="T17" s="419"/>
+      <c r="U17" s="419"/>
+      <c r="V17" s="419"/>
+      <c r="W17" s="419"/>
+      <c r="X17" s="419"/>
+      <c r="Y17" s="419"/>
+    </row>
+    <row r="18" spans="16:25">
+      <c r="P18" s="418">
+        <v>2005</v>
+      </c>
+      <c r="Q18" s="419"/>
+      <c r="R18" s="419"/>
+      <c r="S18" s="419"/>
+      <c r="T18" s="419"/>
+      <c r="U18" s="419"/>
+      <c r="V18" s="419"/>
+      <c r="W18" s="419"/>
+      <c r="X18" s="419"/>
+      <c r="Y18" s="419"/>
+    </row>
+    <row r="19" spans="16:25">
+      <c r="P19" s="418">
+        <v>2006</v>
+      </c>
+      <c r="Q19" s="419"/>
+      <c r="R19" s="419"/>
+      <c r="S19" s="419"/>
+      <c r="T19" s="419"/>
+      <c r="U19" s="419"/>
+      <c r="V19" s="419"/>
+      <c r="W19" s="419"/>
+      <c r="X19" s="419"/>
+      <c r="Y19" s="419"/>
+    </row>
+    <row r="20" spans="16:25">
+      <c r="P20" s="418">
+        <v>2007</v>
+      </c>
+      <c r="Q20" s="419"/>
+      <c r="R20" s="419"/>
+      <c r="S20" s="419"/>
+      <c r="T20" s="419"/>
+      <c r="U20" s="419"/>
+      <c r="V20" s="419"/>
+      <c r="W20" s="419"/>
+      <c r="X20" s="419"/>
+      <c r="Y20" s="419"/>
+    </row>
+    <row r="21" spans="16:25">
+      <c r="P21" s="418">
+        <v>2008</v>
+      </c>
+      <c r="Q21" s="419"/>
+      <c r="R21" s="419"/>
+      <c r="S21" s="419"/>
+      <c r="T21" s="419"/>
+      <c r="U21" s="419"/>
+      <c r="V21" s="419"/>
+      <c r="W21" s="419"/>
+      <c r="X21" s="419"/>
+      <c r="Y21" s="419"/>
+    </row>
+    <row r="22" spans="16:25">
+      <c r="P22" s="418">
+        <v>2009</v>
+      </c>
+      <c r="Q22" s="419"/>
+      <c r="R22" s="419"/>
+      <c r="S22" s="419"/>
+      <c r="T22" s="419"/>
+      <c r="U22" s="419"/>
+      <c r="V22" s="419"/>
+      <c r="W22" s="419"/>
+      <c r="X22" s="419"/>
+      <c r="Y22" s="419"/>
+    </row>
+    <row r="23" spans="16:25">
+      <c r="P23" s="418">
+        <v>2010</v>
+      </c>
+      <c r="Q23" s="419"/>
+      <c r="R23" s="419"/>
+      <c r="S23" s="419"/>
+      <c r="T23" s="419"/>
+      <c r="U23" s="419"/>
+      <c r="V23" s="419"/>
+      <c r="W23" s="419"/>
+      <c r="X23" s="419"/>
+      <c r="Y23" s="419"/>
+    </row>
+    <row r="24" spans="16:25">
+      <c r="P24" s="418">
+        <v>2011</v>
+      </c>
+      <c r="Q24" s="419"/>
+      <c r="R24" s="419"/>
+      <c r="S24" s="419"/>
+      <c r="T24" s="419"/>
+      <c r="U24" s="419"/>
+      <c r="V24" s="419"/>
+      <c r="W24" s="419"/>
+      <c r="X24" s="419"/>
+      <c r="Y24" s="419"/>
+    </row>
+    <row r="25" spans="16:25">
+      <c r="P25" s="418">
+        <v>2012</v>
+      </c>
+      <c r="Q25" s="419"/>
+      <c r="R25" s="419"/>
+      <c r="S25" s="419"/>
+      <c r="T25" s="419"/>
+      <c r="U25" s="419"/>
+      <c r="V25" s="419"/>
+      <c r="W25" s="419"/>
+      <c r="X25" s="419"/>
+      <c r="Y25" s="419"/>
+    </row>
+    <row r="26" spans="16:25">
+      <c r="P26" s="418">
+        <v>2013</v>
+      </c>
+      <c r="Q26" s="419"/>
+      <c r="R26" s="419"/>
+      <c r="S26" s="419"/>
+      <c r="T26" s="419"/>
+      <c r="U26" s="419"/>
+      <c r="V26" s="419"/>
+      <c r="W26" s="419"/>
+      <c r="X26" s="419"/>
+      <c r="Y26" s="419"/>
+    </row>
+    <row r="27" spans="16:25">
+      <c r="P27" s="418">
+        <v>2014</v>
+      </c>
+      <c r="Q27" s="419"/>
+      <c r="R27" s="419"/>
+      <c r="S27" s="419"/>
+      <c r="T27" s="419"/>
+      <c r="U27" s="419"/>
+      <c r="V27" s="419"/>
+      <c r="W27" s="419"/>
+      <c r="X27" s="419"/>
+      <c r="Y27" s="419"/>
+    </row>
+    <row r="28" spans="16:25">
+      <c r="P28" s="418">
+        <v>2015</v>
+      </c>
+      <c r="Q28" s="419"/>
+      <c r="R28" s="419"/>
+      <c r="S28" s="419"/>
+      <c r="T28" s="419"/>
+      <c r="U28" s="419"/>
+      <c r="V28" s="419"/>
+      <c r="W28" s="419"/>
+      <c r="X28" s="419"/>
+      <c r="Y28" s="419"/>
+    </row>
+    <row r="29" spans="16:25">
+      <c r="P29" s="418">
+        <v>2016</v>
+      </c>
+      <c r="Q29" s="419"/>
+      <c r="R29" s="419"/>
+      <c r="S29" s="419"/>
+      <c r="T29" s="419"/>
+      <c r="U29" s="419"/>
+      <c r="V29" s="419"/>
+      <c r="W29" s="419"/>
+      <c r="X29" s="419"/>
+      <c r="Y29" s="419"/>
+    </row>
+    <row r="30" spans="16:25">
+      <c r="P30" s="418">
+        <v>2017</v>
+      </c>
+      <c r="Q30" s="419"/>
+      <c r="R30" s="419"/>
+      <c r="S30" s="419"/>
+      <c r="T30" s="419"/>
+      <c r="U30" s="419"/>
+      <c r="V30" s="419"/>
+      <c r="W30" s="419"/>
+      <c r="X30" s="419"/>
+      <c r="Y30" s="419"/>
+    </row>
+    <row r="31" spans="16:25">
+      <c r="P31" s="418">
+        <v>2018</v>
+      </c>
+      <c r="Q31" s="419"/>
+      <c r="R31" s="419"/>
+      <c r="S31" s="419"/>
+      <c r="T31" s="419"/>
+      <c r="U31" s="419"/>
+      <c r="V31" s="419"/>
+      <c r="W31" s="419"/>
+      <c r="X31" s="419"/>
+      <c r="Y31" s="419"/>
+    </row>
+    <row r="32" spans="16:25">
+      <c r="P32" s="418">
+        <v>2019</v>
+      </c>
+      <c r="Q32" s="419"/>
+      <c r="R32" s="419"/>
+      <c r="S32" s="419"/>
+      <c r="T32" s="419"/>
+      <c r="U32" s="419"/>
+      <c r="V32" s="419"/>
+      <c r="W32" s="419"/>
+      <c r="X32" s="419"/>
+      <c r="Y32" s="419"/>
+    </row>
+    <row r="33" spans="16:25">
+      <c r="P33" s="418">
+        <v>2020</v>
+      </c>
+      <c r="Q33" s="419"/>
+      <c r="R33" s="419"/>
+      <c r="S33" s="419"/>
+      <c r="T33" s="419"/>
+      <c r="U33" s="419"/>
+      <c r="V33" s="419"/>
+      <c r="W33" s="419"/>
+      <c r="X33" s="419"/>
+      <c r="Y33" s="419"/>
+    </row>
+    <row r="34" spans="16:25">
+      <c r="P34" s="418">
+        <v>2021</v>
+      </c>
+      <c r="Q34" s="419"/>
+      <c r="R34" s="419"/>
+      <c r="S34" s="419"/>
+      <c r="T34" s="419"/>
+      <c r="U34" s="419"/>
+      <c r="V34" s="419"/>
+      <c r="W34" s="419"/>
+      <c r="X34" s="419"/>
+      <c r="Y34" s="419"/>
+    </row>
+    <row r="35" spans="16:25">
+      <c r="P35" s="418">
+        <v>2022</v>
+      </c>
+      <c r="Q35" s="419"/>
+      <c r="R35" s="419"/>
+      <c r="S35" s="419"/>
+      <c r="T35" s="419"/>
+      <c r="U35" s="419"/>
+      <c r="V35" s="419"/>
+      <c r="W35" s="419"/>
+      <c r="X35" s="419"/>
+      <c r="Y35" s="419"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E629DCA-6F5D-43FC-A242-B121366FCBB1}">
   <dimension ref="A1:N74"/>
@@ -38100,7 +39272,7 @@
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="5" spans="1:8">
-      <c r="A5" s="453" t="s">
+      <c r="A5" s="455" t="s">
         <v>155</v>
       </c>
       <c r="B5" s="46" t="s">
@@ -38117,7 +39289,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A6" s="454"/>
+      <c r="A6" s="456"/>
       <c r="B6" s="135" t="s">
         <v>157</v>
       </c>
@@ -38218,10 +39390,10 @@
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A13" s="455" t="s">
+      <c r="A13" s="457" t="s">
         <v>171</v>
       </c>
-      <c r="B13" s="456"/>
+      <c r="B13" s="458"/>
       <c r="C13" s="75" t="s">
         <v>172</v>
       </c>
@@ -38236,7 +39408,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A14" s="457" t="s">
+      <c r="A14" s="459" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="7">
@@ -38256,7 +39428,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A15" s="458"/>
+      <c r="A15" s="460"/>
       <c r="B15" s="7">
         <v>2007</v>
       </c>
@@ -38274,7 +39446,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A16" s="458"/>
+      <c r="A16" s="460"/>
       <c r="B16" s="7">
         <v>2014</v>
       </c>
@@ -38292,7 +39464,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="459"/>
+      <c r="A17" s="461"/>
       <c r="B17" s="69">
         <v>2021</v>
       </c>
@@ -38310,7 +39482,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="421" t="s">
+      <c r="A18" s="423" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="20">
@@ -38330,7 +39502,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="422"/>
+      <c r="A19" s="424"/>
       <c r="B19" s="20">
         <v>2007</v>
       </c>
@@ -38348,7 +39520,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="422"/>
+      <c r="A20" s="424"/>
       <c r="B20" s="20">
         <v>2014</v>
       </c>
@@ -38366,7 +39538,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="437"/>
+      <c r="A21" s="439"/>
       <c r="B21" s="20">
         <v>2021</v>
       </c>
@@ -38384,7 +39556,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="418" t="s">
+      <c r="A22" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="7">
@@ -38404,7 +39576,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="419"/>
+      <c r="A23" s="421"/>
       <c r="B23" s="7">
         <v>2007</v>
       </c>
@@ -38422,7 +39594,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="419"/>
+      <c r="A24" s="421"/>
       <c r="B24" s="7">
         <v>2014</v>
       </c>
@@ -38440,7 +39612,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="420"/>
+      <c r="A25" s="422"/>
       <c r="B25" s="69">
         <v>2021</v>
       </c>
@@ -38458,7 +39630,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="421" t="s">
+      <c r="A26" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="20">
@@ -38478,7 +39650,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="422"/>
+      <c r="A27" s="424"/>
       <c r="B27" s="20">
         <v>2007</v>
       </c>
@@ -38496,7 +39668,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="422"/>
+      <c r="A28" s="424"/>
       <c r="B28" s="20">
         <v>2014</v>
       </c>
@@ -38514,7 +39686,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="422"/>
+      <c r="A29" s="424"/>
       <c r="B29" s="20">
         <v>2021</v>
       </c>
@@ -38532,7 +39704,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="419" t="s">
+      <c r="A30" s="421" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="7">
@@ -38552,7 +39724,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="419"/>
+      <c r="A31" s="421"/>
       <c r="B31" s="7">
         <v>2007</v>
       </c>
@@ -38570,7 +39742,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="419"/>
+      <c r="A32" s="421"/>
       <c r="B32" s="7">
         <v>2014</v>
       </c>
@@ -38588,7 +39760,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A33" s="420"/>
+      <c r="A33" s="422"/>
       <c r="B33" s="69">
         <v>2021</v>
       </c>
@@ -38606,7 +39778,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="421" t="s">
+      <c r="A34" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="20">
@@ -38626,7 +39798,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A35" s="422"/>
+      <c r="A35" s="424"/>
       <c r="B35" s="20">
         <v>2007</v>
       </c>
@@ -38644,7 +39816,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A36" s="422"/>
+      <c r="A36" s="424"/>
       <c r="B36" s="20">
         <v>2014</v>
       </c>
@@ -38662,7 +39834,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A37" s="437"/>
+      <c r="A37" s="439"/>
       <c r="B37" s="20">
         <v>2021</v>
       </c>
@@ -39336,9 +40508,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A742BE1-6C52-4CDC-94FE-EAFF10A9BF96}">
   <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24">
-      <c r="A1" s="453" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="455" t="s">
         <v>915</v>
       </c>
       <c r="B1" s="44" t="s">
@@ -39358,7 +40541,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A2" s="454"/>
+      <c r="A2" s="456"/>
       <c r="B2" s="178" t="s">
         <v>917</v>
       </c>
@@ -39534,7 +40717,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="13" spans="1:6" ht="21.75" thickBot="1">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1">
       <c r="A13" s="2"/>
       <c r="B13" s="3" t="s">
         <v>192</v>
@@ -39570,7 +40753,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="192.75" thickBot="1">
+    <row r="15" spans="1:6" ht="60.75" thickBot="1">
       <c r="A15" s="40" t="s">
         <v>930</v>
       </c>
@@ -39630,7 +40813,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="72.75" thickBot="1">
+    <row r="18" spans="1:10" ht="60.75" thickBot="1">
       <c r="A18" s="40" t="s">
         <v>937</v>
       </c>
@@ -39825,24 +41008,24 @@
     </row>
     <row r="29" spans="1:10" ht="15.75" thickBot="1"/>
     <row r="30" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A30" s="465"/>
-      <c r="B30" s="467">
+      <c r="A30" s="467"/>
+      <c r="B30" s="469">
         <v>2017</v>
       </c>
-      <c r="C30" s="467">
+      <c r="C30" s="469">
         <v>2018</v>
       </c>
-      <c r="D30" s="469">
+      <c r="D30" s="471">
         <v>2019</v>
       </c>
-      <c r="E30" s="464">
+      <c r="E30" s="466">
         <v>2020</v>
       </c>
-      <c r="F30" s="463"/>
-      <c r="G30" s="461">
+      <c r="F30" s="465"/>
+      <c r="G30" s="463">
         <v>2021</v>
       </c>
-      <c r="H30" s="462"/>
+      <c r="H30" s="464"/>
       <c r="I30" s="11" t="s">
         <v>8</v>
       </c>
@@ -39851,10 +41034,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A31" s="466"/>
-      <c r="B31" s="468"/>
-      <c r="C31" s="468"/>
-      <c r="D31" s="470"/>
+      <c r="A31" s="468"/>
+      <c r="B31" s="470"/>
+      <c r="C31" s="470"/>
+      <c r="D31" s="472"/>
       <c r="E31" s="333" t="s">
         <v>948</v>
       </c>
@@ -40195,18 +41378,18 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" thickBot="1"/>
-    <row r="44" spans="1:10" ht="24.75" thickBot="1">
-      <c r="A44" s="424" t="s">
+    <row r="44" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A44" s="426" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="461" t="s">
+      <c r="B44" s="463" t="s">
         <v>611</v>
       </c>
-      <c r="C44" s="463"/>
+      <c r="C44" s="465"/>
       <c r="D44" s="98" t="s">
         <v>953</v>
       </c>
-      <c r="E44" s="428" t="s">
+      <c r="E44" s="430" t="s">
         <v>928</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -40217,7 +41400,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A45" s="425"/>
+      <c r="A45" s="427"/>
       <c r="B45" s="173" t="s">
         <v>955</v>
       </c>
@@ -40227,7 +41410,7 @@
       <c r="D45" s="135" t="s">
         <v>954</v>
       </c>
-      <c r="E45" s="429"/>
+      <c r="E45" s="431"/>
       <c r="F45" s="54" t="s">
         <v>966</v>
       </c>
@@ -40250,7 +41433,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="409.6" thickBot="1">
+    <row r="47" spans="1:10" ht="72.75" thickBot="1">
       <c r="A47" s="230" t="s">
         <v>2</v>
       </c>
@@ -40271,7 +41454,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="180.75" thickBot="1">
+    <row r="48" spans="1:10" ht="24.75" thickBot="1">
       <c r="A48" s="26" t="s">
         <v>3</v>
       </c>
@@ -40292,7 +41475,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="60.75" thickBot="1">
+    <row r="49" spans="1:7" ht="15.75" thickBot="1">
       <c r="A49" s="40" t="s">
         <v>960</v>
       </c>
@@ -40313,7 +41496,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="409.6" thickBot="1">
+    <row r="50" spans="1:7" ht="72.75" thickBot="1">
       <c r="A50" s="40" t="s">
         <v>296</v>
       </c>
@@ -40334,7 +41517,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="72.75" thickBot="1">
+    <row r="51" spans="1:7" ht="15.75" thickBot="1">
       <c r="A51" s="40" t="s">
         <v>963</v>
       </c>
@@ -40355,7 +41538,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="36.75" thickBot="1">
+    <row r="52" spans="1:7" ht="15.75" thickBot="1">
       <c r="A52" s="42" t="s">
         <v>76</v>
       </c>
@@ -40481,7 +41664,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="48.75" thickBot="1">
+    <row r="61" spans="1:7" ht="24.75" thickBot="1">
       <c r="A61" s="40" t="s">
         <v>48</v>
       </c>
@@ -40498,7 +41681,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="48.75" thickBot="1">
+    <row r="62" spans="1:7" ht="24.75" thickBot="1">
       <c r="A62" s="42" t="s">
         <v>76</v>
       </c>
@@ -40516,11 +41699,11 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" thickBot="1"/>
-    <row r="65" spans="1:6" ht="24">
-      <c r="A65" s="453" t="s">
+    <row r="65" spans="1:6">
+      <c r="A65" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B65" s="426" t="s">
+      <c r="B65" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="46" t="s">
@@ -40536,9 +41719,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A66" s="454"/>
-      <c r="B66" s="427"/>
+    <row r="66" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A66" s="456"/>
+      <c r="B66" s="429"/>
       <c r="C66" s="135" t="s">
         <v>197</v>
       </c>
@@ -40552,8 +41735,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A67" s="418" t="s">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A67" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B67" s="7">
@@ -40573,7 +41756,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A68" s="419"/>
+      <c r="A68" s="421"/>
       <c r="B68" s="7">
         <v>2007</v>
       </c>
@@ -40591,7 +41774,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A69" s="419"/>
+      <c r="A69" s="421"/>
       <c r="B69" s="7">
         <v>2014</v>
       </c>
@@ -40609,7 +41792,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A70" s="420"/>
+      <c r="A70" s="422"/>
       <c r="B70" s="69">
         <v>2021</v>
       </c>
@@ -40626,8 +41809,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A71" s="421" t="s">
+    <row r="71" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A71" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B71" s="20">
@@ -40647,7 +41830,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A72" s="422"/>
+      <c r="A72" s="424"/>
       <c r="B72" s="20">
         <v>2007</v>
       </c>
@@ -40665,7 +41848,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A73" s="422"/>
+      <c r="A73" s="424"/>
       <c r="B73" s="20">
         <v>2014</v>
       </c>
@@ -40683,7 +41866,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A74" s="437"/>
+      <c r="A74" s="439"/>
       <c r="B74" s="20">
         <v>2021</v>
       </c>
@@ -40700,8 +41883,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A75" s="447" t="s">
+    <row r="75" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A75" s="449" t="s">
         <v>18</v>
       </c>
       <c r="B75" s="7">
@@ -40721,7 +41904,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A76" s="448"/>
+      <c r="A76" s="450"/>
       <c r="B76" s="7">
         <v>2007</v>
       </c>
@@ -40739,7 +41922,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A77" s="448"/>
+      <c r="A77" s="450"/>
       <c r="B77" s="7">
         <v>2014</v>
       </c>
@@ -40757,7 +41940,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A78" s="460"/>
+      <c r="A78" s="462"/>
       <c r="B78" s="69">
         <v>2021</v>
       </c>
@@ -40774,8 +41957,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A79" s="421" t="s">
+    <row r="79" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A79" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="20">
@@ -40795,7 +41978,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A80" s="422"/>
+      <c r="A80" s="424"/>
       <c r="B80" s="20">
         <v>2007</v>
       </c>
@@ -40813,7 +41996,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A81" s="422"/>
+      <c r="A81" s="424"/>
       <c r="B81" s="20">
         <v>2014</v>
       </c>
@@ -40831,7 +42014,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A82" s="437"/>
+      <c r="A82" s="439"/>
       <c r="B82" s="20">
         <v>2021</v>
       </c>
@@ -40848,8 +42031,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A83" s="418" t="s">
+    <row r="83" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A83" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="7">
@@ -40869,7 +42052,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A84" s="419"/>
+      <c r="A84" s="421"/>
       <c r="B84" s="7">
         <v>2007</v>
       </c>
@@ -40887,7 +42070,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A85" s="419"/>
+      <c r="A85" s="421"/>
       <c r="B85" s="7">
         <v>2014</v>
       </c>
@@ -40905,7 +42088,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A86" s="420"/>
+      <c r="A86" s="422"/>
       <c r="B86" s="69">
         <v>2021</v>
       </c>
@@ -40922,8 +42105,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A87" s="421" t="s">
+    <row r="87" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A87" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B87" s="20">
@@ -40943,12 +42126,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A88" s="422"/>
+      <c r="A88" s="424"/>
       <c r="B88" s="20">
         <v>2007</v>
       </c>
-      <c r="C88" s="20">
-        <v>56</v>
+      <c r="C88" s="20" t="s">
+        <v>1340</v>
       </c>
       <c r="D88" s="111">
         <v>10762600000</v>
@@ -40960,8 +42143,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A89" s="422"/>
+    <row r="89" spans="1:6" ht="24.75" thickBot="1">
+      <c r="A89" s="424"/>
       <c r="B89" s="20">
         <v>2014</v>
       </c>
@@ -40978,8 +42161,8 @@
         <v>975</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A90" s="423"/>
+    <row r="90" spans="1:6" ht="24.75" thickBot="1">
+      <c r="A90" s="425"/>
       <c r="B90" s="24">
         <v>2021</v>
       </c>
@@ -40997,14 +42180,14 @@
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="93" spans="1:6" ht="48">
-      <c r="A93" s="453" t="s">
+    <row r="93" spans="1:6" ht="24">
+      <c r="A93" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B93" s="98" t="s">
         <v>285</v>
       </c>
-      <c r="C93" s="426" t="s">
+      <c r="C93" s="428" t="s">
         <v>44</v>
       </c>
       <c r="D93" s="47" t="s">
@@ -41018,11 +42201,11 @@
       </c>
     </row>
     <row r="94" spans="1:6" ht="18.75" thickBot="1">
-      <c r="A94" s="454"/>
+      <c r="A94" s="456"/>
       <c r="B94" s="135" t="s">
         <v>976</v>
       </c>
-      <c r="C94" s="427"/>
+      <c r="C94" s="429"/>
       <c r="D94" s="136" t="s">
         <v>921</v>
       </c>
@@ -41374,7 +42557,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" thickBot="1"/>
-    <row r="118" spans="1:5" ht="30.75" thickBot="1">
+    <row r="118" spans="1:5" ht="21.75" thickBot="1">
       <c r="A118" s="82"/>
       <c r="B118" s="3" t="s">
         <v>192</v>
@@ -41475,7 +42658,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" thickBot="1"/>
-    <row r="126" spans="1:5" ht="60.75" thickBot="1">
+    <row r="126" spans="1:5" ht="36.75" thickBot="1">
       <c r="A126" s="71" t="s">
         <v>992</v>
       </c>
@@ -41492,7 +42675,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="96.75" thickBot="1">
+    <row r="127" spans="1:5" ht="48.75" thickBot="1">
       <c r="A127" s="40" t="s">
         <v>16</v>
       </c>
@@ -41524,7 +42707,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="120.75" thickBot="1">
+    <row r="129" spans="1:5" ht="48.75" thickBot="1">
       <c r="A129" s="40" t="s">
         <v>18</v>
       </c>
@@ -41556,7 +42739,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="60.75" thickBot="1">
+    <row r="131" spans="1:5" ht="24.75" thickBot="1">
       <c r="A131" s="40" t="s">
         <v>48</v>
       </c>
@@ -42175,7 +43358,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A26" s="418" t="s">
+      <c r="A26" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="69">
@@ -42195,7 +43378,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A27" s="419"/>
+      <c r="A27" s="421"/>
       <c r="B27" s="69">
         <v>2007</v>
       </c>
@@ -42213,7 +43396,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A28" s="419"/>
+      <c r="A28" s="421"/>
       <c r="B28" s="69">
         <v>2014</v>
       </c>
@@ -42231,7 +43414,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A29" s="420"/>
+      <c r="A29" s="422"/>
       <c r="B29" s="69">
         <v>2021</v>
       </c>
@@ -42249,7 +43432,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A30" s="421" t="s">
+      <c r="A30" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="20">
@@ -42269,7 +43452,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A31" s="422"/>
+      <c r="A31" s="424"/>
       <c r="B31" s="20">
         <v>2007</v>
       </c>
@@ -42287,7 +43470,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A32" s="422"/>
+      <c r="A32" s="424"/>
       <c r="B32" s="20">
         <v>2014</v>
       </c>
@@ -42305,7 +43488,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="437"/>
+      <c r="A33" s="439"/>
       <c r="B33" s="20">
         <v>2021</v>
       </c>
@@ -42323,7 +43506,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="418" t="s">
+      <c r="A34" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B34" s="69">
@@ -42343,7 +43526,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="419"/>
+      <c r="A35" s="421"/>
       <c r="B35" s="69">
         <v>2007</v>
       </c>
@@ -42361,7 +43544,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="419"/>
+      <c r="A36" s="421"/>
       <c r="B36" s="69">
         <v>2014</v>
       </c>
@@ -42379,7 +43562,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="420"/>
+      <c r="A37" s="422"/>
       <c r="B37" s="69">
         <v>2021</v>
       </c>
@@ -42397,7 +43580,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="421" t="s">
+      <c r="A38" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="20">
@@ -42417,7 +43600,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="422"/>
+      <c r="A39" s="424"/>
       <c r="B39" s="20">
         <v>2007</v>
       </c>
@@ -42435,7 +43618,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="422"/>
+      <c r="A40" s="424"/>
       <c r="B40" s="20">
         <v>2014</v>
       </c>
@@ -42453,7 +43636,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="423"/>
+      <c r="A41" s="425"/>
       <c r="B41" s="24">
         <v>2021</v>
       </c>
@@ -42471,7 +43654,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="475" t="s">
+      <c r="A42" s="477" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="69">
@@ -42491,7 +43674,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="419"/>
+      <c r="A43" s="421"/>
       <c r="B43" s="69">
         <v>2007</v>
       </c>
@@ -42509,7 +43692,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="419"/>
+      <c r="A44" s="421"/>
       <c r="B44" s="69">
         <v>2014</v>
       </c>
@@ -42527,7 +43710,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="420"/>
+      <c r="A45" s="422"/>
       <c r="B45" s="69">
         <v>2021</v>
       </c>
@@ -42545,7 +43728,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="421" t="s">
+      <c r="A46" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="20">
@@ -42565,7 +43748,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="422"/>
+      <c r="A47" s="424"/>
       <c r="B47" s="20">
         <v>2007</v>
       </c>
@@ -42583,7 +43766,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="422"/>
+      <c r="A48" s="424"/>
       <c r="B48" s="20">
         <v>2014</v>
       </c>
@@ -42601,7 +43784,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A49" s="423"/>
+      <c r="A49" s="425"/>
       <c r="B49" s="24">
         <v>2021</v>
       </c>
@@ -42877,7 +44060,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A65" s="471" t="s">
+      <c r="A65" s="473" t="s">
         <v>138</v>
       </c>
       <c r="B65" s="104" t="s">
@@ -42906,7 +44089,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A66" s="472"/>
+      <c r="A66" s="474"/>
       <c r="B66" s="104" t="s">
         <v>140</v>
       </c>
@@ -42933,7 +44116,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A67" s="473" t="s">
+      <c r="A67" s="475" t="s">
         <v>141</v>
       </c>
       <c r="B67" s="107" t="s">
@@ -42962,7 +44145,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A68" s="459"/>
+      <c r="A68" s="461"/>
       <c r="B68" s="107" t="s">
         <v>140</v>
       </c>
@@ -42989,7 +44172,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A69" s="471" t="s">
+      <c r="A69" s="473" t="s">
         <v>142</v>
       </c>
       <c r="B69" s="104" t="s">
@@ -43018,7 +44201,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A70" s="472"/>
+      <c r="A70" s="474"/>
       <c r="B70" s="104" t="s">
         <v>140</v>
       </c>
@@ -43045,7 +44228,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A71" s="473" t="s">
+      <c r="A71" s="475" t="s">
         <v>143</v>
       </c>
       <c r="B71" s="101" t="s">
@@ -43074,7 +44257,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A72" s="459"/>
+      <c r="A72" s="461"/>
       <c r="B72" s="107" t="s">
         <v>140</v>
       </c>
@@ -43101,7 +44284,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A73" s="471" t="s">
+      <c r="A73" s="473" t="s">
         <v>144</v>
       </c>
       <c r="B73" s="104" t="s">
@@ -43130,7 +44313,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A74" s="472"/>
+      <c r="A74" s="474"/>
       <c r="B74" s="104" t="s">
         <v>140</v>
       </c>
@@ -43157,7 +44340,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A75" s="473" t="s">
+      <c r="A75" s="475" t="s">
         <v>145</v>
       </c>
       <c r="B75" s="101" t="s">
@@ -43186,7 +44369,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A76" s="459"/>
+      <c r="A76" s="461"/>
       <c r="B76" s="107" t="s">
         <v>140</v>
       </c>
@@ -43213,7 +44396,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A77" s="471" t="s">
+      <c r="A77" s="473" t="s">
         <v>146</v>
       </c>
       <c r="B77" s="104" t="s">
@@ -43242,7 +44425,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A78" s="472"/>
+      <c r="A78" s="474"/>
       <c r="B78" s="104" t="s">
         <v>140</v>
       </c>
@@ -43269,7 +44452,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A79" s="473" t="s">
+      <c r="A79" s="475" t="s">
         <v>147</v>
       </c>
       <c r="B79" s="101" t="s">
@@ -43298,7 +44481,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A80" s="459"/>
+      <c r="A80" s="461"/>
       <c r="B80" s="107" t="s">
         <v>140</v>
       </c>
@@ -43325,7 +44508,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="44.25" customHeight="1" thickBot="1">
-      <c r="A81" s="471" t="s">
+      <c r="A81" s="473" t="s">
         <v>148</v>
       </c>
       <c r="B81" s="104" t="s">
@@ -43354,7 +44537,7 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A82" s="474"/>
+      <c r="A82" s="476"/>
       <c r="B82" s="128" t="s">
         <v>140</v>
       </c>
@@ -43408,11 +44591,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="36">
-      <c r="A1" s="465"/>
+      <c r="A1" s="467"/>
       <c r="B1" s="44" t="s">
         <v>1000</v>
       </c>
-      <c r="C1" s="478" t="s">
+      <c r="C1" s="480" t="s">
         <v>1002</v>
       </c>
       <c r="D1" s="337" t="s">
@@ -43426,11 +44609,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A2" s="477"/>
+      <c r="A2" s="479"/>
       <c r="B2" s="178" t="s">
         <v>1001</v>
       </c>
-      <c r="C2" s="479"/>
+      <c r="C2" s="481"/>
       <c r="D2" s="136" t="s">
         <v>287</v>
       </c>
@@ -43838,7 +45021,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="418" t="s">
+      <c r="A31" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="7">
@@ -43858,7 +45041,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="419"/>
+      <c r="A32" s="421"/>
       <c r="B32" s="7">
         <v>2007</v>
       </c>
@@ -43876,7 +45059,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="419"/>
+      <c r="A33" s="421"/>
       <c r="B33" s="7">
         <v>2014</v>
       </c>
@@ -43894,7 +45077,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="420"/>
+      <c r="A34" s="422"/>
       <c r="B34" s="69">
         <v>2021</v>
       </c>
@@ -43912,7 +45095,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="480" t="s">
+      <c r="A35" s="482" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="20">
@@ -43932,7 +45115,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="481"/>
+      <c r="A36" s="483"/>
       <c r="B36" s="20">
         <v>2007</v>
       </c>
@@ -43950,7 +45133,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="481"/>
+      <c r="A37" s="483"/>
       <c r="B37" s="20">
         <v>2014</v>
       </c>
@@ -43968,7 +45151,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="482"/>
+      <c r="A38" s="484"/>
       <c r="B38" s="20">
         <v>2021</v>
       </c>
@@ -43986,7 +45169,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="418" t="s">
+      <c r="A39" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="7">
@@ -44006,7 +45189,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="419"/>
+      <c r="A40" s="421"/>
       <c r="B40" s="7">
         <v>2007</v>
       </c>
@@ -44024,7 +45207,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="419"/>
+      <c r="A41" s="421"/>
       <c r="B41" s="7">
         <v>2014</v>
       </c>
@@ -44042,7 +45225,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="420"/>
+      <c r="A42" s="422"/>
       <c r="B42" s="69">
         <v>2021</v>
       </c>
@@ -44060,7 +45243,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="480" t="s">
+      <c r="A43" s="482" t="s">
         <v>19</v>
       </c>
       <c r="B43" s="20">
@@ -44080,7 +45263,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="481"/>
+      <c r="A44" s="483"/>
       <c r="B44" s="20">
         <v>2007</v>
       </c>
@@ -44098,7 +45281,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="481"/>
+      <c r="A45" s="483"/>
       <c r="B45" s="20">
         <v>2014</v>
       </c>
@@ -44116,7 +45299,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="482"/>
+      <c r="A46" s="484"/>
       <c r="B46" s="20">
         <v>2021</v>
       </c>
@@ -44134,7 +45317,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="418" t="s">
+      <c r="A47" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B47" s="7">
@@ -44154,7 +45337,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="419"/>
+      <c r="A48" s="421"/>
       <c r="B48" s="7">
         <v>2007</v>
       </c>
@@ -44172,7 +45355,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="419"/>
+      <c r="A49" s="421"/>
       <c r="B49" s="7">
         <v>2014</v>
       </c>
@@ -44190,7 +45373,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="420"/>
+      <c r="A50" s="422"/>
       <c r="B50" s="69">
         <v>2021</v>
       </c>
@@ -44208,7 +45391,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="421" t="s">
+      <c r="A51" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="20">
@@ -44228,7 +45411,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="422"/>
+      <c r="A52" s="424"/>
       <c r="B52" s="20">
         <v>2007</v>
       </c>
@@ -44246,7 +45429,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="422"/>
+      <c r="A53" s="424"/>
       <c r="B53" s="20">
         <v>2014</v>
       </c>
@@ -44264,7 +45447,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="423"/>
+      <c r="A54" s="425"/>
       <c r="B54" s="24">
         <v>2021</v>
       </c>
@@ -44283,13 +45466,13 @@
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="57" spans="1:6" ht="48">
-      <c r="A57" s="424" t="s">
+      <c r="A57" s="426" t="s">
         <v>12</v>
       </c>
       <c r="B57" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="445" t="s">
+      <c r="C57" s="447" t="s">
         <v>44</v>
       </c>
       <c r="D57" s="47" t="s">
@@ -44303,11 +45486,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="18.75" thickBot="1">
-      <c r="A58" s="425"/>
+      <c r="A58" s="427"/>
       <c r="B58" s="178" t="s">
         <v>1013</v>
       </c>
-      <c r="C58" s="476"/>
+      <c r="C58" s="478"/>
       <c r="D58" s="136" t="s">
         <v>1015</v>
       </c>
@@ -44856,16 +46039,16 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="22" spans="1:6">
-      <c r="A22" s="453" t="s">
+      <c r="A22" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="426" t="s">
+      <c r="B22" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D22" s="428" t="s">
+      <c r="D22" s="430" t="s">
         <v>198</v>
       </c>
       <c r="E22" s="11" t="s">
@@ -44876,12 +46059,12 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A23" s="454"/>
-      <c r="B23" s="427"/>
+      <c r="A23" s="456"/>
+      <c r="B23" s="429"/>
       <c r="C23" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="429"/>
+      <c r="D23" s="431"/>
       <c r="E23" s="30" t="s">
         <v>26</v>
       </c>
@@ -44966,7 +46149,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="421" t="s">
+      <c r="A28" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="20">
@@ -44986,7 +46169,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="422"/>
+      <c r="A29" s="424"/>
       <c r="B29" s="20">
         <v>2007</v>
       </c>
@@ -45004,7 +46187,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="422"/>
+      <c r="A30" s="424"/>
       <c r="B30" s="20">
         <v>2014</v>
       </c>
@@ -45022,7 +46205,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="437"/>
+      <c r="A31" s="439"/>
       <c r="B31" s="20">
         <v>2021</v>
       </c>
@@ -45040,7 +46223,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="418" t="s">
+      <c r="A32" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B32" s="7">
@@ -45060,7 +46243,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="419"/>
+      <c r="A33" s="421"/>
       <c r="B33" s="7">
         <v>2007</v>
       </c>
@@ -45078,7 +46261,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="419"/>
+      <c r="A34" s="421"/>
       <c r="B34" s="7">
         <v>2014</v>
       </c>
@@ -45096,7 +46279,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="420"/>
+      <c r="A35" s="422"/>
       <c r="B35" s="69">
         <v>2021</v>
       </c>
@@ -45114,7 +46297,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="421" t="s">
+      <c r="A36" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B36" s="20">
@@ -45134,7 +46317,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="422"/>
+      <c r="A37" s="424"/>
       <c r="B37" s="20">
         <v>2007</v>
       </c>
@@ -45152,7 +46335,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="422"/>
+      <c r="A38" s="424"/>
       <c r="B38" s="20">
         <v>2014</v>
       </c>
@@ -45170,7 +46353,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="437"/>
+      <c r="A39" s="439"/>
       <c r="B39" s="20">
         <v>2021</v>
       </c>
@@ -45188,7 +46371,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="418" t="s">
+      <c r="A40" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B40" s="7">
@@ -45208,7 +46391,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="419"/>
+      <c r="A41" s="421"/>
       <c r="B41" s="7">
         <v>2007</v>
       </c>
@@ -45226,7 +46409,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="419"/>
+      <c r="A42" s="421"/>
       <c r="B42" s="7">
         <v>2014</v>
       </c>
@@ -45244,7 +46427,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="419"/>
+      <c r="A43" s="421"/>
       <c r="B43" s="7">
         <v>2016</v>
       </c>
@@ -45262,7 +46445,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="420"/>
+      <c r="A44" s="422"/>
       <c r="B44" s="69">
         <v>2021</v>
       </c>
@@ -45280,7 +46463,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="421" t="s">
+      <c r="A45" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="20">
@@ -45300,7 +46483,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A46" s="422"/>
+      <c r="A46" s="424"/>
       <c r="B46" s="20">
         <v>2007</v>
       </c>
@@ -45318,7 +46501,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A47" s="422"/>
+      <c r="A47" s="424"/>
       <c r="B47" s="20">
         <v>2014</v>
       </c>
@@ -45336,7 +46519,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="423"/>
+      <c r="A48" s="425"/>
       <c r="B48" s="24">
         <v>2021</v>
       </c>
@@ -46997,16 +48180,16 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="24" spans="1:6">
-      <c r="A24" s="453" t="s">
+      <c r="A24" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="426" t="s">
+      <c r="B24" s="428" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D24" s="428" t="s">
+      <c r="D24" s="430" t="s">
         <v>274</v>
       </c>
       <c r="E24" s="11" t="s">
@@ -47017,12 +48200,12 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A25" s="454"/>
-      <c r="B25" s="427"/>
+      <c r="A25" s="456"/>
+      <c r="B25" s="429"/>
       <c r="C25" s="152" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="429"/>
+      <c r="D25" s="431"/>
       <c r="E25" s="30" t="s">
         <v>26</v>
       </c>
@@ -47031,7 +48214,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="486" t="s">
+      <c r="A26" s="488" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="7">
@@ -47051,7 +48234,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="487"/>
+      <c r="A27" s="489"/>
       <c r="B27" s="7">
         <v>2007</v>
       </c>
@@ -47069,7 +48252,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="487"/>
+      <c r="A28" s="489"/>
       <c r="B28" s="7">
         <v>2014</v>
       </c>
@@ -47087,7 +48270,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="488"/>
+      <c r="A29" s="490"/>
       <c r="B29" s="69">
         <v>2021</v>
       </c>
@@ -47105,7 +48288,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="489" t="s">
+      <c r="A30" s="491" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="20">
@@ -47125,7 +48308,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="490"/>
+      <c r="A31" s="492"/>
       <c r="B31" s="20">
         <v>2007</v>
       </c>
@@ -47143,7 +48326,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="490"/>
+      <c r="A32" s="492"/>
       <c r="B32" s="20">
         <v>2014</v>
       </c>
@@ -47161,7 +48344,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="491"/>
+      <c r="A33" s="493"/>
       <c r="B33" s="20">
         <v>2021</v>
       </c>
@@ -47179,7 +48362,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="492" t="s">
+      <c r="A34" s="494" t="s">
         <v>18</v>
       </c>
       <c r="B34" s="7">
@@ -47199,7 +48382,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="493"/>
+      <c r="A35" s="495"/>
       <c r="B35" s="7">
         <v>2007</v>
       </c>
@@ -47217,7 +48400,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="493"/>
+      <c r="A36" s="495"/>
       <c r="B36" s="7">
         <v>2014</v>
       </c>
@@ -47235,7 +48418,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="494"/>
+      <c r="A37" s="496"/>
       <c r="B37" s="69">
         <v>2021</v>
       </c>
@@ -47253,7 +48436,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="489" t="s">
+      <c r="A38" s="491" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="20">
@@ -47273,7 +48456,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="490"/>
+      <c r="A39" s="492"/>
       <c r="B39" s="20">
         <v>2007</v>
       </c>
@@ -47291,7 +48474,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="490"/>
+      <c r="A40" s="492"/>
       <c r="B40" s="20">
         <v>2014</v>
       </c>
@@ -47309,7 +48492,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="491"/>
+      <c r="A41" s="493"/>
       <c r="B41" s="20">
         <v>2021</v>
       </c>
@@ -47327,7 +48510,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="496" t="s">
+      <c r="A42" s="498" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="153">
@@ -47347,7 +48530,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="497"/>
+      <c r="A43" s="499"/>
       <c r="B43" s="153">
         <v>2007</v>
       </c>
@@ -47365,7 +48548,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="497"/>
+      <c r="A44" s="499"/>
       <c r="B44" s="153">
         <v>2014</v>
       </c>
@@ -47383,7 +48566,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="498"/>
+      <c r="A45" s="500"/>
       <c r="B45" s="155">
         <v>2021</v>
       </c>
@@ -47576,13 +48759,13 @@
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="56" spans="1:8" ht="24">
-      <c r="A56" s="453" t="s">
+      <c r="A56" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B56" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="C56" s="499" t="s">
+      <c r="C56" s="501" t="s">
         <v>44</v>
       </c>
       <c r="D56" s="47" t="s">
@@ -47596,11 +48779,11 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="18.75" thickBot="1">
-      <c r="A57" s="454"/>
+      <c r="A57" s="456"/>
       <c r="B57" s="135" t="s">
         <v>286</v>
       </c>
-      <c r="C57" s="500"/>
+      <c r="C57" s="502"/>
       <c r="D57" s="136" t="s">
         <v>287</v>
       </c>
@@ -47836,22 +49019,22 @@
     </row>
     <row r="71" spans="1:10" ht="15.75" thickBot="1"/>
     <row r="72" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A72" s="495" t="s">
+      <c r="A72" s="497" t="s">
         <v>294</v>
       </c>
-      <c r="B72" s="484"/>
-      <c r="C72" s="483" t="s">
+      <c r="B72" s="486"/>
+      <c r="C72" s="485" t="s">
         <v>295</v>
       </c>
-      <c r="D72" s="484"/>
-      <c r="E72" s="483" t="s">
+      <c r="D72" s="486"/>
+      <c r="E72" s="485" t="s">
         <v>296</v>
       </c>
-      <c r="F72" s="484"/>
-      <c r="G72" s="483" t="s">
+      <c r="F72" s="486"/>
+      <c r="G72" s="485" t="s">
         <v>297</v>
       </c>
-      <c r="H72" s="485"/>
+      <c r="H72" s="487"/>
       <c r="I72" s="11" t="s">
         <v>8</v>
       </c>
@@ -48380,6 +49563,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FBBC0CE-D650-4544-AD96-5FEDEB51DACA}">
   <dimension ref="A1:L108"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" thickBot="1">
       <c r="A1" s="2"/>
@@ -48710,22 +49907,22 @@
     </row>
     <row r="17" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="18" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A18" s="465"/>
-      <c r="B18" s="467" t="s">
+      <c r="A18" s="467"/>
+      <c r="B18" s="469" t="s">
         <v>343</v>
       </c>
-      <c r="C18" s="499" t="s">
+      <c r="C18" s="501" t="s">
         <v>344</v>
       </c>
-      <c r="D18" s="464" t="s">
+      <c r="D18" s="466" t="s">
         <v>345</v>
       </c>
-      <c r="E18" s="463"/>
+      <c r="E18" s="465"/>
       <c r="F18" s="171"/>
-      <c r="G18" s="501" t="s">
+      <c r="G18" s="503" t="s">
         <v>346</v>
       </c>
-      <c r="H18" s="501"/>
+      <c r="H18" s="503"/>
       <c r="I18" s="171"/>
       <c r="J18" s="172"/>
       <c r="K18" s="11" t="s">
@@ -48736,9 +49933,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A19" s="477"/>
-      <c r="B19" s="502"/>
-      <c r="C19" s="500"/>
+      <c r="A19" s="479"/>
+      <c r="B19" s="504"/>
+      <c r="C19" s="502"/>
       <c r="D19" s="36" t="s">
         <v>347</v>
       </c>
@@ -49217,7 +50414,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="418" t="s">
+      <c r="A45" s="420" t="s">
         <v>16</v>
       </c>
       <c r="B45" s="7">
@@ -49237,7 +50434,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="419"/>
+      <c r="A46" s="421"/>
       <c r="B46" s="7">
         <v>2007</v>
       </c>
@@ -49255,7 +50452,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="419"/>
+      <c r="A47" s="421"/>
       <c r="B47" s="7">
         <v>2014</v>
       </c>
@@ -49273,7 +50470,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="420"/>
+      <c r="A48" s="422"/>
       <c r="B48" s="69">
         <v>2021</v>
       </c>
@@ -49291,7 +50488,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="421" t="s">
+      <c r="A49" s="423" t="s">
         <v>17</v>
       </c>
       <c r="B49" s="20">
@@ -49311,7 +50508,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="422"/>
+      <c r="A50" s="424"/>
       <c r="B50" s="20">
         <v>2007</v>
       </c>
@@ -49329,7 +50526,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="422"/>
+      <c r="A51" s="424"/>
       <c r="B51" s="20">
         <v>2014</v>
       </c>
@@ -49347,7 +50544,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="437"/>
+      <c r="A52" s="439"/>
       <c r="B52" s="20">
         <v>2021</v>
       </c>
@@ -49365,7 +50562,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="418" t="s">
+      <c r="A53" s="420" t="s">
         <v>18</v>
       </c>
       <c r="B53" s="7">
@@ -49385,7 +50582,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="419"/>
+      <c r="A54" s="421"/>
       <c r="B54" s="7">
         <v>2007</v>
       </c>
@@ -49403,7 +50600,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="419"/>
+      <c r="A55" s="421"/>
       <c r="B55" s="7">
         <v>2014</v>
       </c>
@@ -49421,7 +50618,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="420"/>
+      <c r="A56" s="422"/>
       <c r="B56" s="69">
         <v>2021</v>
       </c>
@@ -49439,7 +50636,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="421" t="s">
+      <c r="A57" s="423" t="s">
         <v>19</v>
       </c>
       <c r="B57" s="20">
@@ -49459,7 +50656,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="422"/>
+      <c r="A58" s="424"/>
       <c r="B58" s="20">
         <v>2007</v>
       </c>
@@ -49477,7 +50674,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="422"/>
+      <c r="A59" s="424"/>
       <c r="B59" s="20">
         <v>2014</v>
       </c>
@@ -49495,7 +50692,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="437"/>
+      <c r="A60" s="439"/>
       <c r="B60" s="20">
         <v>2021</v>
       </c>
@@ -49513,7 +50710,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="418" t="s">
+      <c r="A61" s="420" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="7">
@@ -49533,7 +50730,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="419"/>
+      <c r="A62" s="421"/>
       <c r="B62" s="7">
         <v>2007</v>
       </c>
@@ -49551,7 +50748,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="419"/>
+      <c r="A63" s="421"/>
       <c r="B63" s="7">
         <v>2014</v>
       </c>
@@ -49569,7 +50766,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="420"/>
+      <c r="A64" s="422"/>
       <c r="B64" s="69">
         <v>2021</v>
       </c>
@@ -49587,7 +50784,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A65" s="421" t="s">
+      <c r="A65" s="423" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="20">
@@ -49607,12 +50804,12 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A66" s="422"/>
+      <c r="A66" s="424"/>
       <c r="B66" s="20">
         <v>2007</v>
       </c>
-      <c r="C66" s="20">
-        <v>8</v>
+      <c r="C66" s="20" t="s">
+        <v>1354</v>
       </c>
       <c r="D66" s="21">
         <v>18000</v>
@@ -49625,12 +50822,12 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A67" s="422"/>
+      <c r="A67" s="424"/>
       <c r="B67" s="20">
         <v>2014</v>
       </c>
-      <c r="C67" s="20">
-        <v>0.1</v>
+      <c r="C67" s="20" t="s">
+        <v>1353</v>
       </c>
       <c r="D67" s="21">
         <v>1000</v>
@@ -49643,12 +50840,12 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A68" s="423"/>
+      <c r="A68" s="425"/>
       <c r="B68" s="24">
         <v>2021</v>
       </c>
-      <c r="C68" s="24">
-        <v>0</v>
+      <c r="C68" s="24" t="s">
+        <v>1355</v>
       </c>
       <c r="D68" s="177">
         <v>0</v>
@@ -49765,16 +50962,16 @@
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="77" spans="1:8" ht="48">
-      <c r="A77" s="453" t="s">
+      <c r="A77" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B77" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="C77" s="445" t="s">
+      <c r="C77" s="447" t="s">
         <v>44</v>
       </c>
-      <c r="D77" s="428" t="s">
+      <c r="D77" s="430" t="s">
         <v>216</v>
       </c>
       <c r="E77" s="11" t="s">
@@ -49785,12 +50982,12 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="18.75" thickBot="1">
-      <c r="A78" s="454"/>
+      <c r="A78" s="456"/>
       <c r="B78" s="178" t="s">
         <v>361</v>
       </c>
-      <c r="C78" s="476"/>
-      <c r="D78" s="429"/>
+      <c r="C78" s="478"/>
+      <c r="D78" s="431"/>
       <c r="E78" s="30" t="s">
         <v>51</v>
       </c>

--- a/Data_Raw/Manually_Collected_Data_Version2.xlsx
+++ b/Data_Raw/Manually_Collected_Data_Version2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\From BigDisk\GIT\Benefish_Data_Collection\Data_Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62CAFA2-176A-4AEE-AFAD-4387F3637DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AAAB93-E8C1-42D8-A888-ED1C8702D42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="913" firstSheet="8" activeTab="8" xr2:uid="{DADAB8C2-813A-4B64-AE11-C65CAFCECFBF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="913" firstSheet="4" activeTab="17" xr2:uid="{DADAB8C2-813A-4B64-AE11-C65CAFCECFBF}"/>
   </bookViews>
   <sheets>
     <sheet name="American_Samoa" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5968" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5967" uniqueCount="1356">
   <si>
     <t>Live fish</t>
   </si>
@@ -7894,6 +7894,27 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7909,6 +7930,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7930,28 +7954,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="11"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7966,9 +7987,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7981,24 +7999,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8020,38 +8020,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8059,15 +8065,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8149,6 +8149,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8176,12 +8182,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
@@ -8194,6 +8194,18 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8215,24 +8227,27 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8245,21 +8260,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8275,6 +8275,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8305,12 +8311,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
@@ -8326,39 +8326,63 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -8370,30 +8394,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9047,20 +9047,20 @@
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1"/>
     <row r="18" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A18" s="435" t="s">
+      <c r="A18" s="423" t="s">
         <v>887</v>
       </c>
-      <c r="B18" s="436"/>
-      <c r="C18" s="436"/>
-      <c r="D18" s="436"/>
-      <c r="E18" s="436"/>
-      <c r="F18" s="437"/>
+      <c r="B18" s="424"/>
+      <c r="C18" s="424"/>
+      <c r="D18" s="424"/>
+      <c r="E18" s="424"/>
+      <c r="F18" s="425"/>
       <c r="G18" s="252"/>
-      <c r="H18" s="438" t="s">
+      <c r="H18" s="426" t="s">
         <v>888</v>
       </c>
-      <c r="I18" s="438"/>
-      <c r="J18" s="438"/>
+      <c r="I18" s="426"/>
+      <c r="J18" s="426"/>
       <c r="K18" s="328"/>
       <c r="L18" s="11" t="s">
         <v>8</v>
@@ -9585,7 +9585,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="420" t="s">
+      <c r="A41" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B41" s="7">
@@ -9605,7 +9605,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="421"/>
+      <c r="A42" s="428"/>
       <c r="B42" s="7">
         <v>2007</v>
       </c>
@@ -9623,7 +9623,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="421"/>
+      <c r="A43" s="428"/>
       <c r="B43" s="7">
         <v>2014</v>
       </c>
@@ -9641,7 +9641,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="422"/>
+      <c r="A44" s="429"/>
       <c r="B44" s="69">
         <v>2021</v>
       </c>
@@ -9659,7 +9659,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="423" t="s">
+      <c r="A45" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B45" s="20">
@@ -9679,7 +9679,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="424"/>
+      <c r="A46" s="431"/>
       <c r="B46" s="20">
         <v>2007</v>
       </c>
@@ -9697,7 +9697,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="424"/>
+      <c r="A47" s="431"/>
       <c r="B47" s="20">
         <v>2014</v>
       </c>
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="439"/>
+      <c r="A48" s="432"/>
       <c r="B48" s="20">
         <v>2021</v>
       </c>
@@ -9733,7 +9733,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="420" t="s">
+      <c r="A49" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B49" s="7">
@@ -9753,7 +9753,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="421"/>
+      <c r="A50" s="428"/>
       <c r="B50" s="7">
         <v>2007</v>
       </c>
@@ -9771,7 +9771,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="421"/>
+      <c r="A51" s="428"/>
       <c r="B51" s="7">
         <v>2014</v>
       </c>
@@ -9789,7 +9789,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="422"/>
+      <c r="A52" s="429"/>
       <c r="B52" s="69">
         <v>2021</v>
       </c>
@@ -9807,7 +9807,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="432" t="s">
+      <c r="A53" s="420" t="s">
         <v>19</v>
       </c>
       <c r="B53" s="20">
@@ -9827,7 +9827,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="433"/>
+      <c r="A54" s="421"/>
       <c r="B54" s="20">
         <v>2007</v>
       </c>
@@ -9845,7 +9845,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="433"/>
+      <c r="A55" s="421"/>
       <c r="B55" s="20">
         <v>2014</v>
       </c>
@@ -9863,7 +9863,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="434"/>
+      <c r="A56" s="422"/>
       <c r="B56" s="20">
         <v>2021</v>
       </c>
@@ -9881,7 +9881,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="420" t="s">
+      <c r="A57" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B57" s="7">
@@ -9901,7 +9901,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="421"/>
+      <c r="A58" s="428"/>
       <c r="B58" s="7">
         <v>2007</v>
       </c>
@@ -9919,7 +9919,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="421"/>
+      <c r="A59" s="428"/>
       <c r="B59" s="7">
         <v>2014</v>
       </c>
@@ -9937,7 +9937,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="422"/>
+      <c r="A60" s="429"/>
       <c r="B60" s="69">
         <v>2021</v>
       </c>
@@ -9955,7 +9955,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="423" t="s">
+      <c r="A61" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="20">
@@ -9975,7 +9975,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="424"/>
+      <c r="A62" s="431"/>
       <c r="B62" s="20">
         <v>2007</v>
       </c>
@@ -9993,7 +9993,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="424"/>
+      <c r="A63" s="431"/>
       <c r="B63" s="20">
         <v>2014</v>
       </c>
@@ -10011,7 +10011,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="425"/>
+      <c r="A64" s="433"/>
       <c r="B64" s="24">
         <v>2021</v>
       </c>
@@ -10030,16 +10030,16 @@
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="67" spans="1:8" ht="48">
-      <c r="A67" s="426" t="s">
+      <c r="A67" s="434" t="s">
         <v>12</v>
       </c>
       <c r="B67" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C67" s="428" t="s">
+      <c r="C67" s="436" t="s">
         <v>44</v>
       </c>
-      <c r="D67" s="430" t="s">
+      <c r="D67" s="438" t="s">
         <v>133</v>
       </c>
       <c r="E67" s="11" t="s">
@@ -10050,12 +10050,12 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="18.75" thickBot="1">
-      <c r="A68" s="427"/>
+      <c r="A68" s="435"/>
       <c r="B68" s="135" t="s">
         <v>904</v>
       </c>
-      <c r="C68" s="429"/>
-      <c r="D68" s="431"/>
+      <c r="C68" s="437"/>
+      <c r="D68" s="439"/>
       <c r="E68" s="30" t="s">
         <v>905</v>
       </c>
@@ -10366,17 +10366,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A57:A60"/>
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
     <mergeCell ref="A53:A56"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="A41:A44"/>
     <mergeCell ref="A45:A48"/>
     <mergeCell ref="A49:A52"/>
-    <mergeCell ref="A57:A60"/>
-    <mergeCell ref="A61:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11140,10 +11140,10 @@
       <c r="B41" s="46" t="s">
         <v>631</v>
       </c>
-      <c r="C41" s="428" t="s">
+      <c r="C41" s="436" t="s">
         <v>353</v>
       </c>
-      <c r="D41" s="430" t="s">
+      <c r="D41" s="438" t="s">
         <v>1042</v>
       </c>
       <c r="E41" s="11" t="s">
@@ -11158,8 +11158,8 @@
       <c r="B42" s="36" t="s">
         <v>1041</v>
       </c>
-      <c r="C42" s="429"/>
-      <c r="D42" s="431"/>
+      <c r="C42" s="437"/>
+      <c r="D42" s="439"/>
       <c r="E42" s="30" t="s">
         <v>26</v>
       </c>
@@ -11168,7 +11168,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A43" s="420" t="s">
+      <c r="A43" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B43" s="7">
@@ -11188,7 +11188,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="421"/>
+      <c r="A44" s="428"/>
       <c r="B44" s="7">
         <v>2007</v>
       </c>
@@ -11206,7 +11206,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="421"/>
+      <c r="A45" s="428"/>
       <c r="B45" s="7">
         <v>2014</v>
       </c>
@@ -11224,7 +11224,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="422"/>
+      <c r="A46" s="429"/>
       <c r="B46" s="69">
         <v>2021</v>
       </c>
@@ -11242,7 +11242,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A47" s="423" t="s">
+      <c r="A47" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="20">
@@ -11262,7 +11262,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="424"/>
+      <c r="A48" s="431"/>
       <c r="B48" s="20">
         <v>2007</v>
       </c>
@@ -11280,7 +11280,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="424"/>
+      <c r="A49" s="431"/>
       <c r="B49" s="20">
         <v>2014</v>
       </c>
@@ -11298,7 +11298,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="439"/>
+      <c r="A50" s="432"/>
       <c r="B50" s="20">
         <v>2021</v>
       </c>
@@ -11316,7 +11316,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A51" s="420" t="s">
+      <c r="A51" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B51" s="7">
@@ -11336,7 +11336,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="421"/>
+      <c r="A52" s="428"/>
       <c r="B52" s="7">
         <v>2007</v>
       </c>
@@ -11354,7 +11354,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="84.75" thickBot="1">
-      <c r="A53" s="421"/>
+      <c r="A53" s="428"/>
       <c r="B53" s="7">
         <v>2014</v>
       </c>
@@ -11372,7 +11372,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="422"/>
+      <c r="A54" s="429"/>
       <c r="B54" s="69">
         <v>2021</v>
       </c>
@@ -11390,7 +11390,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A55" s="423" t="s">
+      <c r="A55" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B55" s="20">
@@ -11410,7 +11410,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="424"/>
+      <c r="A56" s="431"/>
       <c r="B56" s="20">
         <v>2007</v>
       </c>
@@ -11428,7 +11428,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="424"/>
+      <c r="A57" s="431"/>
       <c r="B57" s="20">
         <v>2014</v>
       </c>
@@ -11446,7 +11446,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="439"/>
+      <c r="A58" s="432"/>
       <c r="B58" s="20">
         <v>2021</v>
       </c>
@@ -11464,7 +11464,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A59" s="420" t="s">
+      <c r="A59" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B59" s="7">
@@ -11484,7 +11484,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="421"/>
+      <c r="A60" s="428"/>
       <c r="B60" s="7">
         <v>2007</v>
       </c>
@@ -11502,7 +11502,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="421"/>
+      <c r="A61" s="428"/>
       <c r="B61" s="7">
         <v>2014</v>
       </c>
@@ -11520,7 +11520,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="422"/>
+      <c r="A62" s="429"/>
       <c r="B62" s="69">
         <v>2021</v>
       </c>
@@ -11538,7 +11538,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A63" s="423" t="s">
+      <c r="A63" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="20">
@@ -11558,7 +11558,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="424"/>
+      <c r="A64" s="431"/>
       <c r="B64" s="20">
         <v>2007</v>
       </c>
@@ -11576,7 +11576,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A65" s="424"/>
+      <c r="A65" s="431"/>
       <c r="B65" s="20">
         <v>2014</v>
       </c>
@@ -11594,7 +11594,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A66" s="425"/>
+      <c r="A66" s="433"/>
       <c r="B66" s="24">
         <v>2021</v>
       </c>
@@ -11619,7 +11619,7 @@
       <c r="B69" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C69" s="447" t="s">
+      <c r="C69" s="453" t="s">
         <v>44</v>
       </c>
       <c r="D69" s="47" t="s">
@@ -12030,10 +12030,10 @@
     </row>
     <row r="89" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="90" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A90" s="514">
+      <c r="A90" s="505">
         <v>2016</v>
       </c>
-      <c r="B90" s="515"/>
+      <c r="B90" s="506"/>
       <c r="C90" s="3">
         <v>2017</v>
       </c>
@@ -12294,19 +12294,19 @@
         <v>36</v>
       </c>
       <c r="B101" s="252"/>
-      <c r="C101" s="438" t="s">
+      <c r="C101" s="426" t="s">
         <v>1048</v>
       </c>
-      <c r="D101" s="509"/>
-      <c r="E101" s="510" t="s">
+      <c r="D101" s="511"/>
+      <c r="E101" s="512" t="s">
         <v>923</v>
       </c>
-      <c r="F101" s="511"/>
+      <c r="F101" s="513"/>
       <c r="G101" s="252"/>
-      <c r="H101" s="511" t="s">
+      <c r="H101" s="513" t="s">
         <v>75</v>
       </c>
-      <c r="I101" s="511"/>
+      <c r="I101" s="513"/>
       <c r="J101" s="328"/>
       <c r="K101" s="11" t="s">
         <v>8</v>
@@ -12322,21 +12322,21 @@
       <c r="B102" s="101" t="s">
         <v>1063</v>
       </c>
-      <c r="C102" s="512" t="s">
+      <c r="C102" s="514" t="s">
         <v>1064</v>
       </c>
-      <c r="D102" s="513"/>
-      <c r="E102" s="512" t="s">
+      <c r="D102" s="515"/>
+      <c r="E102" s="514" t="s">
         <v>1063</v>
       </c>
-      <c r="F102" s="513"/>
+      <c r="F102" s="515"/>
       <c r="G102" s="7" t="s">
         <v>1064</v>
       </c>
-      <c r="H102" s="512" t="s">
+      <c r="H102" s="514" t="s">
         <v>1063</v>
       </c>
-      <c r="I102" s="513"/>
+      <c r="I102" s="515"/>
       <c r="J102" s="12" t="s">
         <v>1064</v>
       </c>
@@ -12354,21 +12354,21 @@
       <c r="B103" s="311">
         <v>0.8</v>
       </c>
-      <c r="C103" s="505">
+      <c r="C103" s="507">
         <v>0.2</v>
       </c>
-      <c r="D103" s="506"/>
-      <c r="E103" s="505">
+      <c r="D103" s="508"/>
+      <c r="E103" s="507">
         <v>0.94</v>
       </c>
-      <c r="F103" s="506"/>
+      <c r="F103" s="508"/>
       <c r="G103" s="311">
         <v>0.06</v>
       </c>
-      <c r="H103" s="505">
+      <c r="H103" s="507">
         <v>1</v>
       </c>
-      <c r="I103" s="506"/>
+      <c r="I103" s="508"/>
       <c r="J103" s="312">
         <v>0</v>
       </c>
@@ -12462,21 +12462,21 @@
       <c r="B106" s="69" t="s">
         <v>1074</v>
       </c>
-      <c r="C106" s="507" t="s">
+      <c r="C106" s="509" t="s">
         <v>1075</v>
       </c>
-      <c r="D106" s="508"/>
-      <c r="E106" s="507" t="s">
+      <c r="D106" s="510"/>
+      <c r="E106" s="509" t="s">
         <v>1076</v>
       </c>
-      <c r="F106" s="508"/>
+      <c r="F106" s="510"/>
       <c r="G106" s="69" t="s">
         <v>1077</v>
       </c>
-      <c r="H106" s="507" t="s">
+      <c r="H106" s="509" t="s">
         <v>1078</v>
       </c>
-      <c r="I106" s="508"/>
+      <c r="I106" s="510"/>
       <c r="J106" s="51" t="s">
         <v>105</v>
       </c>
@@ -12498,10 +12498,10 @@
       <c r="C109" s="46" t="s">
         <v>1082</v>
       </c>
-      <c r="D109" s="428" t="s">
+      <c r="D109" s="436" t="s">
         <v>1085</v>
       </c>
-      <c r="E109" s="430" t="s">
+      <c r="E109" s="438" t="s">
         <v>1086</v>
       </c>
       <c r="F109" s="11" t="s">
@@ -12519,8 +12519,8 @@
       <c r="C110" s="36" t="s">
         <v>1084</v>
       </c>
-      <c r="D110" s="429"/>
-      <c r="E110" s="431"/>
+      <c r="D110" s="437"/>
+      <c r="E110" s="439"/>
       <c r="F110" s="30" t="s">
         <v>1090</v>
       </c>
@@ -12719,6 +12719,21 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="E109:E110"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="H102:I102"/>
     <mergeCell ref="A90:B90"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="C41:C42"/>
@@ -12731,21 +12746,6 @@
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="C69:C70"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="D109:D110"/>
-    <mergeCell ref="E109:E110"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="E103:F103"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" location="_ftn1" display="_ftn1" xr:uid="{9F985B06-5BF5-4426-82E7-BDE487DF777B}"/>
@@ -12917,7 +12917,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A11" s="420" t="s">
+      <c r="A11" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="7">
@@ -12937,7 +12937,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A12" s="421"/>
+      <c r="A12" s="428"/>
       <c r="B12" s="7">
         <v>2007</v>
       </c>
@@ -12955,7 +12955,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A13" s="421"/>
+      <c r="A13" s="428"/>
       <c r="B13" s="7">
         <v>2014</v>
       </c>
@@ -12973,7 +12973,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A14" s="422"/>
+      <c r="A14" s="429"/>
       <c r="B14" s="69">
         <v>2021</v>
       </c>
@@ -12991,7 +12991,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A15" s="423" t="s">
+      <c r="A15" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="20">
@@ -13011,7 +13011,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A16" s="424"/>
+      <c r="A16" s="431"/>
       <c r="B16" s="20">
         <v>2007</v>
       </c>
@@ -13029,7 +13029,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="424"/>
+      <c r="A17" s="431"/>
       <c r="B17" s="20">
         <v>2014</v>
       </c>
@@ -13047,7 +13047,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="439"/>
+      <c r="A18" s="432"/>
       <c r="B18" s="20">
         <v>2021</v>
       </c>
@@ -13139,7 +13139,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="423" t="s">
+      <c r="A23" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="20">
@@ -13159,7 +13159,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="424"/>
+      <c r="A24" s="431"/>
       <c r="B24" s="20">
         <v>2007</v>
       </c>
@@ -13177,7 +13177,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="424"/>
+      <c r="A25" s="431"/>
       <c r="B25" s="20">
         <v>2014</v>
       </c>
@@ -13195,7 +13195,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="439"/>
+      <c r="A26" s="432"/>
       <c r="B26" s="20">
         <v>2021</v>
       </c>
@@ -13213,7 +13213,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="420" t="s">
+      <c r="A27" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B27" s="7">
@@ -13233,7 +13233,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="421"/>
+      <c r="A28" s="428"/>
       <c r="B28" s="7">
         <v>2007</v>
       </c>
@@ -13251,7 +13251,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="421"/>
+      <c r="A29" s="428"/>
       <c r="B29" s="7">
         <v>2014</v>
       </c>
@@ -13269,7 +13269,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="422"/>
+      <c r="A30" s="429"/>
       <c r="B30" s="69">
         <v>2021</v>
       </c>
@@ -13287,7 +13287,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="423" t="s">
+      <c r="A31" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="20">
@@ -13307,7 +13307,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="424"/>
+      <c r="A32" s="431"/>
       <c r="B32" s="20">
         <v>2007</v>
       </c>
@@ -13325,7 +13325,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A33" s="424"/>
+      <c r="A33" s="431"/>
       <c r="B33" s="20">
         <v>2014</v>
       </c>
@@ -13343,7 +13343,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="425"/>
+      <c r="A34" s="433"/>
       <c r="B34" s="24">
         <v>2021</v>
       </c>
@@ -13459,10 +13459,10 @@
       <c r="B41" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="428" t="s">
+      <c r="C41" s="436" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="430" t="s">
+      <c r="D41" s="438" t="s">
         <v>408</v>
       </c>
       <c r="E41" s="11" t="s">
@@ -13477,8 +13477,8 @@
       <c r="B42" s="135" t="s">
         <v>407</v>
       </c>
-      <c r="C42" s="429"/>
-      <c r="D42" s="431"/>
+      <c r="C42" s="437"/>
+      <c r="D42" s="439"/>
       <c r="E42" s="30" t="s">
         <v>409</v>
       </c>
@@ -14152,11 +14152,11 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="10" spans="1:6" ht="30.6" customHeight="1">
-      <c r="A10" s="467"/>
-      <c r="B10" s="428" t="s">
+      <c r="A10" s="462"/>
+      <c r="B10" s="436" t="s">
         <v>1101</v>
       </c>
-      <c r="C10" s="428" t="s">
+      <c r="C10" s="436" t="s">
         <v>1098</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -14171,8 +14171,8 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1">
       <c r="A11" s="479"/>
-      <c r="B11" s="429"/>
-      <c r="C11" s="429"/>
+      <c r="B11" s="437"/>
+      <c r="C11" s="437"/>
       <c r="D11" s="136" t="s">
         <v>1103</v>
       </c>
@@ -14442,10 +14442,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="30" spans="1:6">
-      <c r="A30" s="426" t="s">
+      <c r="A30" s="434" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="428" t="s">
+      <c r="B30" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="46" t="s">
@@ -14462,8 +14462,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="27.75" thickBot="1">
-      <c r="A31" s="427"/>
-      <c r="B31" s="429"/>
+      <c r="A31" s="435"/>
+      <c r="B31" s="437"/>
       <c r="C31" s="135" t="s">
         <v>197</v>
       </c>
@@ -14478,7 +14478,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="420" t="s">
+      <c r="A32" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="7">
@@ -14498,7 +14498,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="421"/>
+      <c r="A33" s="428"/>
       <c r="B33" s="7">
         <v>2007</v>
       </c>
@@ -14516,7 +14516,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="421"/>
+      <c r="A34" s="428"/>
       <c r="B34" s="7">
         <v>2014</v>
       </c>
@@ -14534,7 +14534,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="422"/>
+      <c r="A35" s="429"/>
       <c r="B35" s="69">
         <v>2021</v>
       </c>
@@ -14552,7 +14552,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="473" t="s">
+      <c r="A36" s="475" t="s">
         <v>17</v>
       </c>
       <c r="B36" s="20">
@@ -14608,7 +14608,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="474"/>
+      <c r="A39" s="476"/>
       <c r="B39" s="20">
         <v>2021</v>
       </c>
@@ -14626,7 +14626,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="420" t="s">
+      <c r="A40" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B40" s="7">
@@ -14646,7 +14646,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="421"/>
+      <c r="A41" s="428"/>
       <c r="B41" s="7">
         <v>2007</v>
       </c>
@@ -14664,7 +14664,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="421"/>
+      <c r="A42" s="428"/>
       <c r="B42" s="7">
         <v>2014</v>
       </c>
@@ -14682,7 +14682,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="422"/>
+      <c r="A43" s="429"/>
       <c r="B43" s="69">
         <v>2021</v>
       </c>
@@ -14700,7 +14700,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="473" t="s">
+      <c r="A44" s="475" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="20">
@@ -14756,7 +14756,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="474"/>
+      <c r="A47" s="476"/>
       <c r="B47" s="20">
         <v>2021</v>
       </c>
@@ -14774,7 +14774,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="420" t="s">
+      <c r="A48" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B48" s="7">
@@ -14794,7 +14794,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="421"/>
+      <c r="A49" s="428"/>
       <c r="B49" s="7">
         <v>2007</v>
       </c>
@@ -14812,7 +14812,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="421"/>
+      <c r="A50" s="428"/>
       <c r="B50" s="7">
         <v>2014</v>
       </c>
@@ -14830,7 +14830,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="422"/>
+      <c r="A51" s="429"/>
       <c r="B51" s="69">
         <v>2021</v>
       </c>
@@ -14848,7 +14848,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="423" t="s">
+      <c r="A52" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="20">
@@ -14868,7 +14868,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="424"/>
+      <c r="A53" s="431"/>
       <c r="B53" s="20">
         <v>2007</v>
       </c>
@@ -14886,7 +14886,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="24.75" thickBot="1">
-      <c r="A54" s="424"/>
+      <c r="A54" s="431"/>
       <c r="B54" s="20">
         <v>2014</v>
       </c>
@@ -14904,7 +14904,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="425"/>
+      <c r="A55" s="433"/>
       <c r="B55" s="24">
         <v>2021</v>
       </c>
@@ -15064,17 +15064,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A52:A55"/>
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="A52:A55"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15846,10 +15846,10 @@
       <c r="A43" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="527" t="s">
+      <c r="B43" s="520" t="s">
         <v>477</v>
       </c>
-      <c r="C43" s="528"/>
+      <c r="C43" s="521"/>
       <c r="D43" s="47" t="s">
         <v>478</v>
       </c>
@@ -15862,8 +15862,8 @@
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
       <c r="A44" s="456"/>
-      <c r="B44" s="529"/>
-      <c r="C44" s="530"/>
+      <c r="B44" s="522"/>
+      <c r="C44" s="523"/>
       <c r="D44" s="136" t="s">
         <v>287</v>
       </c>
@@ -15875,7 +15875,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="420" t="s">
+      <c r="A45" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B45" s="7">
@@ -15895,7 +15895,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="421"/>
+      <c r="A46" s="428"/>
       <c r="B46" s="7">
         <v>2007</v>
       </c>
@@ -15913,7 +15913,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="421"/>
+      <c r="A47" s="428"/>
       <c r="B47" s="7">
         <v>2014</v>
       </c>
@@ -15931,7 +15931,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="422"/>
+      <c r="A48" s="429"/>
       <c r="B48" s="69">
         <v>2021</v>
       </c>
@@ -15949,7 +15949,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="423" t="s">
+      <c r="A49" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B49" s="20">
@@ -15969,7 +15969,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="424"/>
+      <c r="A50" s="431"/>
       <c r="B50" s="20">
         <v>2007</v>
       </c>
@@ -15987,7 +15987,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="424"/>
+      <c r="A51" s="431"/>
       <c r="B51" s="20">
         <v>2014</v>
       </c>
@@ -16005,7 +16005,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="439"/>
+      <c r="A52" s="432"/>
       <c r="B52" s="20">
         <v>2021</v>
       </c>
@@ -16023,7 +16023,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="420" t="s">
+      <c r="A53" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B53" s="7">
@@ -16043,7 +16043,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="421"/>
+      <c r="A54" s="428"/>
       <c r="B54" s="7">
         <v>2007</v>
       </c>
@@ -16061,7 +16061,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="421"/>
+      <c r="A55" s="428"/>
       <c r="B55" s="7">
         <v>2014</v>
       </c>
@@ -16079,7 +16079,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="422"/>
+      <c r="A56" s="429"/>
       <c r="B56" s="69">
         <v>2021</v>
       </c>
@@ -16097,7 +16097,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="423" t="s">
+      <c r="A57" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B57" s="20">
@@ -16117,7 +16117,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="424"/>
+      <c r="A58" s="431"/>
       <c r="B58" s="20">
         <v>2007</v>
       </c>
@@ -16135,7 +16135,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="424"/>
+      <c r="A59" s="431"/>
       <c r="B59" s="20">
         <v>2014</v>
       </c>
@@ -16153,7 +16153,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="439"/>
+      <c r="A60" s="432"/>
       <c r="B60" s="20">
         <v>2021</v>
       </c>
@@ -16171,7 +16171,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="420" t="s">
+      <c r="A61" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="7">
@@ -16191,7 +16191,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="421"/>
+      <c r="A62" s="428"/>
       <c r="B62" s="7">
         <v>2007</v>
       </c>
@@ -16209,7 +16209,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="422"/>
+      <c r="A63" s="429"/>
       <c r="B63" s="69">
         <v>2014</v>
       </c>
@@ -16227,7 +16227,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="423" t="s">
+      <c r="A64" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="20">
@@ -16247,7 +16247,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="24.75" thickBot="1">
-      <c r="A65" s="424"/>
+      <c r="A65" s="431"/>
       <c r="B65" s="20">
         <v>2007</v>
       </c>
@@ -16265,7 +16265,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="36.75" thickBot="1">
-      <c r="A66" s="424"/>
+      <c r="A66" s="431"/>
       <c r="B66" s="20">
         <v>2014</v>
       </c>
@@ -16283,7 +16283,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="24.75" thickBot="1">
-      <c r="A67" s="425"/>
+      <c r="A67" s="433"/>
       <c r="B67" s="24">
         <v>2021</v>
       </c>
@@ -16393,13 +16393,13 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="74" spans="1:7" ht="48">
-      <c r="A74" s="520" t="s">
+      <c r="A74" s="524" t="s">
         <v>12</v>
       </c>
       <c r="B74" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="428" t="s">
+      <c r="C74" s="436" t="s">
         <v>44</v>
       </c>
       <c r="D74" s="47" t="s">
@@ -16413,11 +16413,11 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="18.75" thickBot="1">
-      <c r="A75" s="521"/>
+      <c r="A75" s="525"/>
       <c r="B75" s="135" t="s">
         <v>490</v>
       </c>
-      <c r="C75" s="429"/>
+      <c r="C75" s="437"/>
       <c r="D75" s="136" t="s">
         <v>287</v>
       </c>
@@ -16760,17 +16760,17 @@
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1"/>
     <row r="95" spans="1:8" ht="36">
-      <c r="A95" s="522"/>
-      <c r="B95" s="524" t="s">
+      <c r="A95" s="526"/>
+      <c r="B95" s="528" t="s">
         <v>499</v>
       </c>
-      <c r="C95" s="471" t="s">
+      <c r="C95" s="466" t="s">
         <v>500</v>
       </c>
       <c r="D95" s="46" t="s">
         <v>501</v>
       </c>
-      <c r="E95" s="469" t="s">
+      <c r="E95" s="464" t="s">
         <v>503</v>
       </c>
       <c r="F95" s="47" t="s">
@@ -16784,9 +16784,9 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="36.75" thickBot="1">
-      <c r="A96" s="523"/>
-      <c r="B96" s="525"/>
-      <c r="C96" s="526"/>
+      <c r="A96" s="527"/>
+      <c r="B96" s="529"/>
+      <c r="C96" s="530"/>
       <c r="D96" s="224" t="s">
         <v>502</v>
       </c>
@@ -17088,11 +17088,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:C44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="A53:A56"/>
     <mergeCell ref="E95:E96"/>
     <mergeCell ref="A57:A60"/>
     <mergeCell ref="A61:A63"/>
@@ -17102,6 +17097,11 @@
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B95:B96"/>
     <mergeCell ref="C95:C96"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:C44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A53:A56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17411,11 +17411,11 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="526"/>
+      <c r="A21" s="530"/>
       <c r="B21" s="286" t="s">
         <v>1118</v>
       </c>
-      <c r="C21" s="429"/>
+      <c r="C21" s="437"/>
       <c r="D21" s="178" t="s">
         <v>46</v>
       </c>
@@ -18126,13 +18126,13 @@
       <c r="A31" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="469" t="s">
+      <c r="B31" s="464" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D31" s="430" t="s">
+      <c r="D31" s="438" t="s">
         <v>529</v>
       </c>
       <c r="E31" s="11" t="s">
@@ -18148,7 +18148,7 @@
       <c r="C32" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="D32" s="431"/>
+      <c r="D32" s="439"/>
       <c r="E32" s="30" t="s">
         <v>26</v>
       </c>
@@ -18157,7 +18157,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="420" t="s">
+      <c r="A33" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="7">
@@ -18177,7 +18177,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="421"/>
+      <c r="A34" s="428"/>
       <c r="B34" s="7">
         <v>2007</v>
       </c>
@@ -18195,7 +18195,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="421"/>
+      <c r="A35" s="428"/>
       <c r="B35" s="7">
         <v>2014</v>
       </c>
@@ -18213,7 +18213,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="422"/>
+      <c r="A36" s="429"/>
       <c r="B36" s="69">
         <v>2021</v>
       </c>
@@ -18231,7 +18231,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="423" t="s">
+      <c r="A37" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B37" s="20">
@@ -18251,7 +18251,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="424"/>
+      <c r="A38" s="431"/>
       <c r="B38" s="20">
         <v>2007</v>
       </c>
@@ -18269,7 +18269,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="424"/>
+      <c r="A39" s="431"/>
       <c r="B39" s="20">
         <v>2014</v>
       </c>
@@ -18287,7 +18287,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="439"/>
+      <c r="A40" s="432"/>
       <c r="B40" s="20">
         <v>2021</v>
       </c>
@@ -18305,7 +18305,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="420" t="s">
+      <c r="A41" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B41" s="7">
@@ -18325,7 +18325,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="421"/>
+      <c r="A42" s="428"/>
       <c r="B42" s="7">
         <v>2007</v>
       </c>
@@ -18343,7 +18343,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="421"/>
+      <c r="A43" s="428"/>
       <c r="B43" s="7">
         <v>2014</v>
       </c>
@@ -18361,7 +18361,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="422"/>
+      <c r="A44" s="429"/>
       <c r="B44" s="69">
         <v>2021</v>
       </c>
@@ -18379,7 +18379,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="423" t="s">
+      <c r="A45" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B45" s="20">
@@ -18399,7 +18399,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="424"/>
+      <c r="A46" s="431"/>
       <c r="B46" s="20">
         <v>2007</v>
       </c>
@@ -18417,7 +18417,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="424"/>
+      <c r="A47" s="431"/>
       <c r="B47" s="20">
         <v>2014</v>
       </c>
@@ -18435,7 +18435,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="439"/>
+      <c r="A48" s="432"/>
       <c r="B48" s="20">
         <v>2021</v>
       </c>
@@ -18453,7 +18453,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A49" s="420" t="s">
+      <c r="A49" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B49" s="7">
@@ -18473,7 +18473,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A50" s="421"/>
+      <c r="A50" s="428"/>
       <c r="B50" s="7">
         <v>2007</v>
       </c>
@@ -18491,7 +18491,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A51" s="421"/>
+      <c r="A51" s="428"/>
       <c r="B51" s="7">
         <v>2014</v>
       </c>
@@ -18509,7 +18509,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A52" s="422"/>
+      <c r="A52" s="429"/>
       <c r="B52" s="69">
         <v>2021</v>
       </c>
@@ -18527,7 +18527,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A53" s="423" t="s">
+      <c r="A53" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="20">
@@ -18547,7 +18547,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A54" s="424"/>
+      <c r="A54" s="431"/>
       <c r="B54" s="20">
         <v>2007</v>
       </c>
@@ -18565,7 +18565,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="36.75" thickBot="1">
-      <c r="A55" s="424"/>
+      <c r="A55" s="431"/>
       <c r="B55" s="20">
         <v>2014</v>
       </c>
@@ -18583,7 +18583,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A56" s="425"/>
+      <c r="A56" s="433"/>
       <c r="B56" s="24">
         <v>2021</v>
       </c>
@@ -18852,10 +18852,10 @@
       <c r="B66" s="231" t="s">
         <v>285</v>
       </c>
-      <c r="C66" s="535" t="s">
+      <c r="C66" s="540" t="s">
         <v>44</v>
       </c>
-      <c r="D66" s="533" t="s">
+      <c r="D66" s="538" t="s">
         <v>541</v>
       </c>
       <c r="E66" s="11" t="s">
@@ -18870,8 +18870,8 @@
       <c r="B67" s="135" t="s">
         <v>540</v>
       </c>
-      <c r="C67" s="536"/>
-      <c r="D67" s="534"/>
+      <c r="C67" s="541"/>
+      <c r="D67" s="539"/>
       <c r="E67" s="30" t="s">
         <v>51</v>
       </c>
@@ -19090,14 +19090,14 @@
       <c r="A81" s="455" t="s">
         <v>556</v>
       </c>
-      <c r="B81" s="463" t="s">
+      <c r="B81" s="468" t="s">
         <v>557</v>
       </c>
-      <c r="C81" s="466"/>
-      <c r="D81" s="466"/>
-      <c r="E81" s="466"/>
-      <c r="F81" s="466"/>
-      <c r="G81" s="464"/>
+      <c r="C81" s="471"/>
+      <c r="D81" s="471"/>
+      <c r="E81" s="471"/>
+      <c r="F81" s="471"/>
+      <c r="G81" s="469"/>
       <c r="H81" s="11" t="s">
         <v>8</v>
       </c>
@@ -19106,19 +19106,19 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A82" s="537"/>
-      <c r="B82" s="539">
+      <c r="A82" s="533"/>
+      <c r="B82" s="535">
         <v>2018</v>
       </c>
-      <c r="C82" s="540"/>
-      <c r="D82" s="539">
+      <c r="C82" s="536"/>
+      <c r="D82" s="535">
         <v>2019</v>
       </c>
-      <c r="E82" s="540"/>
-      <c r="F82" s="539">
+      <c r="E82" s="536"/>
+      <c r="F82" s="535">
         <v>2020</v>
       </c>
-      <c r="G82" s="541"/>
+      <c r="G82" s="537"/>
       <c r="H82" s="30" t="s">
         <v>577</v>
       </c>
@@ -19127,7 +19127,7 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A83" s="538"/>
+      <c r="A83" s="534"/>
       <c r="B83" s="234" t="s">
         <v>558</v>
       </c>
@@ -19706,11 +19706,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="B81:G81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
     <mergeCell ref="D66:D67"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="B31:B32"/>
@@ -19723,6 +19718,11 @@
     <mergeCell ref="A53:A56"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="B81:G81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A6" location="_ftn1" display="_ftn1" xr:uid="{88A27A76-82D3-4610-8B7C-2CFCB91C8902}"/>
@@ -20268,7 +20268,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="420" t="s">
+      <c r="A34" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="7">
@@ -20288,7 +20288,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="421"/>
+      <c r="A35" s="428"/>
       <c r="B35" s="7">
         <v>2007</v>
       </c>
@@ -20306,7 +20306,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="421"/>
+      <c r="A36" s="428"/>
       <c r="B36" s="7">
         <v>2014</v>
       </c>
@@ -20324,7 +20324,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="422"/>
+      <c r="A37" s="429"/>
       <c r="B37" s="69">
         <v>2021</v>
       </c>
@@ -20342,7 +20342,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="423" t="s">
+      <c r="A38" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="20">
@@ -20362,7 +20362,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="424"/>
+      <c r="A39" s="431"/>
       <c r="B39" s="20">
         <v>2007</v>
       </c>
@@ -20380,7 +20380,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="424"/>
+      <c r="A40" s="431"/>
       <c r="B40" s="20">
         <v>2014</v>
       </c>
@@ -20398,7 +20398,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="439"/>
+      <c r="A41" s="432"/>
       <c r="B41" s="20">
         <v>2021</v>
       </c>
@@ -20490,7 +20490,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="423" t="s">
+      <c r="A46" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B46" s="20">
@@ -20510,7 +20510,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="424"/>
+      <c r="A47" s="431"/>
       <c r="B47" s="20">
         <v>2007</v>
       </c>
@@ -20528,7 +20528,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="424"/>
+      <c r="A48" s="431"/>
       <c r="B48" s="20">
         <v>2014</v>
       </c>
@@ -20546,7 +20546,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="439"/>
+      <c r="A49" s="432"/>
       <c r="B49" s="20">
         <v>2021</v>
       </c>
@@ -20638,7 +20638,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="423" t="s">
+      <c r="A54" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="20">
@@ -20658,7 +20658,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="424"/>
+      <c r="A55" s="431"/>
       <c r="B55" s="20">
         <v>2007</v>
       </c>
@@ -20676,7 +20676,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="424"/>
+      <c r="A56" s="431"/>
       <c r="B56" s="20">
         <v>2014</v>
       </c>
@@ -20694,7 +20694,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="425"/>
+      <c r="A57" s="433"/>
       <c r="B57" s="24">
         <v>2021</v>
       </c>
@@ -22293,7 +22293,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A22" s="420">
+      <c r="A22" s="427">
         <v>2016</v>
       </c>
       <c r="B22" s="101" t="s">
@@ -22328,7 +22328,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A23" s="444"/>
+      <c r="A23" s="446"/>
       <c r="B23" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22361,7 +22361,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A24" s="420">
+      <c r="A24" s="427">
         <v>2017</v>
       </c>
       <c r="B24" s="101" t="s">
@@ -22396,7 +22396,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A25" s="444"/>
+      <c r="A25" s="446"/>
       <c r="B25" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22429,7 +22429,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A26" s="420">
+      <c r="A26" s="427">
         <v>2018</v>
       </c>
       <c r="B26" s="101" t="s">
@@ -22464,7 +22464,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A27" s="444"/>
+      <c r="A27" s="446"/>
       <c r="B27" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22497,7 +22497,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A28" s="420">
+      <c r="A28" s="427">
         <v>2019</v>
       </c>
       <c r="B28" s="101" t="s">
@@ -22532,7 +22532,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A29" s="444"/>
+      <c r="A29" s="446"/>
       <c r="B29" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22565,7 +22565,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A30" s="420">
+      <c r="A30" s="427">
         <v>2020</v>
       </c>
       <c r="B30" s="101" t="s">
@@ -22600,7 +22600,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A31" s="444"/>
+      <c r="A31" s="446"/>
       <c r="B31" s="101" t="s">
         <v>1125</v>
       </c>
@@ -22633,7 +22633,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A32" s="420">
+      <c r="A32" s="427">
         <v>2021</v>
       </c>
       <c r="B32" s="101" t="s">
@@ -22668,7 +22668,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="24.75" thickBot="1">
-      <c r="A33" s="422"/>
+      <c r="A33" s="429"/>
       <c r="B33" s="107" t="s">
         <v>1125</v>
       </c>
@@ -22859,7 +22859,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A47" s="420" t="s">
+      <c r="A47" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B47" s="7">
@@ -22879,7 +22879,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A48" s="421"/>
+      <c r="A48" s="428"/>
       <c r="B48" s="7">
         <v>2007</v>
       </c>
@@ -22897,7 +22897,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="421"/>
+      <c r="A49" s="428"/>
       <c r="B49" s="7">
         <v>2014</v>
       </c>
@@ -22915,7 +22915,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="422"/>
+      <c r="A50" s="429"/>
       <c r="B50" s="69">
         <v>2021</v>
       </c>
@@ -22933,7 +22933,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="423" t="s">
+      <c r="A51" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B51" s="20">
@@ -22953,7 +22953,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="424"/>
+      <c r="A52" s="431"/>
       <c r="B52" s="20">
         <v>2007</v>
       </c>
@@ -22971,7 +22971,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="424"/>
+      <c r="A53" s="431"/>
       <c r="B53" s="20">
         <v>2014</v>
       </c>
@@ -22989,7 +22989,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="439"/>
+      <c r="A54" s="432"/>
       <c r="B54" s="20">
         <v>2021</v>
       </c>
@@ -23007,7 +23007,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="420" t="s">
+      <c r="A55" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B55" s="7">
@@ -23027,7 +23027,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="421"/>
+      <c r="A56" s="428"/>
       <c r="B56" s="7">
         <v>2007</v>
       </c>
@@ -23045,7 +23045,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="421"/>
+      <c r="A57" s="428"/>
       <c r="B57" s="7">
         <v>2014</v>
       </c>
@@ -23063,7 +23063,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="422"/>
+      <c r="A58" s="429"/>
       <c r="B58" s="69">
         <v>2021</v>
       </c>
@@ -23081,7 +23081,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="423" t="s">
+      <c r="A59" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B59" s="20">
@@ -23101,7 +23101,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="424"/>
+      <c r="A60" s="431"/>
       <c r="B60" s="20">
         <v>2007</v>
       </c>
@@ -23119,7 +23119,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="424"/>
+      <c r="A61" s="431"/>
       <c r="B61" s="20">
         <v>2014</v>
       </c>
@@ -23137,7 +23137,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="439"/>
+      <c r="A62" s="432"/>
       <c r="B62" s="20">
         <v>2021</v>
       </c>
@@ -23155,7 +23155,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="420" t="s">
+      <c r="A63" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="7">
@@ -23175,7 +23175,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="421"/>
+      <c r="A64" s="428"/>
       <c r="B64" s="7">
         <v>2007</v>
       </c>
@@ -23193,7 +23193,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A65" s="421"/>
+      <c r="A65" s="428"/>
       <c r="B65" s="7">
         <v>2014</v>
       </c>
@@ -23211,7 +23211,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A66" s="422"/>
+      <c r="A66" s="429"/>
       <c r="B66" s="69">
         <v>2021</v>
       </c>
@@ -23229,7 +23229,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A67" s="423" t="s">
+      <c r="A67" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="20">
@@ -23249,7 +23249,7 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A68" s="424"/>
+      <c r="A68" s="431"/>
       <c r="B68" s="20">
         <v>2007</v>
       </c>
@@ -23267,7 +23267,7 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A69" s="424"/>
+      <c r="A69" s="431"/>
       <c r="B69" s="20">
         <v>2014</v>
       </c>
@@ -23285,7 +23285,7 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A70" s="425"/>
+      <c r="A70" s="433"/>
       <c r="B70" s="24">
         <v>2021</v>
       </c>
@@ -23447,10 +23447,10 @@
       <c r="B81" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="428" t="s">
+      <c r="C81" s="436" t="s">
         <v>44</v>
       </c>
-      <c r="D81" s="430" t="s">
+      <c r="D81" s="438" t="s">
         <v>1155</v>
       </c>
       <c r="E81" s="11" t="s">
@@ -23465,8 +23465,8 @@
       <c r="B82" s="135" t="s">
         <v>1154</v>
       </c>
-      <c r="C82" s="429"/>
-      <c r="D82" s="431"/>
+      <c r="C82" s="437"/>
+      <c r="D82" s="439"/>
       <c r="E82" s="30" t="s">
         <v>1156</v>
       </c>
@@ -23777,6 +23777,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
     <mergeCell ref="A59:A62"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F20:G20"/>
@@ -23789,11 +23794,6 @@
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24155,7 +24155,7 @@
       <c r="A19" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="428" t="s">
+      <c r="B19" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="46" t="s">
@@ -24173,7 +24173,7 @@
     </row>
     <row r="20" spans="1:6" ht="18.75" thickBot="1">
       <c r="A20" s="456"/>
-      <c r="B20" s="429"/>
+      <c r="B20" s="437"/>
       <c r="C20" s="286" t="s">
         <v>197</v>
       </c>
@@ -24188,7 +24188,9 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="287"/>
+      <c r="A21" s="287" t="s">
+        <v>16</v>
+      </c>
       <c r="B21" s="219">
         <v>1999</v>
       </c>
@@ -24206,7 +24208,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="557" t="s">
+      <c r="A22" s="547" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="7">
@@ -24226,7 +24228,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="557"/>
+      <c r="A23" s="547"/>
       <c r="B23" s="7">
         <v>2014</v>
       </c>
@@ -24244,7 +24246,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="558"/>
+      <c r="A24" s="548"/>
       <c r="B24" s="69">
         <v>2021</v>
       </c>
@@ -24262,7 +24264,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="423" t="s">
+      <c r="A25" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="20">
@@ -24282,7 +24284,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="424"/>
+      <c r="A26" s="431"/>
       <c r="B26" s="20">
         <v>2007</v>
       </c>
@@ -24300,7 +24302,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="424"/>
+      <c r="A27" s="431"/>
       <c r="B27" s="20">
         <v>2014</v>
       </c>
@@ -24318,7 +24320,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="439"/>
+      <c r="A28" s="432"/>
       <c r="B28" s="20">
         <v>2021</v>
       </c>
@@ -24336,7 +24338,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="420" t="s">
+      <c r="A29" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B29" s="7">
@@ -24356,7 +24358,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="421"/>
+      <c r="A30" s="428"/>
       <c r="B30" s="7">
         <v>2007</v>
       </c>
@@ -24374,7 +24376,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="421"/>
+      <c r="A31" s="428"/>
       <c r="B31" s="7">
         <v>2014</v>
       </c>
@@ -24392,7 +24394,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="422"/>
+      <c r="A32" s="429"/>
       <c r="B32" s="69">
         <v>2021</v>
       </c>
@@ -24484,7 +24486,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A37" s="420" t="s">
+      <c r="A37" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B37" s="7">
@@ -24504,7 +24506,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A38" s="421"/>
+      <c r="A38" s="428"/>
       <c r="B38" s="7">
         <v>2007</v>
       </c>
@@ -24522,7 +24524,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A39" s="421"/>
+      <c r="A39" s="428"/>
       <c r="B39" s="7">
         <v>2014</v>
       </c>
@@ -24540,7 +24542,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A40" s="422"/>
+      <c r="A40" s="429"/>
       <c r="B40" s="69">
         <v>2021</v>
       </c>
@@ -24558,7 +24560,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A41" s="423" t="s">
+      <c r="A41" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="20">
@@ -24578,7 +24580,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A42" s="424"/>
+      <c r="A42" s="431"/>
       <c r="B42" s="20">
         <v>2007</v>
       </c>
@@ -24596,7 +24598,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A43" s="424"/>
+      <c r="A43" s="431"/>
       <c r="B43" s="20">
         <v>2014</v>
       </c>
@@ -24614,7 +24616,7 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A44" s="425"/>
+      <c r="A44" s="433"/>
       <c r="B44" s="24">
         <v>2021</v>
       </c>
@@ -25316,18 +25318,18 @@
       <c r="B85" s="227" t="s">
         <v>76</v>
       </c>
-      <c r="C85" s="463" t="s">
+      <c r="C85" s="468" t="s">
         <v>768</v>
       </c>
-      <c r="D85" s="465"/>
-      <c r="E85" s="463" t="s">
+      <c r="D85" s="470"/>
+      <c r="E85" s="468" t="s">
         <v>769</v>
       </c>
-      <c r="F85" s="466"/>
-      <c r="G85" s="466" t="s">
+      <c r="F85" s="471"/>
+      <c r="G85" s="471" t="s">
         <v>770</v>
       </c>
-      <c r="H85" s="464"/>
+      <c r="H85" s="469"/>
       <c r="I85" s="11" t="s">
         <v>8</v>
       </c>
@@ -25336,26 +25338,26 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="27" customHeight="1">
-      <c r="A86" s="537"/>
-      <c r="B86" s="547" t="s">
+      <c r="A86" s="533"/>
+      <c r="B86" s="549" t="s">
         <v>771</v>
       </c>
-      <c r="C86" s="549" t="s">
+      <c r="C86" s="551" t="s">
         <v>772</v>
       </c>
       <c r="D86" s="309" t="s">
         <v>773</v>
       </c>
-      <c r="E86" s="549" t="s">
+      <c r="E86" s="551" t="s">
         <v>772</v>
       </c>
-      <c r="F86" s="551" t="s">
+      <c r="F86" s="553" t="s">
         <v>775</v>
       </c>
-      <c r="G86" s="553" t="s">
+      <c r="G86" s="555" t="s">
         <v>772</v>
       </c>
-      <c r="H86" s="555" t="s">
+      <c r="H86" s="557" t="s">
         <v>775</v>
       </c>
       <c r="I86" s="30" t="s">
@@ -25367,15 +25369,15 @@
     </row>
     <row r="87" spans="1:10" ht="15.75" thickBot="1">
       <c r="A87" s="456"/>
-      <c r="B87" s="548"/>
-      <c r="C87" s="550"/>
+      <c r="B87" s="550"/>
+      <c r="C87" s="552"/>
       <c r="D87" s="310" t="s">
         <v>774</v>
       </c>
-      <c r="E87" s="550"/>
-      <c r="F87" s="552"/>
-      <c r="G87" s="554"/>
-      <c r="H87" s="556"/>
+      <c r="E87" s="552"/>
+      <c r="F87" s="554"/>
+      <c r="G87" s="556"/>
+      <c r="H87" s="558"/>
       <c r="I87" s="30" t="s">
         <v>782</v>
       </c>
@@ -25798,16 +25800,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A41:A44"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="E85:F85"/>
     <mergeCell ref="G85:H85"/>
@@ -25817,6 +25809,16 @@
     <mergeCell ref="F86:F87"/>
     <mergeCell ref="G86:G87"/>
     <mergeCell ref="H86:H87"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26188,7 +26190,7 @@
       <c r="A19" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="428" t="s">
+      <c r="B19" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="46" t="s">
@@ -26206,7 +26208,7 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
       <c r="A20" s="456"/>
-      <c r="B20" s="429"/>
+      <c r="B20" s="437"/>
       <c r="C20" s="135" t="s">
         <v>591</v>
       </c>
@@ -26369,7 +26371,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="420" t="s">
+      <c r="A29" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B29" s="7">
@@ -26389,7 +26391,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="421"/>
+      <c r="A30" s="428"/>
       <c r="B30" s="7">
         <v>2007</v>
       </c>
@@ -26407,7 +26409,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="421"/>
+      <c r="A31" s="428"/>
       <c r="B31" s="7">
         <v>2014</v>
       </c>
@@ -26425,7 +26427,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="422"/>
+      <c r="A32" s="429"/>
       <c r="B32" s="69">
         <v>2021</v>
       </c>
@@ -26443,7 +26445,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="423" t="s">
+      <c r="A33" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B33" s="20">
@@ -26463,7 +26465,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A34" s="424"/>
+      <c r="A34" s="431"/>
       <c r="B34" s="20">
         <v>2007</v>
       </c>
@@ -26481,7 +26483,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A35" s="424"/>
+      <c r="A35" s="431"/>
       <c r="B35" s="20">
         <v>2014</v>
       </c>
@@ -26499,7 +26501,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A36" s="439"/>
+      <c r="A36" s="432"/>
       <c r="B36" s="20">
         <v>2021</v>
       </c>
@@ -26517,7 +26519,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A37" s="420" t="s">
+      <c r="A37" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B37" s="7">
@@ -26537,7 +26539,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A38" s="421"/>
+      <c r="A38" s="428"/>
       <c r="B38" s="7">
         <v>2007</v>
       </c>
@@ -26555,7 +26557,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A39" s="421"/>
+      <c r="A39" s="428"/>
       <c r="B39" s="7">
         <v>2014</v>
       </c>
@@ -26573,7 +26575,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A40" s="422"/>
+      <c r="A40" s="429"/>
       <c r="B40" s="69">
         <v>2021</v>
       </c>
@@ -26591,7 +26593,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A41" s="423" t="s">
+      <c r="A41" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="20">
@@ -26611,7 +26613,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A42" s="424"/>
+      <c r="A42" s="431"/>
       <c r="B42" s="20">
         <v>2007</v>
       </c>
@@ -26629,7 +26631,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A43" s="424"/>
+      <c r="A43" s="431"/>
       <c r="B43" s="20">
         <v>2014</v>
       </c>
@@ -26647,7 +26649,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A44" s="425"/>
+      <c r="A44" s="433"/>
       <c r="B44" s="24">
         <v>2021</v>
       </c>
@@ -26777,10 +26779,10 @@
       <c r="B52" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="C52" s="428" t="s">
+      <c r="C52" s="436" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="430" t="s">
+      <c r="D52" s="438" t="s">
         <v>603</v>
       </c>
       <c r="E52" s="11" t="s">
@@ -26795,8 +26797,8 @@
       <c r="B53" s="135" t="s">
         <v>602</v>
       </c>
-      <c r="C53" s="429"/>
-      <c r="D53" s="431"/>
+      <c r="C53" s="437"/>
+      <c r="D53" s="439"/>
       <c r="E53" s="30" t="s">
         <v>51</v>
       </c>
@@ -27542,7 +27544,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A14" s="449" t="s">
+      <c r="A14" s="440" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="7">
@@ -27562,7 +27564,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A15" s="450"/>
+      <c r="A15" s="441"/>
       <c r="B15" s="7">
         <v>2007</v>
       </c>
@@ -27580,7 +27582,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A16" s="450"/>
+      <c r="A16" s="441"/>
       <c r="B16" s="7">
         <v>2014</v>
       </c>
@@ -27598,7 +27600,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A17" s="451"/>
+      <c r="A17" s="442"/>
       <c r="B17" s="7">
         <v>2021</v>
       </c>
@@ -27616,7 +27618,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="452" t="s">
+      <c r="A18" s="443" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="20">
@@ -27636,7 +27638,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="453"/>
+      <c r="A19" s="444"/>
       <c r="B19" s="20">
         <v>2007</v>
       </c>
@@ -27654,7 +27656,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="453"/>
+      <c r="A20" s="444"/>
       <c r="B20" s="20">
         <v>2014</v>
       </c>
@@ -27672,7 +27674,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="454"/>
+      <c r="A21" s="445"/>
       <c r="B21" s="20">
         <v>2021</v>
       </c>
@@ -27690,7 +27692,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="420" t="s">
+      <c r="A22" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="7">
@@ -27710,7 +27712,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="421"/>
+      <c r="A23" s="428"/>
       <c r="B23" s="7">
         <v>2007</v>
       </c>
@@ -27728,7 +27730,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="421"/>
+      <c r="A24" s="428"/>
       <c r="B24" s="7">
         <v>2014</v>
       </c>
@@ -27746,7 +27748,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="444"/>
+      <c r="A25" s="446"/>
       <c r="B25" s="7">
         <v>2021</v>
       </c>
@@ -27764,7 +27766,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="452" t="s">
+      <c r="A26" s="443" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="20">
@@ -27784,7 +27786,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="453"/>
+      <c r="A27" s="444"/>
       <c r="B27" s="20">
         <v>2007</v>
       </c>
@@ -27802,7 +27804,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A28" s="453"/>
+      <c r="A28" s="444"/>
       <c r="B28" s="20">
         <v>2014</v>
       </c>
@@ -27820,7 +27822,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="454"/>
+      <c r="A29" s="445"/>
       <c r="B29" s="20">
         <v>2021</v>
       </c>
@@ -27838,7 +27840,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="420" t="s">
+      <c r="A30" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="7">
@@ -27858,7 +27860,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="421"/>
+      <c r="A31" s="428"/>
       <c r="B31" s="7">
         <v>2007</v>
       </c>
@@ -27876,7 +27878,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A32" s="421"/>
+      <c r="A32" s="428"/>
       <c r="B32" s="7">
         <v>2014</v>
       </c>
@@ -27894,7 +27896,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="444"/>
+      <c r="A33" s="446"/>
       <c r="B33" s="7">
         <v>2021</v>
       </c>
@@ -27912,7 +27914,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A34" s="445" t="s">
+      <c r="A34" s="451" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="20">
@@ -27932,7 +27934,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A35" s="424"/>
+      <c r="A35" s="431"/>
       <c r="B35" s="20">
         <v>2007</v>
       </c>
@@ -27950,7 +27952,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A36" s="424"/>
+      <c r="A36" s="431"/>
       <c r="B36" s="20">
         <v>2014</v>
       </c>
@@ -27968,7 +27970,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A37" s="425"/>
+      <c r="A37" s="433"/>
       <c r="B37" s="24">
         <v>2021</v>
       </c>
@@ -28215,13 +28217,13 @@
       <c r="H50" s="31"/>
     </row>
     <row r="51" spans="1:10" ht="24">
-      <c r="A51" s="426" t="s">
+      <c r="A51" s="434" t="s">
         <v>12</v>
       </c>
       <c r="B51" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C51" s="447" t="s">
+      <c r="C51" s="453" t="s">
         <v>44</v>
       </c>
       <c r="D51" s="47" t="s">
@@ -28237,11 +28239,11 @@
       <c r="H51" s="31"/>
     </row>
     <row r="52" spans="1:10" ht="18.75" thickBot="1">
-      <c r="A52" s="446"/>
+      <c r="A52" s="452"/>
       <c r="B52" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="448"/>
+      <c r="C52" s="454"/>
       <c r="D52" s="48" t="s">
         <v>46</v>
       </c>
@@ -28930,19 +28932,19 @@
       <c r="A81" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="440">
+      <c r="B81" s="447">
         <v>0.248</v>
       </c>
-      <c r="C81" s="440">
+      <c r="C81" s="447">
         <v>0.08</v>
       </c>
-      <c r="D81" s="440">
+      <c r="D81" s="447">
         <v>0.152</v>
       </c>
-      <c r="E81" s="440">
+      <c r="E81" s="447">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F81" s="442">
+      <c r="F81" s="449">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="G81" s="30" t="s">
@@ -28956,11 +28958,11 @@
       <c r="A82" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="B82" s="441"/>
-      <c r="C82" s="441"/>
-      <c r="D82" s="441"/>
-      <c r="E82" s="441"/>
-      <c r="F82" s="443"/>
+      <c r="B82" s="448"/>
+      <c r="C82" s="448"/>
+      <c r="D82" s="448"/>
+      <c r="E82" s="448"/>
+      <c r="F82" s="450"/>
       <c r="G82" s="30" t="s">
         <v>69</v>
       </c>
@@ -29035,11 +29037,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="D81:D82"/>
     <mergeCell ref="E81:E82"/>
     <mergeCell ref="F81:F82"/>
     <mergeCell ref="A30:A33"/>
@@ -29048,6 +29045,11 @@
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="B81:B82"/>
     <mergeCell ref="C81:C82"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="D81:D82"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29375,7 +29377,7 @@
       <c r="A17" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="428" t="s">
+      <c r="B17" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="46" t="s">
@@ -29393,7 +29395,7 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
       <c r="A18" s="456"/>
-      <c r="B18" s="429"/>
+      <c r="B18" s="437"/>
       <c r="C18" s="135" t="s">
         <v>808</v>
       </c>
@@ -29953,10 +29955,10 @@
       <c r="B50" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="C50" s="428" t="s">
+      <c r="C50" s="436" t="s">
         <v>44</v>
       </c>
-      <c r="D50" s="430" t="s">
+      <c r="D50" s="438" t="s">
         <v>814</v>
       </c>
       <c r="E50" s="11" t="s">
@@ -29971,8 +29973,8 @@
       <c r="B51" s="135" t="s">
         <v>813</v>
       </c>
-      <c r="C51" s="429"/>
-      <c r="D51" s="431"/>
+      <c r="C51" s="437"/>
+      <c r="D51" s="439"/>
       <c r="E51" s="30" t="s">
         <v>51</v>
       </c>
@@ -30368,17 +30370,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30397,7 +30399,7 @@
       <c r="B1" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="430" t="s">
+      <c r="C1" s="438" t="s">
         <v>826</v>
       </c>
       <c r="D1" s="11" t="s">
@@ -30412,7 +30414,7 @@
       <c r="B2" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="431"/>
+      <c r="C2" s="439"/>
       <c r="D2" s="30" t="s">
         <v>829</v>
       </c>
@@ -30544,11 +30546,11 @@
       <c r="A12" s="562" t="s">
         <v>171</v>
       </c>
-      <c r="B12" s="528"/>
+      <c r="B12" s="521"/>
       <c r="C12" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="430" t="s">
+      <c r="D12" s="438" t="s">
         <v>831</v>
       </c>
       <c r="E12" s="11" t="s">
@@ -30560,11 +30562,11 @@
     </row>
     <row r="13" spans="1:6" ht="27.75" thickBot="1">
       <c r="A13" s="563"/>
-      <c r="B13" s="530"/>
+      <c r="B13" s="523"/>
       <c r="C13" s="135" t="s">
         <v>830</v>
       </c>
-      <c r="D13" s="431"/>
+      <c r="D13" s="439"/>
       <c r="E13" s="30" t="s">
         <v>26</v>
       </c>
@@ -31459,10 +31461,10 @@
     </row>
     <row r="60" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="61" spans="1:9" ht="24.75" thickBot="1">
-      <c r="A61" s="514" t="s">
+      <c r="A61" s="505" t="s">
         <v>851</v>
       </c>
-      <c r="B61" s="515"/>
+      <c r="B61" s="506"/>
       <c r="C61" s="232" t="s">
         <v>852</v>
       </c>
@@ -31667,17 +31669,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:A29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31690,10 +31692,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="566" t="s">
+      <c r="B1" s="564" t="s">
         <v>1174</v>
       </c>
-      <c r="C1" s="509"/>
+      <c r="C1" s="511"/>
       <c r="D1" s="3">
         <v>2018</v>
       </c>
@@ -32063,14 +32065,14 @@
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="16" spans="1:9" ht="24">
-      <c r="A16" s="467"/>
-      <c r="B16" s="567" t="s">
+      <c r="A16" s="462"/>
+      <c r="B16" s="565" t="s">
         <v>1188</v>
       </c>
       <c r="C16" s="46" t="s">
         <v>1189</v>
       </c>
-      <c r="D16" s="569" t="s">
+      <c r="D16" s="567" t="s">
         <v>1191</v>
       </c>
       <c r="E16" s="11" t="s">
@@ -32082,11 +32084,11 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1">
       <c r="A17" s="479"/>
-      <c r="B17" s="568"/>
+      <c r="B17" s="566"/>
       <c r="C17" s="135" t="s">
         <v>1190</v>
       </c>
-      <c r="D17" s="570"/>
+      <c r="D17" s="568"/>
       <c r="E17" s="30" t="s">
         <v>1192</v>
       </c>
@@ -32520,7 +32522,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="571" t="s">
+      <c r="A47" s="569" t="s">
         <v>16</v>
       </c>
       <c r="B47" s="219">
@@ -32540,7 +32542,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="557"/>
+      <c r="A48" s="547"/>
       <c r="B48" s="7">
         <v>2007</v>
       </c>
@@ -32558,7 +32560,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="557"/>
+      <c r="A49" s="547"/>
       <c r="B49" s="7">
         <v>2014</v>
       </c>
@@ -32576,7 +32578,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="558"/>
+      <c r="A50" s="548"/>
       <c r="B50" s="69">
         <v>2021</v>
       </c>
@@ -32594,7 +32596,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="423" t="s">
+      <c r="A51" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B51" s="20">
@@ -32614,7 +32616,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="424"/>
+      <c r="A52" s="431"/>
       <c r="B52" s="20">
         <v>2007</v>
       </c>
@@ -32632,7 +32634,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="424"/>
+      <c r="A53" s="431"/>
       <c r="B53" s="20">
         <v>2014</v>
       </c>
@@ -32650,7 +32652,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="439"/>
+      <c r="A54" s="432"/>
       <c r="B54" s="20">
         <v>2021</v>
       </c>
@@ -32668,7 +32670,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="420" t="s">
+      <c r="A55" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B55" s="7">
@@ -32688,7 +32690,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="421"/>
+      <c r="A56" s="428"/>
       <c r="B56" s="7">
         <v>2007</v>
       </c>
@@ -32706,7 +32708,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="421"/>
+      <c r="A57" s="428"/>
       <c r="B57" s="7">
         <v>2014</v>
       </c>
@@ -32724,7 +32726,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="422"/>
+      <c r="A58" s="429"/>
       <c r="B58" s="69">
         <v>2021</v>
       </c>
@@ -32742,7 +32744,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="423" t="s">
+      <c r="A59" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B59" s="20">
@@ -32762,7 +32764,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="424"/>
+      <c r="A60" s="431"/>
       <c r="B60" s="20">
         <v>2007</v>
       </c>
@@ -32780,7 +32782,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="424"/>
+      <c r="A61" s="431"/>
       <c r="B61" s="20">
         <v>2014</v>
       </c>
@@ -32798,7 +32800,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="439"/>
+      <c r="A62" s="432"/>
       <c r="B62" s="20">
         <v>2021</v>
       </c>
@@ -32816,7 +32818,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="420" t="s">
+      <c r="A63" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B63" s="7">
@@ -32836,7 +32838,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="421"/>
+      <c r="A64" s="428"/>
       <c r="B64" s="7">
         <v>2007</v>
       </c>
@@ -32854,7 +32856,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A65" s="421"/>
+      <c r="A65" s="428"/>
       <c r="B65" s="7">
         <v>2014</v>
       </c>
@@ -32872,7 +32874,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A66" s="422"/>
+      <c r="A66" s="429"/>
       <c r="B66" s="69">
         <v>2021</v>
       </c>
@@ -32890,7 +32892,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A67" s="423" t="s">
+      <c r="A67" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="20">
@@ -32910,7 +32912,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A68" s="424"/>
+      <c r="A68" s="431"/>
       <c r="B68" s="20">
         <v>2007</v>
       </c>
@@ -32928,7 +32930,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A69" s="424"/>
+      <c r="A69" s="431"/>
       <c r="B69" s="20">
         <v>2014</v>
       </c>
@@ -32946,7 +32948,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A70" s="425"/>
+      <c r="A70" s="433"/>
       <c r="B70" s="24">
         <v>2021</v>
       </c>
@@ -32974,7 +32976,7 @@
       <c r="C73" s="501" t="s">
         <v>44</v>
       </c>
-      <c r="D73" s="564" t="s">
+      <c r="D73" s="570" t="s">
         <v>1204</v>
       </c>
       <c r="E73" s="11" t="s">
@@ -32990,7 +32992,7 @@
         <v>1203</v>
       </c>
       <c r="C74" s="502"/>
-      <c r="D74" s="565"/>
+      <c r="D74" s="571"/>
       <c r="E74" s="30" t="s">
         <v>1205</v>
       </c>
@@ -33123,7 +33125,7 @@
       <c r="A83" s="455" t="s">
         <v>556</v>
       </c>
-      <c r="B83" s="428" t="s">
+      <c r="B83" s="436" t="s">
         <v>1207</v>
       </c>
       <c r="C83" s="359" t="s">
@@ -33138,7 +33140,7 @@
     </row>
     <row r="84" spans="1:5" ht="36.75" thickBot="1">
       <c r="A84" s="456"/>
-      <c r="B84" s="429"/>
+      <c r="B84" s="437"/>
       <c r="C84" s="38" t="s">
         <v>1209</v>
       </c>
@@ -33355,12 +33357,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A47:A50"/>
     <mergeCell ref="D73:D74"/>
     <mergeCell ref="A83:A84"/>
     <mergeCell ref="B83:B84"/>
@@ -33370,6 +33366,12 @@
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="A73:A74"/>
     <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A47:A50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33718,7 +33720,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11" ht="22.5">
-      <c r="A1" s="585"/>
+      <c r="A1" s="573"/>
       <c r="B1" s="308" t="s">
         <v>199</v>
       </c>
@@ -33734,7 +33736,7 @@
       <c r="F1" s="572" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="586" t="s">
+      <c r="G1" s="574" t="s">
         <v>76</v>
       </c>
       <c r="H1" s="572" t="s">
@@ -33749,7 +33751,7 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="585"/>
+      <c r="A2" s="573"/>
       <c r="B2" s="308" t="s">
         <v>200</v>
       </c>
@@ -33759,7 +33761,7 @@
       </c>
       <c r="E2" s="572"/>
       <c r="F2" s="572"/>
-      <c r="G2" s="586"/>
+      <c r="G2" s="574"/>
       <c r="H2" s="308" t="s">
         <v>1239</v>
       </c>
@@ -35377,7 +35379,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A55" s="581" t="s">
+      <c r="A55" s="575" t="s">
         <v>1242</v>
       </c>
       <c r="B55" s="382">
@@ -35409,7 +35411,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A56" s="582"/>
+      <c r="A56" s="576"/>
       <c r="B56" s="376">
         <v>2014</v>
       </c>
@@ -35439,7 +35441,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A57" s="583"/>
+      <c r="A57" s="577"/>
       <c r="B57" s="376">
         <v>2021</v>
       </c>
@@ -35469,7 +35471,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A58" s="579" t="s">
+      <c r="A58" s="578" t="s">
         <v>1247</v>
       </c>
       <c r="B58" s="378">
@@ -35501,7 +35503,7 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A59" s="574"/>
+      <c r="A59" s="579"/>
       <c r="B59" s="378">
         <v>2014</v>
       </c>
@@ -35561,7 +35563,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A61" s="581" t="s">
+      <c r="A61" s="575" t="s">
         <v>1244</v>
       </c>
       <c r="B61" s="376">
@@ -35593,7 +35595,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A62" s="582"/>
+      <c r="A62" s="576"/>
       <c r="B62" s="376">
         <v>2014</v>
       </c>
@@ -35623,7 +35625,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A63" s="583"/>
+      <c r="A63" s="577"/>
       <c r="B63" s="376">
         <v>2021</v>
       </c>
@@ -35653,7 +35655,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A64" s="579" t="s">
+      <c r="A64" s="578" t="s">
         <v>1240</v>
       </c>
       <c r="B64" s="378">
@@ -35685,7 +35687,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A65" s="574"/>
+      <c r="A65" s="579"/>
       <c r="B65" s="378">
         <v>2014</v>
       </c>
@@ -35745,7 +35747,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A67" s="581" t="s">
+      <c r="A67" s="575" t="s">
         <v>1249</v>
       </c>
       <c r="B67" s="376">
@@ -35777,7 +35779,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A68" s="582"/>
+      <c r="A68" s="576"/>
       <c r="B68" s="376">
         <v>2014</v>
       </c>
@@ -35807,7 +35809,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A69" s="583"/>
+      <c r="A69" s="577"/>
       <c r="B69" s="376">
         <v>2021</v>
       </c>
@@ -35837,7 +35839,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A70" s="579" t="s">
+      <c r="A70" s="578" t="s">
         <v>1243</v>
       </c>
       <c r="B70" s="378">
@@ -35869,7 +35871,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A71" s="574"/>
+      <c r="A71" s="579"/>
       <c r="B71" s="378">
         <v>2014</v>
       </c>
@@ -35929,7 +35931,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A73" s="581" t="s">
+      <c r="A73" s="575" t="s">
         <v>1251</v>
       </c>
       <c r="B73" s="376">
@@ -35961,7 +35963,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A74" s="582"/>
+      <c r="A74" s="576"/>
       <c r="B74" s="376">
         <v>2014</v>
       </c>
@@ -35991,7 +35993,7 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A75" s="583"/>
+      <c r="A75" s="577"/>
       <c r="B75" s="376">
         <v>2021</v>
       </c>
@@ -36021,7 +36023,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A76" s="579" t="s">
+      <c r="A76" s="578" t="s">
         <v>1241</v>
       </c>
       <c r="B76" s="378">
@@ -36053,7 +36055,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A77" s="574"/>
+      <c r="A77" s="579"/>
       <c r="B77" s="378">
         <v>2014</v>
       </c>
@@ -36113,7 +36115,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A79" s="581" t="s">
+      <c r="A79" s="575" t="s">
         <v>1259</v>
       </c>
       <c r="B79" s="376">
@@ -36145,7 +36147,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A80" s="582"/>
+      <c r="A80" s="576"/>
       <c r="B80" s="376">
         <v>2014</v>
       </c>
@@ -36175,7 +36177,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A81" s="583"/>
+      <c r="A81" s="577"/>
       <c r="B81" s="376">
         <v>2021</v>
       </c>
@@ -36205,7 +36207,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A82" s="579" t="s">
+      <c r="A82" s="578" t="s">
         <v>66</v>
       </c>
       <c r="B82" s="378">
@@ -36237,7 +36239,7 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A83" s="574"/>
+      <c r="A83" s="579"/>
       <c r="B83" s="378">
         <v>2014</v>
       </c>
@@ -36297,7 +36299,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A85" s="581" t="s">
+      <c r="A85" s="575" t="s">
         <v>1252</v>
       </c>
       <c r="B85" s="376">
@@ -36329,7 +36331,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A86" s="582"/>
+      <c r="A86" s="576"/>
       <c r="B86" s="376">
         <v>2014</v>
       </c>
@@ -36359,7 +36361,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A87" s="583"/>
+      <c r="A87" s="577"/>
       <c r="B87" s="376">
         <v>2021</v>
       </c>
@@ -36389,7 +36391,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A88" s="581" t="s">
+      <c r="A88" s="575" t="s">
         <v>1254</v>
       </c>
       <c r="B88" s="382">
@@ -36421,7 +36423,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A89" s="582"/>
+      <c r="A89" s="576"/>
       <c r="B89" s="376">
         <v>2014</v>
       </c>
@@ -36451,7 +36453,7 @@
       </c>
     </row>
     <row r="90" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A90" s="583"/>
+      <c r="A90" s="577"/>
       <c r="B90" s="376">
         <v>2021</v>
       </c>
@@ -36481,7 +36483,7 @@
       </c>
     </row>
     <row r="91" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A91" s="579" t="s">
+      <c r="A91" s="578" t="s">
         <v>1248</v>
       </c>
       <c r="B91" s="378">
@@ -36513,7 +36515,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A92" s="574"/>
+      <c r="A92" s="579"/>
       <c r="B92" s="378">
         <v>2014</v>
       </c>
@@ -36573,7 +36575,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A94" s="581" t="s">
+      <c r="A94" s="575" t="s">
         <v>1250</v>
       </c>
       <c r="B94" s="376">
@@ -36605,7 +36607,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A95" s="582"/>
+      <c r="A95" s="576"/>
       <c r="B95" s="376">
         <v>2014</v>
       </c>
@@ -36635,7 +36637,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A96" s="583"/>
+      <c r="A96" s="577"/>
       <c r="B96" s="376">
         <v>2021</v>
       </c>
@@ -36665,7 +36667,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A97" s="579" t="s">
+      <c r="A97" s="578" t="s">
         <v>1246</v>
       </c>
       <c r="B97" s="378">
@@ -36697,7 +36699,7 @@
       </c>
     </row>
     <row r="98" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A98" s="574"/>
+      <c r="A98" s="579"/>
       <c r="B98" s="378">
         <v>2014</v>
       </c>
@@ -36851,7 +36853,7 @@
       </c>
     </row>
     <row r="103" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A103" s="579" t="s">
+      <c r="A103" s="578" t="s">
         <v>1253</v>
       </c>
       <c r="B103" s="378">
@@ -36883,7 +36885,7 @@
       </c>
     </row>
     <row r="104" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A104" s="574"/>
+      <c r="A104" s="579"/>
       <c r="B104" s="378">
         <v>2014</v>
       </c>
@@ -36943,7 +36945,7 @@
       </c>
     </row>
     <row r="106" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A106" s="581" t="s">
+      <c r="A106" s="575" t="s">
         <v>1264</v>
       </c>
       <c r="B106" s="376">
@@ -36975,7 +36977,7 @@
       </c>
     </row>
     <row r="107" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A107" s="582"/>
+      <c r="A107" s="576"/>
       <c r="B107" s="376">
         <v>2014</v>
       </c>
@@ -37005,7 +37007,7 @@
       </c>
     </row>
     <row r="108" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A108" s="583"/>
+      <c r="A108" s="577"/>
       <c r="B108" s="376">
         <v>2021</v>
       </c>
@@ -37035,7 +37037,7 @@
       </c>
     </row>
     <row r="109" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A109" s="579" t="s">
+      <c r="A109" s="578" t="s">
         <v>1245</v>
       </c>
       <c r="B109" s="378">
@@ -37067,7 +37069,7 @@
       </c>
     </row>
     <row r="110" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A110" s="574"/>
+      <c r="A110" s="579"/>
       <c r="B110" s="378">
         <v>2014</v>
       </c>
@@ -37127,7 +37129,7 @@
       </c>
     </row>
     <row r="112" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A112" s="581" t="s">
+      <c r="A112" s="575" t="s">
         <v>1276</v>
       </c>
       <c r="B112" s="376">
@@ -37159,7 +37161,7 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A113" s="582"/>
+      <c r="A113" s="576"/>
       <c r="B113" s="376">
         <v>2014</v>
       </c>
@@ -37189,7 +37191,7 @@
       </c>
     </row>
     <row r="114" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A114" s="583"/>
+      <c r="A114" s="577"/>
       <c r="B114" s="376">
         <v>2021</v>
       </c>
@@ -37219,7 +37221,7 @@
       </c>
     </row>
     <row r="115" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A115" s="579" t="s">
+      <c r="A115" s="578" t="s">
         <v>1255</v>
       </c>
       <c r="B115" s="378">
@@ -37251,7 +37253,7 @@
       </c>
     </row>
     <row r="116" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A116" s="574"/>
+      <c r="A116" s="579"/>
       <c r="B116" s="378">
         <v>2014</v>
       </c>
@@ -37311,7 +37313,7 @@
       </c>
     </row>
     <row r="118" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A118" s="581" t="s">
+      <c r="A118" s="575" t="s">
         <v>1277</v>
       </c>
       <c r="B118" s="376">
@@ -37343,7 +37345,7 @@
       </c>
     </row>
     <row r="119" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A119" s="582"/>
+      <c r="A119" s="576"/>
       <c r="B119" s="376">
         <v>2014</v>
       </c>
@@ -37373,7 +37375,7 @@
       </c>
     </row>
     <row r="120" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A120" s="583"/>
+      <c r="A120" s="577"/>
       <c r="B120" s="376">
         <v>2021</v>
       </c>
@@ -37403,11 +37405,11 @@
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="584"/>
+      <c r="A123" s="581"/>
       <c r="B123" s="308" t="s">
         <v>1278</v>
       </c>
-      <c r="C123" s="578" t="s">
+      <c r="C123" s="586" t="s">
         <v>1280</v>
       </c>
       <c r="D123" s="308" t="s">
@@ -37433,11 +37435,11 @@
       </c>
     </row>
     <row r="124" spans="1:10" ht="47.25">
-      <c r="A124" s="584"/>
+      <c r="A124" s="581"/>
       <c r="B124" s="386" t="s">
         <v>1279</v>
       </c>
-      <c r="C124" s="578"/>
+      <c r="C124" s="586"/>
       <c r="D124" s="313" t="s">
         <v>1282</v>
       </c>
@@ -37457,9 +37459,9 @@
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="584"/>
+      <c r="A125" s="581"/>
       <c r="B125" s="387"/>
-      <c r="C125" s="578"/>
+      <c r="C125" s="586"/>
       <c r="D125" s="388"/>
       <c r="E125" s="313" t="s">
         <v>1282</v>
@@ -37920,25 +37922,25 @@
       <c r="A140" s="389" t="s">
         <v>1303</v>
       </c>
-      <c r="B140" s="573">
+      <c r="B140" s="582">
         <v>1182000</v>
       </c>
-      <c r="C140" s="574" t="s">
+      <c r="C140" s="579" t="s">
         <v>50</v>
       </c>
-      <c r="D140" s="575">
+      <c r="D140" s="583">
         <v>1182000</v>
       </c>
-      <c r="E140" s="576" t="s">
+      <c r="E140" s="584" t="s">
         <v>50</v>
       </c>
-      <c r="F140" s="576" t="s">
+      <c r="F140" s="584" t="s">
         <v>217</v>
       </c>
-      <c r="G140" s="576">
+      <c r="G140" s="584">
         <v>2019</v>
       </c>
-      <c r="H140" s="577" t="s">
+      <c r="H140" s="585" t="s">
         <v>1300</v>
       </c>
       <c r="I140" s="30" t="s">
@@ -37952,13 +37954,13 @@
       <c r="A141" s="389" t="s">
         <v>1304</v>
       </c>
-      <c r="B141" s="573"/>
-      <c r="C141" s="574"/>
-      <c r="D141" s="575"/>
-      <c r="E141" s="576"/>
-      <c r="F141" s="576"/>
-      <c r="G141" s="576"/>
-      <c r="H141" s="577"/>
+      <c r="B141" s="582"/>
+      <c r="C141" s="579"/>
+      <c r="D141" s="583"/>
+      <c r="E141" s="584"/>
+      <c r="F141" s="584"/>
+      <c r="G141" s="584"/>
+      <c r="H141" s="585"/>
       <c r="I141" s="30" t="s">
         <v>1297</v>
       </c>
@@ -38064,17 +38066,21 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="G123:G125"/>
+    <mergeCell ref="H123:H125"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="F140:F141"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="C123:C125"/>
+    <mergeCell ref="A109:A111"/>
+    <mergeCell ref="A112:A114"/>
+    <mergeCell ref="A115:A117"/>
+    <mergeCell ref="A118:A120"/>
+    <mergeCell ref="A123:A125"/>
     <mergeCell ref="A106:A108"/>
     <mergeCell ref="A70:A72"/>
     <mergeCell ref="A73:A75"/>
@@ -38087,21 +38093,17 @@
     <mergeCell ref="A94:A96"/>
     <mergeCell ref="A97:A99"/>
     <mergeCell ref="A103:A105"/>
-    <mergeCell ref="A109:A111"/>
-    <mergeCell ref="A112:A114"/>
-    <mergeCell ref="A115:A117"/>
-    <mergeCell ref="A118:A120"/>
-    <mergeCell ref="A123:A125"/>
-    <mergeCell ref="G123:G125"/>
-    <mergeCell ref="H123:H125"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="F140:F141"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="H140:H141"/>
-    <mergeCell ref="C123:C125"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39482,7 +39484,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A18" s="423" t="s">
+      <c r="A18" s="430" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="20">
@@ -39502,7 +39504,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A19" s="424"/>
+      <c r="A19" s="431"/>
       <c r="B19" s="20">
         <v>2007</v>
       </c>
@@ -39520,7 +39522,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="424"/>
+      <c r="A20" s="431"/>
       <c r="B20" s="20">
         <v>2014</v>
       </c>
@@ -39538,7 +39540,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A21" s="439"/>
+      <c r="A21" s="432"/>
       <c r="B21" s="20">
         <v>2021</v>
       </c>
@@ -39556,7 +39558,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A22" s="420" t="s">
+      <c r="A22" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="7">
@@ -39576,7 +39578,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A23" s="421"/>
+      <c r="A23" s="428"/>
       <c r="B23" s="7">
         <v>2007</v>
       </c>
@@ -39594,7 +39596,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A24" s="421"/>
+      <c r="A24" s="428"/>
       <c r="B24" s="7">
         <v>2014</v>
       </c>
@@ -39612,7 +39614,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A25" s="422"/>
+      <c r="A25" s="429"/>
       <c r="B25" s="69">
         <v>2021</v>
       </c>
@@ -39630,7 +39632,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A26" s="423" t="s">
+      <c r="A26" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="20">
@@ -39650,7 +39652,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A27" s="424"/>
+      <c r="A27" s="431"/>
       <c r="B27" s="20">
         <v>2007</v>
       </c>
@@ -39668,7 +39670,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="424"/>
+      <c r="A28" s="431"/>
       <c r="B28" s="20">
         <v>2014</v>
       </c>
@@ -39686,7 +39688,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="424"/>
+      <c r="A29" s="431"/>
       <c r="B29" s="20">
         <v>2021</v>
       </c>
@@ -39704,7 +39706,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="421" t="s">
+      <c r="A30" s="428" t="s">
         <v>20</v>
       </c>
       <c r="B30" s="7">
@@ -39724,7 +39726,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="421"/>
+      <c r="A31" s="428"/>
       <c r="B31" s="7">
         <v>2007</v>
       </c>
@@ -39742,7 +39744,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="421"/>
+      <c r="A32" s="428"/>
       <c r="B32" s="7">
         <v>2014</v>
       </c>
@@ -39760,7 +39762,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A33" s="422"/>
+      <c r="A33" s="429"/>
       <c r="B33" s="69">
         <v>2021</v>
       </c>
@@ -39778,7 +39780,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="423" t="s">
+      <c r="A34" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="20">
@@ -39798,7 +39800,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A35" s="424"/>
+      <c r="A35" s="431"/>
       <c r="B35" s="20">
         <v>2007</v>
       </c>
@@ -39816,7 +39818,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A36" s="424"/>
+      <c r="A36" s="431"/>
       <c r="B36" s="20">
         <v>2014</v>
       </c>
@@ -39834,7 +39836,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A37" s="439"/>
+      <c r="A37" s="432"/>
       <c r="B37" s="20">
         <v>2021</v>
       </c>
@@ -41008,24 +41010,24 @@
     </row>
     <row r="29" spans="1:10" ht="15.75" thickBot="1"/>
     <row r="30" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A30" s="467"/>
-      <c r="B30" s="469">
+      <c r="A30" s="462"/>
+      <c r="B30" s="464">
         <v>2017</v>
       </c>
-      <c r="C30" s="469">
+      <c r="C30" s="464">
         <v>2018</v>
       </c>
-      <c r="D30" s="471">
+      <c r="D30" s="466">
         <v>2019</v>
       </c>
-      <c r="E30" s="466">
+      <c r="E30" s="471">
         <v>2020</v>
       </c>
-      <c r="F30" s="465"/>
-      <c r="G30" s="463">
+      <c r="F30" s="470"/>
+      <c r="G30" s="468">
         <v>2021</v>
       </c>
-      <c r="H30" s="464"/>
+      <c r="H30" s="469"/>
       <c r="I30" s="11" t="s">
         <v>8</v>
       </c>
@@ -41034,10 +41036,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A31" s="468"/>
-      <c r="B31" s="470"/>
-      <c r="C31" s="470"/>
-      <c r="D31" s="472"/>
+      <c r="A31" s="463"/>
+      <c r="B31" s="465"/>
+      <c r="C31" s="465"/>
+      <c r="D31" s="467"/>
       <c r="E31" s="333" t="s">
         <v>948</v>
       </c>
@@ -41379,17 +41381,17 @@
     </row>
     <row r="43" spans="1:10" ht="15.75" thickBot="1"/>
     <row r="44" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A44" s="426" t="s">
+      <c r="A44" s="434" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="463" t="s">
+      <c r="B44" s="468" t="s">
         <v>611</v>
       </c>
-      <c r="C44" s="465"/>
+      <c r="C44" s="470"/>
       <c r="D44" s="98" t="s">
         <v>953</v>
       </c>
-      <c r="E44" s="430" t="s">
+      <c r="E44" s="438" t="s">
         <v>928</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -41400,7 +41402,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A45" s="427"/>
+      <c r="A45" s="435"/>
       <c r="B45" s="173" t="s">
         <v>955</v>
       </c>
@@ -41410,7 +41412,7 @@
       <c r="D45" s="135" t="s">
         <v>954</v>
       </c>
-      <c r="E45" s="431"/>
+      <c r="E45" s="439"/>
       <c r="F45" s="54" t="s">
         <v>966</v>
       </c>
@@ -41703,7 +41705,7 @@
       <c r="A65" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B65" s="428" t="s">
+      <c r="B65" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="46" t="s">
@@ -41721,7 +41723,7 @@
     </row>
     <row r="66" spans="1:6" ht="15.75" thickBot="1">
       <c r="A66" s="456"/>
-      <c r="B66" s="429"/>
+      <c r="B66" s="437"/>
       <c r="C66" s="135" t="s">
         <v>197</v>
       </c>
@@ -41736,7 +41738,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A67" s="420" t="s">
+      <c r="A67" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B67" s="7">
@@ -41756,7 +41758,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A68" s="421"/>
+      <c r="A68" s="428"/>
       <c r="B68" s="7">
         <v>2007</v>
       </c>
@@ -41774,7 +41776,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A69" s="421"/>
+      <c r="A69" s="428"/>
       <c r="B69" s="7">
         <v>2014</v>
       </c>
@@ -41792,7 +41794,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A70" s="422"/>
+      <c r="A70" s="429"/>
       <c r="B70" s="69">
         <v>2021</v>
       </c>
@@ -41810,7 +41812,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A71" s="423" t="s">
+      <c r="A71" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B71" s="20">
@@ -41830,7 +41832,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A72" s="424"/>
+      <c r="A72" s="431"/>
       <c r="B72" s="20">
         <v>2007</v>
       </c>
@@ -41848,7 +41850,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A73" s="424"/>
+      <c r="A73" s="431"/>
       <c r="B73" s="20">
         <v>2014</v>
       </c>
@@ -41866,7 +41868,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A74" s="439"/>
+      <c r="A74" s="432"/>
       <c r="B74" s="20">
         <v>2021</v>
       </c>
@@ -41884,7 +41886,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A75" s="449" t="s">
+      <c r="A75" s="440" t="s">
         <v>18</v>
       </c>
       <c r="B75" s="7">
@@ -41904,7 +41906,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A76" s="450"/>
+      <c r="A76" s="441"/>
       <c r="B76" s="7">
         <v>2007</v>
       </c>
@@ -41922,7 +41924,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A77" s="450"/>
+      <c r="A77" s="441"/>
       <c r="B77" s="7">
         <v>2014</v>
       </c>
@@ -41940,7 +41942,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A78" s="462"/>
+      <c r="A78" s="472"/>
       <c r="B78" s="69">
         <v>2021</v>
       </c>
@@ -41958,7 +41960,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A79" s="423" t="s">
+      <c r="A79" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B79" s="20">
@@ -41978,7 +41980,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A80" s="424"/>
+      <c r="A80" s="431"/>
       <c r="B80" s="20">
         <v>2007</v>
       </c>
@@ -41996,7 +41998,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A81" s="424"/>
+      <c r="A81" s="431"/>
       <c r="B81" s="20">
         <v>2014</v>
       </c>
@@ -42014,7 +42016,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A82" s="439"/>
+      <c r="A82" s="432"/>
       <c r="B82" s="20">
         <v>2021</v>
       </c>
@@ -42032,7 +42034,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A83" s="420" t="s">
+      <c r="A83" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B83" s="7">
@@ -42052,7 +42054,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A84" s="421"/>
+      <c r="A84" s="428"/>
       <c r="B84" s="7">
         <v>2007</v>
       </c>
@@ -42070,7 +42072,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A85" s="421"/>
+      <c r="A85" s="428"/>
       <c r="B85" s="7">
         <v>2014</v>
       </c>
@@ -42088,7 +42090,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A86" s="422"/>
+      <c r="A86" s="429"/>
       <c r="B86" s="69">
         <v>2021</v>
       </c>
@@ -42106,7 +42108,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A87" s="423" t="s">
+      <c r="A87" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B87" s="20">
@@ -42126,7 +42128,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A88" s="424"/>
+      <c r="A88" s="431"/>
       <c r="B88" s="20">
         <v>2007</v>
       </c>
@@ -42144,7 +42146,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="24.75" thickBot="1">
-      <c r="A89" s="424"/>
+      <c r="A89" s="431"/>
       <c r="B89" s="20">
         <v>2014</v>
       </c>
@@ -42162,7 +42164,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.75" thickBot="1">
-      <c r="A90" s="425"/>
+      <c r="A90" s="433"/>
       <c r="B90" s="24">
         <v>2021</v>
       </c>
@@ -42187,7 +42189,7 @@
       <c r="B93" s="98" t="s">
         <v>285</v>
       </c>
-      <c r="C93" s="428" t="s">
+      <c r="C93" s="436" t="s">
         <v>44</v>
       </c>
       <c r="D93" s="47" t="s">
@@ -42205,7 +42207,7 @@
       <c r="B94" s="135" t="s">
         <v>976</v>
       </c>
-      <c r="C94" s="429"/>
+      <c r="C94" s="437"/>
       <c r="D94" s="136" t="s">
         <v>921</v>
       </c>
@@ -42773,18 +42775,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="E30:F30"/>
     <mergeCell ref="A93:A94"/>
     <mergeCell ref="C93:C94"/>
     <mergeCell ref="A67:A70"/>
@@ -42793,6 +42783,18 @@
     <mergeCell ref="A79:A82"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="A87:A90"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -43358,7 +43360,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A26" s="420" t="s">
+      <c r="A26" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B26" s="69">
@@ -43378,7 +43380,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A27" s="421"/>
+      <c r="A27" s="428"/>
       <c r="B27" s="69">
         <v>2007</v>
       </c>
@@ -43396,7 +43398,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A28" s="421"/>
+      <c r="A28" s="428"/>
       <c r="B28" s="69">
         <v>2014</v>
       </c>
@@ -43414,7 +43416,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A29" s="422"/>
+      <c r="A29" s="429"/>
       <c r="B29" s="69">
         <v>2021</v>
       </c>
@@ -43432,7 +43434,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A30" s="423" t="s">
+      <c r="A30" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B30" s="20">
@@ -43452,7 +43454,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A31" s="424"/>
+      <c r="A31" s="431"/>
       <c r="B31" s="20">
         <v>2007</v>
       </c>
@@ -43470,7 +43472,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A32" s="424"/>
+      <c r="A32" s="431"/>
       <c r="B32" s="20">
         <v>2014</v>
       </c>
@@ -43488,7 +43490,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="439"/>
+      <c r="A33" s="432"/>
       <c r="B33" s="20">
         <v>2021</v>
       </c>
@@ -43506,7 +43508,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="420" t="s">
+      <c r="A34" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B34" s="69">
@@ -43526,7 +43528,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="421"/>
+      <c r="A35" s="428"/>
       <c r="B35" s="69">
         <v>2007</v>
       </c>
@@ -43544,7 +43546,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="421"/>
+      <c r="A36" s="428"/>
       <c r="B36" s="69">
         <v>2014</v>
       </c>
@@ -43562,7 +43564,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="422"/>
+      <c r="A37" s="429"/>
       <c r="B37" s="69">
         <v>2021</v>
       </c>
@@ -43580,7 +43582,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="423" t="s">
+      <c r="A38" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="20">
@@ -43600,7 +43602,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="424"/>
+      <c r="A39" s="431"/>
       <c r="B39" s="20">
         <v>2007</v>
       </c>
@@ -43618,7 +43620,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="424"/>
+      <c r="A40" s="431"/>
       <c r="B40" s="20">
         <v>2014</v>
       </c>
@@ -43636,7 +43638,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="425"/>
+      <c r="A41" s="433"/>
       <c r="B41" s="24">
         <v>2021</v>
       </c>
@@ -43654,7 +43656,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="477" t="s">
+      <c r="A42" s="474" t="s">
         <v>20</v>
       </c>
       <c r="B42" s="69">
@@ -43674,7 +43676,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="421"/>
+      <c r="A43" s="428"/>
       <c r="B43" s="69">
         <v>2007</v>
       </c>
@@ -43692,7 +43694,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="421"/>
+      <c r="A44" s="428"/>
       <c r="B44" s="69">
         <v>2014</v>
       </c>
@@ -43710,7 +43712,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="422"/>
+      <c r="A45" s="429"/>
       <c r="B45" s="69">
         <v>2021</v>
       </c>
@@ -43728,7 +43730,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="423" t="s">
+      <c r="A46" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="20">
@@ -43748,7 +43750,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="424"/>
+      <c r="A47" s="431"/>
       <c r="B47" s="20">
         <v>2007</v>
       </c>
@@ -43766,7 +43768,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="424"/>
+      <c r="A48" s="431"/>
       <c r="B48" s="20">
         <v>2014</v>
       </c>
@@ -43784,7 +43786,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A49" s="425"/>
+      <c r="A49" s="433"/>
       <c r="B49" s="24">
         <v>2021</v>
       </c>
@@ -44060,7 +44062,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A65" s="473" t="s">
+      <c r="A65" s="475" t="s">
         <v>138</v>
       </c>
       <c r="B65" s="104" t="s">
@@ -44089,7 +44091,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A66" s="474"/>
+      <c r="A66" s="476"/>
       <c r="B66" s="104" t="s">
         <v>140</v>
       </c>
@@ -44116,7 +44118,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A67" s="475" t="s">
+      <c r="A67" s="473" t="s">
         <v>141</v>
       </c>
       <c r="B67" s="107" t="s">
@@ -44172,7 +44174,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A69" s="473" t="s">
+      <c r="A69" s="475" t="s">
         <v>142</v>
       </c>
       <c r="B69" s="104" t="s">
@@ -44201,7 +44203,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A70" s="474"/>
+      <c r="A70" s="476"/>
       <c r="B70" s="104" t="s">
         <v>140</v>
       </c>
@@ -44228,7 +44230,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A71" s="475" t="s">
+      <c r="A71" s="473" t="s">
         <v>143</v>
       </c>
       <c r="B71" s="101" t="s">
@@ -44284,7 +44286,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A73" s="473" t="s">
+      <c r="A73" s="475" t="s">
         <v>144</v>
       </c>
       <c r="B73" s="104" t="s">
@@ -44313,7 +44315,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A74" s="474"/>
+      <c r="A74" s="476"/>
       <c r="B74" s="104" t="s">
         <v>140</v>
       </c>
@@ -44340,7 +44342,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A75" s="475" t="s">
+      <c r="A75" s="473" t="s">
         <v>145</v>
       </c>
       <c r="B75" s="101" t="s">
@@ -44396,7 +44398,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A77" s="473" t="s">
+      <c r="A77" s="475" t="s">
         <v>146</v>
       </c>
       <c r="B77" s="104" t="s">
@@ -44425,7 +44427,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A78" s="474"/>
+      <c r="A78" s="476"/>
       <c r="B78" s="104" t="s">
         <v>140</v>
       </c>
@@ -44452,7 +44454,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A79" s="475" t="s">
+      <c r="A79" s="473" t="s">
         <v>147</v>
       </c>
       <c r="B79" s="101" t="s">
@@ -44508,7 +44510,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="44.25" customHeight="1" thickBot="1">
-      <c r="A81" s="473" t="s">
+      <c r="A81" s="475" t="s">
         <v>148</v>
       </c>
       <c r="B81" s="104" t="s">
@@ -44537,7 +44539,7 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A82" s="476"/>
+      <c r="A82" s="477"/>
       <c r="B82" s="128" t="s">
         <v>140</v>
       </c>
@@ -44565,6 +44567,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A81:A82"/>
     <mergeCell ref="A71:A72"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A30:A33"/>
@@ -44575,11 +44582,6 @@
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="A81:A82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44591,7 +44593,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="36">
-      <c r="A1" s="467"/>
+      <c r="A1" s="462"/>
       <c r="B1" s="44" t="s">
         <v>1000</v>
       </c>
@@ -45021,7 +45023,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="420" t="s">
+      <c r="A31" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="7">
@@ -45041,7 +45043,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="421"/>
+      <c r="A32" s="428"/>
       <c r="B32" s="7">
         <v>2007</v>
       </c>
@@ -45059,7 +45061,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="421"/>
+      <c r="A33" s="428"/>
       <c r="B33" s="7">
         <v>2014</v>
       </c>
@@ -45077,7 +45079,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="422"/>
+      <c r="A34" s="429"/>
       <c r="B34" s="69">
         <v>2021</v>
       </c>
@@ -45169,7 +45171,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="420" t="s">
+      <c r="A39" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="7">
@@ -45189,7 +45191,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="421"/>
+      <c r="A40" s="428"/>
       <c r="B40" s="7">
         <v>2007</v>
       </c>
@@ -45207,7 +45209,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="421"/>
+      <c r="A41" s="428"/>
       <c r="B41" s="7">
         <v>2014</v>
       </c>
@@ -45225,7 +45227,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="422"/>
+      <c r="A42" s="429"/>
       <c r="B42" s="69">
         <v>2021</v>
       </c>
@@ -45317,7 +45319,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="420" t="s">
+      <c r="A47" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B47" s="7">
@@ -45337,7 +45339,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="421"/>
+      <c r="A48" s="428"/>
       <c r="B48" s="7">
         <v>2007</v>
       </c>
@@ -45355,7 +45357,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="421"/>
+      <c r="A49" s="428"/>
       <c r="B49" s="7">
         <v>2014</v>
       </c>
@@ -45373,7 +45375,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="422"/>
+      <c r="A50" s="429"/>
       <c r="B50" s="69">
         <v>2021</v>
       </c>
@@ -45391,7 +45393,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="423" t="s">
+      <c r="A51" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="20">
@@ -45411,7 +45413,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="424"/>
+      <c r="A52" s="431"/>
       <c r="B52" s="20">
         <v>2007</v>
       </c>
@@ -45429,7 +45431,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="424"/>
+      <c r="A53" s="431"/>
       <c r="B53" s="20">
         <v>2014</v>
       </c>
@@ -45447,7 +45449,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="425"/>
+      <c r="A54" s="433"/>
       <c r="B54" s="24">
         <v>2021</v>
       </c>
@@ -45466,13 +45468,13 @@
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="57" spans="1:6" ht="48">
-      <c r="A57" s="426" t="s">
+      <c r="A57" s="434" t="s">
         <v>12</v>
       </c>
       <c r="B57" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="447" t="s">
+      <c r="C57" s="453" t="s">
         <v>44</v>
       </c>
       <c r="D57" s="47" t="s">
@@ -45486,7 +45488,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="18.75" thickBot="1">
-      <c r="A58" s="427"/>
+      <c r="A58" s="435"/>
       <c r="B58" s="178" t="s">
         <v>1013</v>
       </c>
@@ -45640,8 +45642,23 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568532B4-8586-4B07-A82E-C3B89C9AD92E}">
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1" s="2"/>
@@ -46042,13 +46059,13 @@
       <c r="A22" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="428" t="s">
+      <c r="B22" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D22" s="430" t="s">
+      <c r="D22" s="438" t="s">
         <v>198</v>
       </c>
       <c r="E22" s="11" t="s">
@@ -46060,11 +46077,11 @@
     </row>
     <row r="23" spans="1:6" ht="27.75" thickBot="1">
       <c r="A23" s="456"/>
-      <c r="B23" s="429"/>
+      <c r="B23" s="437"/>
       <c r="C23" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="431"/>
+      <c r="D23" s="439"/>
       <c r="E23" s="30" t="s">
         <v>26</v>
       </c>
@@ -46149,7 +46166,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A28" s="423" t="s">
+      <c r="A28" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="20">
@@ -46169,7 +46186,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A29" s="424"/>
+      <c r="A29" s="431"/>
       <c r="B29" s="20">
         <v>2007</v>
       </c>
@@ -46187,7 +46204,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A30" s="424"/>
+      <c r="A30" s="431"/>
       <c r="B30" s="20">
         <v>2014</v>
       </c>
@@ -46205,7 +46222,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A31" s="439"/>
+      <c r="A31" s="432"/>
       <c r="B31" s="20">
         <v>2021</v>
       </c>
@@ -46223,7 +46240,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A32" s="420" t="s">
+      <c r="A32" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B32" s="7">
@@ -46243,7 +46260,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A33" s="421"/>
+      <c r="A33" s="428"/>
       <c r="B33" s="7">
         <v>2007</v>
       </c>
@@ -46261,7 +46278,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A34" s="421"/>
+      <c r="A34" s="428"/>
       <c r="B34" s="7">
         <v>2014</v>
       </c>
@@ -46279,7 +46296,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A35" s="422"/>
+      <c r="A35" s="429"/>
       <c r="B35" s="69">
         <v>2021</v>
       </c>
@@ -46297,7 +46314,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A36" s="423" t="s">
+      <c r="A36" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B36" s="20">
@@ -46317,7 +46334,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A37" s="424"/>
+      <c r="A37" s="431"/>
       <c r="B37" s="20">
         <v>2007</v>
       </c>
@@ -46335,7 +46352,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A38" s="424"/>
+      <c r="A38" s="431"/>
       <c r="B38" s="20">
         <v>2014</v>
       </c>
@@ -46353,7 +46370,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A39" s="439"/>
+      <c r="A39" s="432"/>
       <c r="B39" s="20">
         <v>2021</v>
       </c>
@@ -46371,7 +46388,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A40" s="420" t="s">
+      <c r="A40" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B40" s="7">
@@ -46391,7 +46408,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A41" s="421"/>
+      <c r="A41" s="428"/>
       <c r="B41" s="7">
         <v>2007</v>
       </c>
@@ -46409,7 +46426,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A42" s="421"/>
+      <c r="A42" s="428"/>
       <c r="B42" s="7">
         <v>2014</v>
       </c>
@@ -46427,14 +46444,14 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A43" s="421"/>
-      <c r="B43" s="7">
-        <v>2016</v>
-      </c>
-      <c r="C43" s="7">
-        <v>0</v>
-      </c>
-      <c r="D43" s="12">
+      <c r="A43" s="429"/>
+      <c r="B43" s="69">
+        <v>2021</v>
+      </c>
+      <c r="C43" s="69">
+        <v>0</v>
+      </c>
+      <c r="D43" s="51">
         <v>0</v>
       </c>
       <c r="E43" s="30" t="s">
@@ -46445,15 +46462,17 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A44" s="422"/>
-      <c r="B44" s="69">
-        <v>2021</v>
-      </c>
-      <c r="C44" s="69">
-        <v>0</v>
-      </c>
-      <c r="D44" s="51">
-        <v>0</v>
+      <c r="A44" s="430" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="20">
+        <v>1999</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>21</v>
       </c>
       <c r="E44" s="30" t="s">
         <v>26</v>
@@ -46462,18 +46481,16 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="423" t="s">
-        <v>22</v>
-      </c>
+    <row r="45" spans="1:6" ht="36.75" thickBot="1">
+      <c r="A45" s="431"/>
       <c r="B45" s="20">
-        <v>1999</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>21</v>
+        <v>2007</v>
+      </c>
+      <c r="C45" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" s="21">
+        <v>90000</v>
       </c>
       <c r="E45" s="30" t="s">
         <v>26</v>
@@ -46483,15 +46500,15 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A46" s="424"/>
+      <c r="A46" s="431"/>
       <c r="B46" s="20">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C46" s="144" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D46" s="21">
-        <v>90000</v>
+        <v>289757</v>
       </c>
       <c r="E46" s="30" t="s">
         <v>26</v>
@@ -46500,16 +46517,16 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="36.75" thickBot="1">
-      <c r="A47" s="424"/>
-      <c r="B47" s="20">
-        <v>2014</v>
-      </c>
-      <c r="C47" s="144" t="s">
-        <v>202</v>
-      </c>
-      <c r="D47" s="21">
-        <v>289757</v>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A47" s="433"/>
+      <c r="B47" s="24">
+        <v>2021</v>
+      </c>
+      <c r="C47" s="24">
+        <v>2</v>
+      </c>
+      <c r="D47" s="25">
+        <v>10000</v>
       </c>
       <c r="E47" s="30" t="s">
         <v>26</v>
@@ -46518,67 +46535,75 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="425"/>
-      <c r="B48" s="24">
-        <v>2021</v>
-      </c>
-      <c r="C48" s="24">
-        <v>2</v>
-      </c>
-      <c r="D48" s="25">
-        <v>10000</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="F48" s="141" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1"/>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3">
+    <row r="48" spans="1:6" ht="15.75" thickBot="1"/>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3">
         <v>2017</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G49" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H49" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="60.75" thickBot="1">
+    <row r="50" spans="1:8" ht="60.75" thickBot="1">
+      <c r="A50" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B50" s="119">
+        <v>5678</v>
+      </c>
+      <c r="C50" s="119">
+        <v>6183</v>
+      </c>
+      <c r="D50" s="119">
+        <v>5924</v>
+      </c>
+      <c r="E50" s="84">
+        <v>6403</v>
+      </c>
+      <c r="F50" s="120">
+        <v>5959</v>
+      </c>
+      <c r="G50" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="H50" s="141" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="24.75" thickBot="1">
       <c r="A51" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="B51" s="119">
-        <v>5678</v>
-      </c>
-      <c r="C51" s="119">
-        <v>6183</v>
-      </c>
-      <c r="D51" s="119">
-        <v>5924</v>
-      </c>
-      <c r="E51" s="84">
-        <v>6403</v>
-      </c>
-      <c r="F51" s="120">
-        <v>5959</v>
+        <v>208</v>
+      </c>
+      <c r="B51" s="147">
+        <v>75</v>
+      </c>
+      <c r="C51" s="86">
+        <v>75</v>
+      </c>
+      <c r="D51" s="86">
+        <v>75</v>
+      </c>
+      <c r="E51" s="86">
+        <v>75</v>
+      </c>
+      <c r="F51" s="137">
+        <v>75</v>
       </c>
       <c r="G51" s="30" t="s">
         <v>213</v>
@@ -46587,24 +46612,24 @@
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="24.75" thickBot="1">
+    <row r="52" spans="1:8" ht="60.75" thickBot="1">
       <c r="A52" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="B52" s="147">
-        <v>75</v>
-      </c>
-      <c r="C52" s="86">
-        <v>75</v>
-      </c>
-      <c r="D52" s="86">
-        <v>75</v>
-      </c>
-      <c r="E52" s="86">
-        <v>75</v>
-      </c>
-      <c r="F52" s="137">
-        <v>75</v>
+        <v>209</v>
+      </c>
+      <c r="B52" s="119">
+        <v>9464</v>
+      </c>
+      <c r="C52" s="119">
+        <v>10305</v>
+      </c>
+      <c r="D52" s="119">
+        <v>9874</v>
+      </c>
+      <c r="E52" s="119">
+        <v>10672</v>
+      </c>
+      <c r="F52" s="120">
+        <v>9932</v>
       </c>
       <c r="G52" s="30" t="s">
         <v>213</v>
@@ -46613,24 +46638,24 @@
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="60.75" thickBot="1">
+    <row r="53" spans="1:8" ht="36.75" thickBot="1">
       <c r="A53" s="40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B53" s="119">
-        <v>9464</v>
+        <v>4973</v>
       </c>
       <c r="C53" s="119">
-        <v>10305</v>
+        <v>10229</v>
       </c>
       <c r="D53" s="119">
-        <v>9874</v>
-      </c>
-      <c r="E53" s="119">
-        <v>10672</v>
+        <v>9306</v>
+      </c>
+      <c r="E53" s="84">
+        <v>6223</v>
       </c>
       <c r="F53" s="120">
-        <v>9932</v>
+        <v>8226</v>
       </c>
       <c r="G53" s="30" t="s">
         <v>213</v>
@@ -46639,24 +46664,24 @@
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="36.75" thickBot="1">
+    <row r="54" spans="1:8" ht="48.75" thickBot="1">
       <c r="A54" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="B54" s="119">
-        <v>4973</v>
+        <v>211</v>
+      </c>
+      <c r="B54" s="8">
+        <v>22207</v>
       </c>
       <c r="C54" s="119">
-        <v>10229</v>
+        <v>26792</v>
       </c>
       <c r="D54" s="119">
-        <v>9306</v>
-      </c>
-      <c r="E54" s="84">
-        <v>6223</v>
-      </c>
-      <c r="F54" s="120">
-        <v>8226</v>
+        <v>25179</v>
+      </c>
+      <c r="E54" s="119">
+        <v>23373</v>
+      </c>
+      <c r="F54" s="68">
+        <v>24192</v>
       </c>
       <c r="G54" s="30" t="s">
         <v>213</v>
@@ -46667,22 +46692,22 @@
     </row>
     <row r="55" spans="1:8" ht="48.75" thickBot="1">
       <c r="A55" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="B55" s="8">
-        <v>22207</v>
-      </c>
-      <c r="C55" s="119">
-        <v>26792</v>
-      </c>
-      <c r="D55" s="119">
-        <v>25179</v>
+        <v>212</v>
+      </c>
+      <c r="B55" s="121">
+        <v>245532</v>
+      </c>
+      <c r="C55" s="8">
+        <v>262640</v>
+      </c>
+      <c r="D55" s="8">
+        <v>252344</v>
       </c>
       <c r="E55" s="119">
-        <v>23373</v>
+        <v>258139</v>
       </c>
       <c r="F55" s="68">
-        <v>24192</v>
+        <v>302793</v>
       </c>
       <c r="G55" s="30" t="s">
         <v>213</v>
@@ -46691,24 +46716,24 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="48.75" thickBot="1">
-      <c r="A56" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="B56" s="121">
-        <v>245532</v>
-      </c>
-      <c r="C56" s="8">
-        <v>262640</v>
-      </c>
-      <c r="D56" s="8">
-        <v>252344</v>
-      </c>
-      <c r="E56" s="119">
-        <v>258139</v>
-      </c>
-      <c r="F56" s="68">
-        <v>302793</v>
+    <row r="56" spans="1:8" ht="36.75" thickBot="1">
+      <c r="A56" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="148">
+        <v>0.09</v>
+      </c>
+      <c r="C56" s="148">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="D56" s="148">
+        <v>0.1</v>
+      </c>
+      <c r="E56" s="149">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="F56" s="139">
+        <v>0.08</v>
       </c>
       <c r="G56" s="30" t="s">
         <v>213</v>
@@ -46717,65 +46742,59 @@
         <v>214</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="36.75" thickBot="1">
-      <c r="A57" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="148">
-        <v>0.09</v>
-      </c>
-      <c r="C57" s="148">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="D57" s="148">
-        <v>0.1</v>
-      </c>
-      <c r="E57" s="149">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="F57" s="139">
-        <v>0.08</v>
-      </c>
-      <c r="G57" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="H57" s="141" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1"/>
-    <row r="59" spans="1:8" ht="48.75" thickBot="1">
-      <c r="A59" s="71" t="s">
+    <row r="57" spans="1:8" ht="15.75" thickBot="1"/>
+    <row r="58" spans="1:8" ht="48.75" thickBot="1">
+      <c r="A58" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F58" s="11" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="36.75" thickBot="1">
+      <c r="A59" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="8">
+        <v>31000000</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="D59" s="19">
+        <v>20150000</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" s="141" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="36.75" thickBot="1">
       <c r="A60" s="40" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B60" s="8">
-        <v>31000000</v>
+        <v>30000000</v>
       </c>
       <c r="C60" s="7">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="D60" s="19">
-        <v>20150000</v>
+        <v>27000000</v>
       </c>
       <c r="E60" s="30" t="s">
         <v>51</v>
@@ -46786,16 +46805,16 @@
     </row>
     <row r="61" spans="1:8" ht="36.75" thickBot="1">
       <c r="A61" s="40" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B61" s="8">
-        <v>30000000</v>
+        <v>131789</v>
       </c>
       <c r="C61" s="7">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="D61" s="19">
-        <v>27000000</v>
+        <v>26358</v>
       </c>
       <c r="E61" s="30" t="s">
         <v>51</v>
@@ -46804,18 +46823,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="36.75" thickBot="1">
+    <row r="62" spans="1:8" ht="24.75" thickBot="1">
       <c r="A62" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="B62" s="8">
-        <v>131789</v>
-      </c>
-      <c r="C62" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="D62" s="19">
-        <v>26358</v>
+        <v>20</v>
+      </c>
+      <c r="B62" s="7">
+        <v>0</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" s="12">
+        <v>0</v>
       </c>
       <c r="E62" s="30" t="s">
         <v>51</v>
@@ -46826,16 +46845,16 @@
     </row>
     <row r="63" spans="1:8" ht="24.75" thickBot="1">
       <c r="A63" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B63" s="7">
-        <v>0</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D63" s="12">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="B63" s="8">
+        <v>10000</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="D63" s="19">
+        <v>7200</v>
       </c>
       <c r="E63" s="30" t="s">
         <v>51</v>
@@ -46844,18 +46863,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="24.75" thickBot="1">
-      <c r="A64" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B64" s="8">
-        <v>10000</v>
-      </c>
-      <c r="C64" s="7">
-        <v>0.72</v>
-      </c>
-      <c r="D64" s="19">
-        <v>7200</v>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A64" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="80">
+        <v>61141789</v>
+      </c>
+      <c r="C64" s="69" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" s="50">
+        <v>47183558</v>
       </c>
       <c r="E64" s="30" t="s">
         <v>51</v>
@@ -46864,69 +46883,75 @@
         <v>218</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A65" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="B65" s="80">
-        <v>61141789</v>
-      </c>
-      <c r="C65" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="D65" s="50">
-        <v>47183558</v>
-      </c>
-      <c r="E65" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F65" s="141" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="15.75" thickBot="1"/>
+    <row r="65" spans="1:13" ht="15.75" thickBot="1"/>
+    <row r="66" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3">
+        <v>2017</v>
+      </c>
+      <c r="C66" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D66" s="3">
+        <v>2019</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2020</v>
+      </c>
+      <c r="F66" s="5">
+        <v>2021</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="67" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="3">
-        <v>2017</v>
-      </c>
-      <c r="C67" s="3">
-        <v>2018</v>
-      </c>
-      <c r="D67" s="3">
-        <v>2019</v>
-      </c>
-      <c r="E67" s="3">
-        <v>2020</v>
-      </c>
-      <c r="F67" s="5">
-        <v>2021</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>27</v>
+      <c r="A67" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B67" s="119">
+        <v>4395</v>
+      </c>
+      <c r="C67" s="119">
+        <v>4704</v>
+      </c>
+      <c r="D67" s="119">
+        <v>9882</v>
+      </c>
+      <c r="E67" s="119">
+        <v>6633</v>
+      </c>
+      <c r="F67" s="68">
+        <v>3537</v>
+      </c>
+      <c r="G67" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="141" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="15.75" thickBot="1">
       <c r="A68" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="B68" s="119">
-        <v>4395</v>
-      </c>
-      <c r="C68" s="119">
-        <v>4704</v>
-      </c>
-      <c r="D68" s="119">
-        <v>9882</v>
-      </c>
-      <c r="E68" s="119">
-        <v>6633</v>
-      </c>
-      <c r="F68" s="68">
-        <v>3537</v>
+        <v>165</v>
+      </c>
+      <c r="B68" s="114">
+        <v>96</v>
+      </c>
+      <c r="C68" s="114">
+        <v>0</v>
+      </c>
+      <c r="D68" s="114">
+        <v>0</v>
+      </c>
+      <c r="E68" s="114">
+        <v>0</v>
+      </c>
+      <c r="F68" s="150">
+        <v>0</v>
       </c>
       <c r="G68" s="30" t="s">
         <v>224</v>
@@ -46935,24 +46960,24 @@
         <v>219</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.75" thickBot="1">
+    <row r="69" spans="1:13" ht="36.75" thickBot="1">
       <c r="A69" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="B69" s="114">
-        <v>96</v>
-      </c>
-      <c r="C69" s="114">
-        <v>0</v>
-      </c>
-      <c r="D69" s="114">
-        <v>0</v>
-      </c>
-      <c r="E69" s="114">
-        <v>0</v>
-      </c>
-      <c r="F69" s="150">
-        <v>0</v>
+        <v>221</v>
+      </c>
+      <c r="B69" s="119">
+        <v>4491</v>
+      </c>
+      <c r="C69" s="119">
+        <v>4704</v>
+      </c>
+      <c r="D69" s="119">
+        <v>9882</v>
+      </c>
+      <c r="E69" s="119">
+        <v>6633</v>
+      </c>
+      <c r="F69" s="68">
+        <v>3537</v>
       </c>
       <c r="G69" s="30" t="s">
         <v>224</v>
@@ -46963,22 +46988,22 @@
     </row>
     <row r="70" spans="1:13" ht="36.75" thickBot="1">
       <c r="A70" s="40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B70" s="119">
-        <v>4491</v>
+        <v>15935</v>
       </c>
       <c r="C70" s="119">
-        <v>4704</v>
+        <v>8915</v>
       </c>
       <c r="D70" s="119">
-        <v>9882</v>
+        <v>12901</v>
       </c>
       <c r="E70" s="119">
-        <v>6633</v>
+        <v>11359</v>
       </c>
       <c r="F70" s="68">
-        <v>3537</v>
+        <v>11512</v>
       </c>
       <c r="G70" s="30" t="s">
         <v>224</v>
@@ -46987,24 +47012,24 @@
         <v>219</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="36.75" thickBot="1">
-      <c r="A71" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="B71" s="119">
-        <v>15935</v>
-      </c>
-      <c r="C71" s="119">
-        <v>8915</v>
-      </c>
-      <c r="D71" s="119">
-        <v>12901</v>
-      </c>
-      <c r="E71" s="119">
-        <v>11359</v>
-      </c>
-      <c r="F71" s="68">
-        <v>11512</v>
+    <row r="71" spans="1:13" ht="60.75" thickBot="1">
+      <c r="A71" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="B71" s="148">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="C71" s="148">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="D71" s="148">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="E71" s="148">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="F71" s="151">
+        <v>0.307</v>
       </c>
       <c r="G71" s="30" t="s">
         <v>224</v>
@@ -47013,73 +47038,88 @@
         <v>219</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="60.75" thickBot="1">
-      <c r="A72" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="B72" s="148">
-        <v>0.28199999999999997</v>
-      </c>
-      <c r="C72" s="148">
-        <v>0.52800000000000002</v>
-      </c>
-      <c r="D72" s="148">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="E72" s="148">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="F72" s="151">
-        <v>0.307</v>
-      </c>
-      <c r="G72" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H72" s="141" t="s">
-        <v>219</v>
+    <row r="73" spans="1:13">
+      <c r="B73" t="s">
+        <v>245</v>
+      </c>
+      <c r="C73" t="s">
+        <v>246</v>
+      </c>
+      <c r="D73" t="s">
+        <v>247</v>
+      </c>
+      <c r="E73" t="s">
+        <v>248</v>
+      </c>
+      <c r="F73" t="s">
+        <v>249</v>
+      </c>
+      <c r="G73" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="H73" t="s">
+        <v>251</v>
+      </c>
+      <c r="I73" t="s">
+        <v>252</v>
+      </c>
+      <c r="J73" t="s">
+        <v>253</v>
+      </c>
+      <c r="K73" t="s">
+        <v>75</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:13">
-      <c r="B74" t="s">
-        <v>245</v>
-      </c>
-      <c r="C74" t="s">
-        <v>246</v>
-      </c>
-      <c r="D74" t="s">
-        <v>247</v>
-      </c>
-      <c r="E74" t="s">
-        <v>248</v>
-      </c>
-      <c r="F74" t="s">
-        <v>249</v>
-      </c>
-      <c r="G74" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="H74" t="s">
-        <v>251</v>
-      </c>
-      <c r="I74" t="s">
-        <v>252</v>
-      </c>
-      <c r="J74" t="s">
-        <v>253</v>
-      </c>
-      <c r="K74" t="s">
-        <v>75</v>
-      </c>
-      <c r="L74" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="M74" s="11" t="s">
-        <v>27</v>
+      <c r="A74" t="s">
+        <v>225</v>
+      </c>
+      <c r="L74" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="M74" s="141" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>226</v>
+      </c>
+      <c r="B75" s="146">
+        <v>1226</v>
+      </c>
+      <c r="C75">
+        <v>451</v>
+      </c>
+      <c r="D75">
+        <v>195</v>
+      </c>
+      <c r="E75">
+        <v>130</v>
+      </c>
+      <c r="F75">
+        <v>77</v>
+      </c>
+      <c r="G75">
+        <v>332</v>
+      </c>
+      <c r="H75">
+        <v>22</v>
+      </c>
+      <c r="I75">
+        <v>37</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>514</v>
       </c>
       <c r="L75" s="30" t="s">
         <v>254</v>
@@ -47090,37 +47130,37 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B76" s="146">
-        <v>1226</v>
+        <v>1399</v>
       </c>
       <c r="C76">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D76">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="E76">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F76">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="G76">
-        <v>332</v>
+        <v>580</v>
       </c>
       <c r="H76">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I76">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K76">
-        <v>514</v>
+        <v>321</v>
       </c>
       <c r="L76" s="30" t="s">
         <v>254</v>
@@ -47131,37 +47171,37 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>227</v>
-      </c>
-      <c r="B77" s="146">
-        <v>1399</v>
+        <v>228</v>
+      </c>
+      <c r="B77">
+        <v>879</v>
       </c>
       <c r="C77">
-        <v>463</v>
+        <v>170</v>
       </c>
       <c r="D77">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="E77">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="F77">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G77">
-        <v>580</v>
+        <v>366</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I77">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="J77">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K77">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="L77" s="30" t="s">
         <v>254</v>
@@ -47172,37 +47212,37 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" t="s">
-        <v>228</v>
-      </c>
-      <c r="B78">
-        <v>879</v>
+        <v>229</v>
+      </c>
+      <c r="B78" s="146">
+        <v>1366</v>
       </c>
       <c r="C78">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="D78">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="E78">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F78">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G78">
-        <v>366</v>
+        <v>478</v>
       </c>
       <c r="H78">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="I78">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="J78">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K78">
-        <v>289</v>
+        <v>370</v>
       </c>
       <c r="L78" s="30" t="s">
         <v>254</v>
@@ -47213,37 +47253,37 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" t="s">
-        <v>229</v>
-      </c>
-      <c r="B79" s="146">
-        <v>1366</v>
+        <v>230</v>
+      </c>
+      <c r="B79">
+        <v>519</v>
       </c>
       <c r="C79">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="D79">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="E79">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="F79">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G79">
-        <v>478</v>
+        <v>11</v>
       </c>
       <c r="H79">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I79">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K79">
-        <v>370</v>
+        <v>39</v>
       </c>
       <c r="L79" s="30" t="s">
         <v>254</v>
@@ -47254,37 +47294,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" t="s">
-        <v>230</v>
-      </c>
-      <c r="B80">
-        <v>519</v>
-      </c>
-      <c r="C80">
-        <v>88</v>
-      </c>
-      <c r="D80">
-        <v>18</v>
-      </c>
-      <c r="E80">
-        <v>5</v>
-      </c>
-      <c r="F80">
-        <v>13</v>
-      </c>
-      <c r="G80">
-        <v>11</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>9</v>
-      </c>
-      <c r="K80">
-        <v>39</v>
+        <v>231</v>
       </c>
       <c r="L80" s="30" t="s">
         <v>254</v>
@@ -47295,7 +47305,37 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>231</v>
+        <v>232</v>
+      </c>
+      <c r="B81" s="146">
+        <v>1226</v>
+      </c>
+      <c r="C81">
+        <v>451</v>
+      </c>
+      <c r="D81">
+        <v>195</v>
+      </c>
+      <c r="E81">
+        <v>130</v>
+      </c>
+      <c r="F81">
+        <v>77</v>
+      </c>
+      <c r="G81">
+        <v>332</v>
+      </c>
+      <c r="H81">
+        <v>22</v>
+      </c>
+      <c r="I81">
+        <v>37</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>514</v>
       </c>
       <c r="L81" s="30" t="s">
         <v>254</v>
@@ -47306,37 +47346,37 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B82" s="146">
-        <v>1226</v>
+        <v>4162</v>
       </c>
       <c r="C82">
-        <v>451</v>
+        <v>923</v>
       </c>
       <c r="D82">
-        <v>195</v>
+        <v>429</v>
       </c>
       <c r="E82">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="F82">
-        <v>77</v>
-      </c>
-      <c r="G82">
-        <v>332</v>
+        <v>361</v>
+      </c>
+      <c r="G82" s="146">
+        <v>1435</v>
       </c>
       <c r="H82">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="I82">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>514</v>
+        <v>46</v>
+      </c>
+      <c r="K82" s="146">
+        <v>1019</v>
       </c>
       <c r="L82" s="30" t="s">
         <v>254</v>
@@ -47347,37 +47387,7 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" t="s">
-        <v>233</v>
-      </c>
-      <c r="B83" s="146">
-        <v>4162</v>
-      </c>
-      <c r="C83">
-        <v>923</v>
-      </c>
-      <c r="D83">
-        <v>429</v>
-      </c>
-      <c r="E83">
-        <v>154</v>
-      </c>
-      <c r="F83">
-        <v>361</v>
-      </c>
-      <c r="G83" s="146">
-        <v>1435</v>
-      </c>
-      <c r="H83">
-        <v>87</v>
-      </c>
-      <c r="I83">
-        <v>145</v>
-      </c>
-      <c r="J83">
-        <v>46</v>
-      </c>
-      <c r="K83" s="146">
-        <v>1019</v>
+        <v>234</v>
       </c>
       <c r="L83" s="30" t="s">
         <v>254</v>
@@ -47388,7 +47398,37 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
-        <v>234</v>
+        <v>235</v>
+      </c>
+      <c r="B84" s="146">
+        <v>5254</v>
+      </c>
+      <c r="C84" s="146">
+        <v>1353</v>
+      </c>
+      <c r="D84">
+        <v>610</v>
+      </c>
+      <c r="E84">
+        <v>284</v>
+      </c>
+      <c r="F84">
+        <v>438</v>
+      </c>
+      <c r="G84">
+        <v>673</v>
+      </c>
+      <c r="H84">
+        <v>109</v>
+      </c>
+      <c r="I84">
+        <v>182</v>
+      </c>
+      <c r="J84">
+        <v>46</v>
+      </c>
+      <c r="K84" s="146">
+        <v>1277</v>
       </c>
       <c r="L84" s="30" t="s">
         <v>254</v>
@@ -47399,37 +47439,37 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" t="s">
-        <v>235</v>
-      </c>
-      <c r="B85" s="146">
-        <v>5254</v>
-      </c>
-      <c r="C85" s="146">
-        <v>1353</v>
+        <v>236</v>
+      </c>
+      <c r="B85">
+        <v>135</v>
+      </c>
+      <c r="C85">
+        <v>21</v>
       </c>
       <c r="D85">
-        <v>610</v>
+        <v>14</v>
       </c>
       <c r="E85">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>438</v>
-      </c>
-      <c r="G85">
-        <v>673</v>
+        <v>0</v>
+      </c>
+      <c r="G85" s="146">
+        <v>1094</v>
       </c>
       <c r="H85">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>46</v>
-      </c>
-      <c r="K85" s="146">
-        <v>1277</v>
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>256</v>
       </c>
       <c r="L85" s="30" t="s">
         <v>254</v>
@@ -47440,37 +47480,7 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" t="s">
-        <v>236</v>
-      </c>
-      <c r="B86">
-        <v>135</v>
-      </c>
-      <c r="C86">
-        <v>21</v>
-      </c>
-      <c r="D86">
-        <v>14</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-      <c r="G86" s="146">
-        <v>1094</v>
-      </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="L86" s="30" t="s">
         <v>254</v>
@@ -47481,7 +47491,37 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" t="s">
-        <v>237</v>
+        <v>238</v>
+      </c>
+      <c r="B87">
+        <v>193</v>
+      </c>
+      <c r="C87">
+        <v>155</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>14</v>
+      </c>
+      <c r="G87">
+        <v>155</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>129</v>
       </c>
       <c r="L87" s="30" t="s">
         <v>254</v>
@@ -47492,25 +47532,25 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B88">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="C88">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F88">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -47522,7 +47562,7 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="L88" s="30" t="s">
         <v>254</v>
@@ -47533,37 +47573,37 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" t="s">
-        <v>239</v>
-      </c>
-      <c r="B89">
-        <v>310</v>
-      </c>
-      <c r="C89">
-        <v>40</v>
+        <v>240</v>
+      </c>
+      <c r="B89" s="146">
+        <v>4668</v>
+      </c>
+      <c r="C89" s="146">
+        <v>1088</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="E89">
-        <v>17</v>
+        <v>267</v>
       </c>
       <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89">
-        <v>87</v>
+        <v>424</v>
+      </c>
+      <c r="G89" s="146">
+        <v>1446</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>92</v>
+        <v>46</v>
+      </c>
+      <c r="K89" s="146">
+        <v>1268</v>
       </c>
       <c r="L89" s="30" t="s">
         <v>254</v>
@@ -47574,37 +47614,37 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" t="s">
-        <v>240</v>
-      </c>
-      <c r="B90" s="146">
-        <v>4668</v>
-      </c>
-      <c r="C90" s="146">
-        <v>1088</v>
+        <v>241</v>
+      </c>
+      <c r="B90">
+        <v>217</v>
+      </c>
+      <c r="C90">
+        <v>92</v>
       </c>
       <c r="D90">
-        <v>616</v>
+        <v>8</v>
       </c>
       <c r="E90">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>424</v>
-      </c>
-      <c r="G90" s="146">
-        <v>1446</v>
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>78</v>
       </c>
       <c r="H90">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="I90">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>46</v>
-      </c>
-      <c r="K90" s="146">
-        <v>1268</v>
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>44</v>
       </c>
       <c r="L90" s="30" t="s">
         <v>254</v>
@@ -47615,37 +47655,7 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" t="s">
-        <v>241</v>
-      </c>
-      <c r="B91">
-        <v>217</v>
-      </c>
-      <c r="C91">
-        <v>92</v>
-      </c>
-      <c r="D91">
-        <v>8</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-      <c r="G91">
-        <v>78</v>
-      </c>
-      <c r="H91">
-        <v>13</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <v>44</v>
+        <v>242</v>
       </c>
       <c r="L91" s="30" t="s">
         <v>254</v>
@@ -47656,7 +47666,37 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>243</v>
+      </c>
+      <c r="B92">
+        <v>161</v>
+      </c>
+      <c r="C92">
+        <v>39</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>60</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>23</v>
       </c>
       <c r="L92" s="30" t="s">
         <v>254</v>
@@ -47667,37 +47707,37 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" t="s">
-        <v>243</v>
-      </c>
-      <c r="B93">
-        <v>161</v>
-      </c>
-      <c r="C93">
-        <v>39</v>
+        <v>244</v>
+      </c>
+      <c r="B93" s="146">
+        <v>5227</v>
+      </c>
+      <c r="C93" s="146">
+        <v>1336</v>
       </c>
       <c r="D93">
-        <v>4</v>
+        <v>619</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="F93">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>60</v>
+        <v>438</v>
+      </c>
+      <c r="G93" s="146">
+        <v>1707</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>23</v>
+        <v>46</v>
+      </c>
+      <c r="K93" s="146">
+        <v>1511</v>
       </c>
       <c r="L93" s="30" t="s">
         <v>254</v>
@@ -47706,51 +47746,10 @@
         <v>255</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
-      <c r="A94" t="s">
-        <v>244</v>
-      </c>
-      <c r="B94" s="146">
-        <v>5227</v>
-      </c>
-      <c r="C94" s="146">
-        <v>1336</v>
-      </c>
-      <c r="D94">
-        <v>619</v>
-      </c>
-      <c r="E94">
-        <v>284</v>
-      </c>
-      <c r="F94">
-        <v>438</v>
-      </c>
-      <c r="G94" s="146">
-        <v>1707</v>
-      </c>
-      <c r="H94">
-        <v>109</v>
-      </c>
-      <c r="I94">
-        <v>182</v>
-      </c>
-      <c r="J94">
-        <v>46</v>
-      </c>
-      <c r="K94" s="146">
-        <v>1511</v>
-      </c>
-      <c r="L94" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="M94" s="141" t="s">
-        <v>255</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:A47"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="D22:D23"/>
@@ -48183,13 +48182,13 @@
       <c r="A24" s="455" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="428" t="s">
+      <c r="B24" s="436" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D24" s="430" t="s">
+      <c r="D24" s="438" t="s">
         <v>274</v>
       </c>
       <c r="E24" s="11" t="s">
@@ -48201,11 +48200,11 @@
     </row>
     <row r="25" spans="1:6" ht="27.75" thickBot="1">
       <c r="A25" s="456"/>
-      <c r="B25" s="429"/>
+      <c r="B25" s="437"/>
       <c r="C25" s="152" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="431"/>
+      <c r="D25" s="439"/>
       <c r="E25" s="30" t="s">
         <v>26</v>
       </c>
@@ -49578,7 +49577,7 @@
     <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36.75" thickBot="1">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>155</v>
@@ -49670,7 +49669,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="24.75" thickBot="1">
+    <row r="6" spans="1:10" ht="15.75" thickBot="1">
       <c r="A6" s="40" t="s">
         <v>295</v>
       </c>
@@ -49797,7 +49796,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="24.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
       <c r="A13" s="145">
         <v>2019</v>
       </c>
@@ -49829,7 +49828,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="24.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
       <c r="A14" s="145">
         <v>2020</v>
       </c>
@@ -49861,7 +49860,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24.75" thickBot="1">
+    <row r="15" spans="1:10" ht="15.75" thickBot="1">
       <c r="A15" s="72">
         <v>2021</v>
       </c>
@@ -49907,17 +49906,17 @@
     </row>
     <row r="17" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="18" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A18" s="467"/>
-      <c r="B18" s="469" t="s">
+      <c r="A18" s="462"/>
+      <c r="B18" s="464" t="s">
         <v>343</v>
       </c>
       <c r="C18" s="501" t="s">
         <v>344</v>
       </c>
-      <c r="D18" s="466" t="s">
+      <c r="D18" s="471" t="s">
         <v>345</v>
       </c>
-      <c r="E18" s="465"/>
+      <c r="E18" s="470"/>
       <c r="F18" s="171"/>
       <c r="G18" s="503" t="s">
         <v>346</v>
@@ -50256,7 +50255,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" thickBot="1"/>
-    <row r="34" spans="1:6" ht="24.75" thickBot="1">
+    <row r="34" spans="1:6" ht="15.75" thickBot="1">
       <c r="A34" s="71" t="s">
         <v>12</v>
       </c>
@@ -50273,7 +50272,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="36.75" thickBot="1">
+    <row r="35" spans="1:6" ht="15.75" thickBot="1">
       <c r="A35" s="40" t="s">
         <v>16</v>
       </c>
@@ -50290,7 +50289,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="36.75" thickBot="1">
+    <row r="36" spans="1:6" ht="15.75" thickBot="1">
       <c r="A36" s="40" t="s">
         <v>47</v>
       </c>
@@ -50307,7 +50306,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="36.75" thickBot="1">
+    <row r="37" spans="1:6" ht="15.75" thickBot="1">
       <c r="A37" s="40" t="s">
         <v>18</v>
       </c>
@@ -50324,7 +50323,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="36.75" thickBot="1">
+    <row r="38" spans="1:6" ht="15.75" thickBot="1">
       <c r="A38" s="40" t="s">
         <v>19</v>
       </c>
@@ -50341,7 +50340,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24.75" thickBot="1">
+    <row r="39" spans="1:6" ht="15.75" thickBot="1">
       <c r="A39" s="40" t="s">
         <v>20</v>
       </c>
@@ -50358,7 +50357,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.75" thickBot="1">
+    <row r="40" spans="1:6" ht="15.75" thickBot="1">
       <c r="A40" s="40" t="s">
         <v>22</v>
       </c>
@@ -50414,7 +50413,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A45" s="420" t="s">
+      <c r="A45" s="427" t="s">
         <v>16</v>
       </c>
       <c r="B45" s="7">
@@ -50434,7 +50433,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A46" s="421"/>
+      <c r="A46" s="428"/>
       <c r="B46" s="7">
         <v>2007</v>
       </c>
@@ -50452,7 +50451,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A47" s="421"/>
+      <c r="A47" s="428"/>
       <c r="B47" s="7">
         <v>2014</v>
       </c>
@@ -50470,7 +50469,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A48" s="422"/>
+      <c r="A48" s="429"/>
       <c r="B48" s="69">
         <v>2021</v>
       </c>
@@ -50488,7 +50487,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="423" t="s">
+      <c r="A49" s="430" t="s">
         <v>17</v>
       </c>
       <c r="B49" s="20">
@@ -50508,7 +50507,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="424"/>
+      <c r="A50" s="431"/>
       <c r="B50" s="20">
         <v>2007</v>
       </c>
@@ -50526,7 +50525,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A51" s="424"/>
+      <c r="A51" s="431"/>
       <c r="B51" s="20">
         <v>2014</v>
       </c>
@@ -50544,7 +50543,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="439"/>
+      <c r="A52" s="432"/>
       <c r="B52" s="20">
         <v>2021</v>
       </c>
@@ -50562,7 +50561,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="420" t="s">
+      <c r="A53" s="427" t="s">
         <v>18</v>
       </c>
       <c r="B53" s="7">
@@ -50582,7 +50581,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="421"/>
+      <c r="A54" s="428"/>
       <c r="B54" s="7">
         <v>2007</v>
       </c>
@@ -50600,7 +50599,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A55" s="421"/>
+      <c r="A55" s="428"/>
       <c r="B55" s="7">
         <v>2014</v>
       </c>
@@ -50618,7 +50617,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="422"/>
+      <c r="A56" s="429"/>
       <c r="B56" s="69">
         <v>2021</v>
       </c>
@@ -50636,7 +50635,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="423" t="s">
+      <c r="A57" s="430" t="s">
         <v>19</v>
       </c>
       <c r="B57" s="20">
@@ -50656,7 +50655,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="424"/>
+      <c r="A58" s="431"/>
       <c r="B58" s="20">
         <v>2007</v>
       </c>
@@ -50674,7 +50673,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="424"/>
+      <c r="A59" s="431"/>
       <c r="B59" s="20">
         <v>2014</v>
       </c>
@@ -50692,7 +50691,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="439"/>
+      <c r="A60" s="432"/>
       <c r="B60" s="20">
         <v>2021</v>
       </c>
@@ -50710,7 +50709,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="420" t="s">
+      <c r="A61" s="427" t="s">
         <v>20</v>
       </c>
       <c r="B61" s="7">
@@ -50730,7 +50729,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A62" s="421"/>
+      <c r="A62" s="428"/>
       <c r="B62" s="7">
         <v>2007</v>
       </c>
@@ -50748,7 +50747,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A63" s="421"/>
+      <c r="A63" s="428"/>
       <c r="B63" s="7">
         <v>2014</v>
       </c>
@@ -50766,7 +50765,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A64" s="422"/>
+      <c r="A64" s="429"/>
       <c r="B64" s="69">
         <v>2021</v>
       </c>
@@ -50784,7 +50783,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A65" s="423" t="s">
+      <c r="A65" s="430" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="20">
@@ -50804,7 +50803,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A66" s="424"/>
+      <c r="A66" s="431"/>
       <c r="B66" s="20">
         <v>2007</v>
       </c>
@@ -50822,7 +50821,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A67" s="424"/>
+      <c r="A67" s="431"/>
       <c r="B67" s="20">
         <v>2014</v>
       </c>
@@ -50840,7 +50839,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A68" s="425"/>
+      <c r="A68" s="433"/>
       <c r="B68" s="24">
         <v>2021</v>
       </c>
@@ -50882,7 +50881,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="60.75" thickBot="1">
+    <row r="72" spans="1:8" ht="24.75" thickBot="1">
       <c r="A72" s="40" t="s">
         <v>358</v>
       </c>
@@ -50908,7 +50907,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="60.75" thickBot="1">
+    <row r="73" spans="1:8" ht="24.75" thickBot="1">
       <c r="A73" s="40" t="s">
         <v>359</v>
       </c>
@@ -50934,7 +50933,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="36.75" thickBot="1">
+    <row r="74" spans="1:8" ht="24.75" thickBot="1">
       <c r="A74" s="42" t="s">
         <v>129</v>
       </c>
@@ -50961,17 +50960,17 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1"/>
-    <row r="77" spans="1:8" ht="48">
+    <row r="77" spans="1:8" ht="36">
       <c r="A77" s="455" t="s">
         <v>12</v>
       </c>
       <c r="B77" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="C77" s="447" t="s">
+      <c r="C77" s="453" t="s">
         <v>44</v>
       </c>
-      <c r="D77" s="430" t="s">
+      <c r="D77" s="438" t="s">
         <v>216</v>
       </c>
       <c r="E77" s="11" t="s">
@@ -50987,7 +50986,7 @@
         <v>361</v>
       </c>
       <c r="C78" s="478"/>
-      <c r="D78" s="431"/>
+      <c r="D78" s="439"/>
       <c r="E78" s="30" t="s">
         <v>51</v>
       </c>
@@ -50995,7 +50994,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="36.75" thickBot="1">
+    <row r="79" spans="1:8" ht="15.75" thickBot="1">
       <c r="A79" s="40" t="s">
         <v>16</v>
       </c>
@@ -51015,7 +51014,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="36.75" thickBot="1">
+    <row r="80" spans="1:8" ht="15.75" thickBot="1">
       <c r="A80" s="40" t="s">
         <v>47</v>
       </c>
@@ -51035,7 +51034,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="36.75" thickBot="1">
+    <row r="81" spans="1:10" ht="15.75" thickBot="1">
       <c r="A81" s="40" t="s">
         <v>18</v>
       </c>
@@ -51055,7 +51054,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="24.75" thickBot="1">
+    <row r="82" spans="1:10" ht="15.75" thickBot="1">
       <c r="A82" s="40" t="s">
         <v>20</v>
       </c>
@@ -51075,7 +51074,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="24.75" thickBot="1">
+    <row r="83" spans="1:10" ht="15.75" thickBot="1">
       <c r="A83" s="40" t="s">
         <v>48</v>
       </c>
@@ -51116,7 +51115,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="15.75" thickBot="1"/>
-    <row r="87" spans="1:10" ht="24.75" thickBot="1">
+    <row r="87" spans="1:10" ht="15.75" thickBot="1">
       <c r="A87" s="71" t="s">
         <v>363</v>
       </c>
@@ -51142,7 +51141,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="48.75" thickBot="1">
+    <row r="88" spans="1:10" ht="24.75" thickBot="1">
       <c r="A88" s="40" t="s">
         <v>369</v>
       </c>
@@ -51168,7 +51167,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="60.75" thickBot="1">
+    <row r="89" spans="1:10" ht="24.75" thickBot="1">
       <c r="A89" s="40" t="s">
         <v>370</v>
       </c>
@@ -51194,7 +51193,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="72.75" thickBot="1">
+    <row r="90" spans="1:10" ht="24.75" thickBot="1">
       <c r="A90" s="40" t="s">
         <v>371</v>
       </c>
@@ -51220,7 +51219,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="36.75" thickBot="1">
+    <row r="91" spans="1:10" ht="15.75" thickBot="1">
       <c r="A91" s="40" t="s">
         <v>372</v>
       </c>
@@ -51246,7 +51245,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="48.75" thickBot="1">
+    <row r="92" spans="1:10" ht="24.75" thickBot="1">
       <c r="A92" s="40" t="s">
         <v>373</v>
       </c>
@@ -51272,7 +51271,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="84.75" thickBot="1">
+    <row r="93" spans="1:10" ht="36.75" thickBot="1">
       <c r="A93" s="42" t="s">
         <v>374</v>
       </c>
@@ -51426,7 +51425,7 @@
       </c>
     </row>
     <row r="101" spans="1:10" ht="15.75" thickBot="1"/>
-    <row r="102" spans="1:10" ht="72.75" thickBot="1">
+    <row r="102" spans="1:10" ht="60.75" thickBot="1">
       <c r="A102" s="71" t="s">
         <v>387</v>
       </c>
@@ -51440,7 +51439,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="108.75" thickBot="1">
+    <row r="103" spans="1:10" ht="60.75" thickBot="1">
       <c r="A103" s="40" t="s">
         <v>389</v>
       </c>
@@ -51454,7 +51453,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="168.75" thickBot="1">
+    <row r="104" spans="1:10" ht="72.75" thickBot="1">
       <c r="A104" s="40" t="s">
         <v>390</v>
       </c>
@@ -51468,7 +51467,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="96.75" thickBot="1">
+    <row r="105" spans="1:10" ht="36.75" thickBot="1">
       <c r="A105" s="40" t="s">
         <v>391</v>
       </c>
@@ -51482,7 +51481,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="84.75" thickBot="1">
+    <row r="106" spans="1:10" ht="36.75" thickBot="1">
       <c r="A106" s="40" t="s">
         <v>392</v>
       </c>
@@ -51496,7 +51495,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="108.75" thickBot="1">
+    <row r="107" spans="1:10" ht="48.75" thickBot="1">
       <c r="A107" s="40" t="s">
         <v>393</v>
       </c>
@@ -51510,7 +51509,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="108.75" thickBot="1">
+    <row r="108" spans="1:10" ht="48.75" thickBot="1">
       <c r="A108" s="42" t="s">
         <v>394</v>
       </c>
